--- a/templates/PLANQLY_PREMIUM_TEMPLATE.xlsx
+++ b/templates/PLANQLY_PREMIUM_TEMPLATE.xlsx
@@ -762,6 +762,12 @@
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
+    <spPr>
+      <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+      </a:ln>
+    </spPr>
     <title>
       <tx>
         <rich>
@@ -778,6 +784,12 @@
       </tx>
     </title>
     <plotArea>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+        </a:ln>
+      </spPr>
       <pieChart>
         <varyColors val="1"/>
         <ser>
@@ -863,6 +875,12 @@
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+        </a:ln>
+      </spPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -874,6 +892,12 @@
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
+    <spPr>
+      <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+      </a:ln>
+    </spPr>
     <title>
       <tx>
         <rich>
@@ -890,6 +914,12 @@
       </tx>
     </title>
     <plotArea>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+        </a:ln>
+      </spPr>
       <barChart>
         <barDir val="col"/>
         <grouping val="clustered"/>
@@ -977,6 +1007,12 @@
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+        </a:ln>
+      </spPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -988,6 +1024,12 @@
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
+    <spPr>
+      <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+      </a:ln>
+    </spPr>
     <title>
       <tx>
         <rich>
@@ -1004,6 +1046,12 @@
       </tx>
     </title>
     <plotArea>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+        </a:ln>
+      </spPr>
       <areaChart>
         <grouping val="standard"/>
         <ser>
@@ -1059,6 +1107,12 @@
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+        </a:ln>
+      </spPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1070,6 +1124,12 @@
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
+    <spPr>
+      <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+      </a:ln>
+    </spPr>
     <title>
       <tx>
         <rich>
@@ -1086,6 +1146,12 @@
       </tx>
     </title>
     <plotArea>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+        </a:ln>
+      </spPr>
       <barChart>
         <barDir val="col"/>
         <grouping val="clustered"/>
@@ -1162,6 +1228,12 @@
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+        </a:ln>
+      </spPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1173,6 +1245,12 @@
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
+    <spPr>
+      <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+      </a:ln>
+    </spPr>
     <title>
       <tx>
         <rich>
@@ -1189,6 +1267,12 @@
       </tx>
     </title>
     <plotArea>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+        </a:ln>
+      </spPr>
       <lineChart>
         <grouping val="standard"/>
         <ser>
@@ -1279,6 +1363,12 @@
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+        </a:ln>
+      </spPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1290,6 +1380,12 @@
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
+    <spPr>
+      <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+      </a:ln>
+    </spPr>
     <title>
       <tx>
         <rich>
@@ -1306,6 +1402,12 @@
       </tx>
     </title>
     <plotArea>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+        </a:ln>
+      </spPr>
       <pieChart>
         <varyColors val="1"/>
         <ser>
@@ -1423,6 +1525,12 @@
     </plotArea>
     <legend>
       <legendPos val="r"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+        </a:ln>
+      </spPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1436,10 +1544,10 @@
     <from>
       <col>7</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3600000" cy="3960000"/>
+    <ext cx="3000000" cy="3000000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1458,10 +1566,10 @@
     <from>
       <col>13</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="3960000"/>
+    <ext cx="3000000" cy="3000000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1478,12 +1586,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>20</col>
+      <col>19</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="3960000"/>
+    <ext cx="3000000" cy="3000000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1502,10 +1610,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4320000" cy="3600000"/>
+    <ext cx="4200000" cy="3200000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -1522,12 +1630,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>8</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="3600000"/>
+    <ext cx="4200000" cy="3200000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -1544,12 +1652,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>16</col>
+      <col>15</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5040000" cy="3600000"/>
+    <ext cx="4200000" cy="3200000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>

--- a/templates/PLANQLY_PREMIUM_TEMPLATE.xlsx
+++ b/templates/PLANQLY_PREMIUM_TEMPLATE.xlsx
@@ -9,17 +9,20 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLANQLY Budget" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PLANQLY Budget'!$B$77:$H$85</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00;[Red]-$#,##0.00"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="53">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -237,8 +240,96 @@
       <color rgb="FF9CA3AF"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Aptos Display"/>
+      <b val="1"/>
+      <color rgb="FFF8FAFC"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <i val="1"/>
+      <color rgb="FF94A3B8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FF94A3B8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos Display"/>
+      <b val="1"/>
+      <color rgb="FFF8FAFC"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="FFF8FAFC"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="FF94A3B8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FFF8FAFC"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FFF8FAFC"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FFD4AF37"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos Display"/>
+      <b val="1"/>
+      <color rgb="FFD4AF37"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FF22C55E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FF94A3B8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos Display"/>
+      <b val="1"/>
+      <color rgb="FF22C55E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FF22C55E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FFEF4444"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -275,8 +366,28 @@
         <fgColor rgb="FF374151"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B1220"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF172033"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF121A2B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D2940"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -419,11 +530,180 @@
         <color rgb="FF06B6D4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF9CA3AF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF8B5CF6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF06B6D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFF59E0B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF10B981"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF3B82F6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3B82F6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFEF4444"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border/>
+    <border>
+      <bottom style="medium">
+        <color rgb="FFD4AF37"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF334155"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF334155"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF22C55E"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF38BDF8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD4AF37"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFEF4444"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF334155"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD4AF37"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD4AF37"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD4AF37"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD4AF37"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1E293B"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF1E293B"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1E293B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF1E293B"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -682,10 +962,190 @@
     <xf numFmtId="0" fontId="37" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="9" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="9" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="9" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="9" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="10" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="9" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="11" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="9" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="42" fillId="10" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="9" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="46" fillId="9" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="8" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="11" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="11" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="10" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="42" fillId="10" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="51" fillId="10" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="10" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="10" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="9" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="42" fillId="9" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="51" fillId="9" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="9" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="9" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="9" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="10" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="52" fillId="9" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="52" fillId="10" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="46" fillId="11" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="10" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEF4444"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF052E16"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF22C55E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1540,14 +2000,19 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
+  <twoCellAnchor editAs="twoCell">
     <from>
       <col>7</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3000000" cy="3000000"/>
+    <to>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1561,15 +2026,20 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
     <from>
       <col>13</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3000000" cy="3000000"/>
+    <to>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1583,15 +2053,20 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
     <from>
-      <col>19</col>
+      <col>20</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3000000" cy="3000000"/>
+    <to>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1605,15 +2080,20 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4200000" cy="3200000"/>
+    <to>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -1627,15 +2107,20 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
     <from>
       <col>8</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4200000" cy="3200000"/>
+    <to>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -1649,15 +2134,20 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="twoCell">
     <from>
-      <col>15</col>
+      <col>17</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4200000" cy="3200000"/>
+    <to>
+      <col>26</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </to>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -1671,7 +2161,7 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </oneCellAnchor>
+  </twoCellAnchor>
 </wsDr>
 </file>
 
@@ -1961,7 +2451,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="003B82F6"/>
+    <tabColor rgb="FFD4AF37"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1994,35 +2484,53 @@
     <col width="9" customWidth="1" min="24" max="24"/>
     <col width="9" customWidth="1" min="25" max="25"/>
     <col width="0.8" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
+    <col hidden="1" width="13" customWidth="1" min="47" max="47"/>
+    <col hidden="1" width="13" customWidth="1" min="48" max="48"/>
+    <col hidden="1" width="13" customWidth="1" min="49" max="49"/>
+    <col hidden="1" width="13" customWidth="1" min="50" max="50"/>
+    <col hidden="1" width="13" customWidth="1" min="51" max="51"/>
+    <col hidden="1" width="13" customWidth="1" min="52" max="52"/>
+    <col hidden="1" width="13" customWidth="1" min="53" max="53"/>
+    <col hidden="1" width="13" customWidth="1" min="54" max="54"/>
+    <col hidden="1" width="13" customWidth="1" min="55" max="55"/>
+    <col hidden="1" width="13" customWidth="1" min="56" max="56"/>
+    <col hidden="1" width="13" customWidth="1" min="57" max="57"/>
   </cols>
   <sheetData>
     <row r="1" ht="6" customHeight="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="1" t="n"/>
-      <c r="R1" s="1" t="n"/>
-      <c r="S1" s="1" t="n"/>
-      <c r="T1" s="1" t="n"/>
-      <c r="U1" s="1" t="n"/>
-      <c r="V1" s="1" t="n"/>
-      <c r="W1" s="1" t="n"/>
-      <c r="X1" s="1" t="n"/>
-      <c r="Y1" s="1" t="n"/>
-      <c r="Z1" s="1" t="n"/>
+      <c r="A1" s="94" t="n"/>
+      <c r="B1" s="94" t="n"/>
+      <c r="C1" s="94" t="n"/>
+      <c r="D1" s="94" t="n"/>
+      <c r="E1" s="94" t="n"/>
+      <c r="F1" s="94" t="n"/>
+      <c r="G1" s="94" t="n"/>
+      <c r="H1" s="94" t="n"/>
+      <c r="I1" s="94" t="n"/>
+      <c r="J1" s="94" t="n"/>
+      <c r="K1" s="94" t="n"/>
+      <c r="L1" s="94" t="n"/>
+      <c r="M1" s="94" t="n"/>
+      <c r="N1" s="94" t="n"/>
+      <c r="O1" s="94" t="n"/>
+      <c r="P1" s="94" t="n"/>
+      <c r="Q1" s="94" t="n"/>
+      <c r="R1" s="94" t="n"/>
+      <c r="S1" s="94" t="n"/>
+      <c r="T1" s="94" t="n"/>
+      <c r="U1" s="94" t="n"/>
+      <c r="V1" s="94" t="n"/>
+      <c r="W1" s="94" t="n"/>
+      <c r="X1" s="94" t="n"/>
+      <c r="Y1" s="94" t="n"/>
+      <c r="Z1" s="94" t="n"/>
       <c r="AA1" s="1" t="n"/>
       <c r="AB1" s="1" t="n"/>
       <c r="AC1" s="1" t="n"/>
@@ -2058,13 +2566,36 @@
       <c r="BG1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="94" t="n"/>
+      <c r="B2" s="95" t="inlineStr">
         <is>
           <t>ABRIL  2026</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="n"/>
+      <c r="C2" s="95" t="n"/>
+      <c r="D2" s="95" t="n"/>
+      <c r="E2" s="95" t="n"/>
+      <c r="F2" s="95" t="n"/>
+      <c r="G2" s="95" t="n"/>
+      <c r="H2" s="95" t="n"/>
+      <c r="I2" s="95" t="n"/>
+      <c r="J2" s="95" t="n"/>
+      <c r="K2" s="95" t="n"/>
+      <c r="L2" s="95" t="n"/>
+      <c r="M2" s="95" t="n"/>
+      <c r="N2" s="95" t="n"/>
+      <c r="O2" s="95" t="n"/>
+      <c r="P2" s="95" t="n"/>
+      <c r="Q2" s="95" t="n"/>
+      <c r="R2" s="95" t="n"/>
+      <c r="S2" s="95" t="n"/>
+      <c r="T2" s="95" t="n"/>
+      <c r="U2" s="95" t="n"/>
+      <c r="V2" s="95" t="n"/>
+      <c r="W2" s="95" t="n"/>
+      <c r="X2" s="95" t="n"/>
+      <c r="Y2" s="95" t="n"/>
+      <c r="Z2" s="95" t="n"/>
       <c r="AA2" s="1" t="n"/>
       <c r="AB2" s="1" t="n"/>
       <c r="AC2" s="1" t="n"/>
@@ -2100,13 +2631,36 @@
       <c r="BG2" s="1" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="94" t="n"/>
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>PLANQLY ASSETS  ·  João  ·  Budget Planner  ·  2026-04-01 → 2026-04-30</t>
         </is>
       </c>
-      <c r="Z3" s="1" t="n"/>
+      <c r="C3" s="96" t="n"/>
+      <c r="D3" s="96" t="n"/>
+      <c r="E3" s="96" t="n"/>
+      <c r="F3" s="96" t="n"/>
+      <c r="G3" s="96" t="n"/>
+      <c r="H3" s="96" t="n"/>
+      <c r="I3" s="96" t="n"/>
+      <c r="J3" s="96" t="n"/>
+      <c r="K3" s="96" t="n"/>
+      <c r="L3" s="96" t="n"/>
+      <c r="M3" s="96" t="n"/>
+      <c r="N3" s="96" t="n"/>
+      <c r="O3" s="96" t="n"/>
+      <c r="P3" s="96" t="n"/>
+      <c r="Q3" s="96" t="n"/>
+      <c r="R3" s="96" t="n"/>
+      <c r="S3" s="96" t="n"/>
+      <c r="T3" s="96" t="n"/>
+      <c r="U3" s="96" t="n"/>
+      <c r="V3" s="96" t="n"/>
+      <c r="W3" s="96" t="n"/>
+      <c r="X3" s="96" t="n"/>
+      <c r="Y3" s="96" t="n"/>
+      <c r="Z3" s="96" t="n"/>
       <c r="AA3" s="1" t="n"/>
       <c r="AB3" s="1" t="n"/>
       <c r="AC3" s="1" t="n"/>
@@ -2142,32 +2696,32 @@
       <c r="BG3" s="1" t="n"/>
     </row>
     <row r="4" ht="8" customHeight="1">
-      <c r="A4" s="1" t="n"/>
-      <c r="B4" s="1" t="n"/>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
-      <c r="I4" s="1" t="n"/>
-      <c r="J4" s="1" t="n"/>
-      <c r="K4" s="1" t="n"/>
-      <c r="L4" s="1" t="n"/>
-      <c r="M4" s="1" t="n"/>
-      <c r="N4" s="1" t="n"/>
-      <c r="O4" s="1" t="n"/>
-      <c r="P4" s="1" t="n"/>
-      <c r="Q4" s="1" t="n"/>
-      <c r="R4" s="1" t="n"/>
-      <c r="S4" s="1" t="n"/>
-      <c r="T4" s="1" t="n"/>
-      <c r="U4" s="1" t="n"/>
-      <c r="V4" s="1" t="n"/>
-      <c r="W4" s="1" t="n"/>
-      <c r="X4" s="1" t="n"/>
-      <c r="Y4" s="1" t="n"/>
-      <c r="Z4" s="1" t="n"/>
+      <c r="A4" s="94" t="n"/>
+      <c r="B4" s="94" t="n"/>
+      <c r="C4" s="94" t="n"/>
+      <c r="D4" s="94" t="n"/>
+      <c r="E4" s="94" t="n"/>
+      <c r="F4" s="94" t="n"/>
+      <c r="G4" s="94" t="n"/>
+      <c r="H4" s="94" t="n"/>
+      <c r="I4" s="94" t="n"/>
+      <c r="J4" s="94" t="n"/>
+      <c r="K4" s="94" t="n"/>
+      <c r="L4" s="94" t="n"/>
+      <c r="M4" s="94" t="n"/>
+      <c r="N4" s="94" t="n"/>
+      <c r="O4" s="94" t="n"/>
+      <c r="P4" s="94" t="n"/>
+      <c r="Q4" s="94" t="n"/>
+      <c r="R4" s="94" t="n"/>
+      <c r="S4" s="94" t="n"/>
+      <c r="T4" s="94" t="n"/>
+      <c r="U4" s="94" t="n"/>
+      <c r="V4" s="94" t="n"/>
+      <c r="W4" s="94" t="n"/>
+      <c r="X4" s="94" t="n"/>
+      <c r="Y4" s="94" t="n"/>
+      <c r="Z4" s="94" t="n"/>
       <c r="AA4" s="1" t="n"/>
       <c r="AB4" s="1" t="n"/>
       <c r="AC4" s="1" t="n"/>
@@ -2203,32 +2757,32 @@
       <c r="BG4" s="1" t="n"/>
     </row>
     <row r="5" ht="6" customHeight="1">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="1" t="n"/>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
-      <c r="H5" s="1" t="n"/>
-      <c r="I5" s="1" t="n"/>
-      <c r="J5" s="1" t="n"/>
-      <c r="K5" s="1" t="n"/>
-      <c r="L5" s="1" t="n"/>
-      <c r="M5" s="1" t="n"/>
-      <c r="N5" s="1" t="n"/>
-      <c r="O5" s="1" t="n"/>
-      <c r="P5" s="1" t="n"/>
-      <c r="Q5" s="1" t="n"/>
-      <c r="R5" s="1" t="n"/>
-      <c r="S5" s="1" t="n"/>
-      <c r="T5" s="1" t="n"/>
-      <c r="U5" s="1" t="n"/>
-      <c r="V5" s="1" t="n"/>
-      <c r="W5" s="1" t="n"/>
-      <c r="X5" s="1" t="n"/>
-      <c r="Y5" s="1" t="n"/>
-      <c r="Z5" s="1" t="n"/>
+      <c r="A5" s="94" t="n"/>
+      <c r="B5" s="94" t="n"/>
+      <c r="C5" s="94" t="n"/>
+      <c r="D5" s="94" t="n"/>
+      <c r="E5" s="94" t="n"/>
+      <c r="F5" s="94" t="n"/>
+      <c r="G5" s="94" t="n"/>
+      <c r="H5" s="94" t="n"/>
+      <c r="I5" s="94" t="n"/>
+      <c r="J5" s="94" t="n"/>
+      <c r="K5" s="94" t="n"/>
+      <c r="L5" s="94" t="n"/>
+      <c r="M5" s="94" t="n"/>
+      <c r="N5" s="94" t="n"/>
+      <c r="O5" s="94" t="n"/>
+      <c r="P5" s="94" t="n"/>
+      <c r="Q5" s="94" t="n"/>
+      <c r="R5" s="94" t="n"/>
+      <c r="S5" s="94" t="n"/>
+      <c r="T5" s="94" t="n"/>
+      <c r="U5" s="94" t="n"/>
+      <c r="V5" s="94" t="n"/>
+      <c r="W5" s="94" t="n"/>
+      <c r="X5" s="94" t="n"/>
+      <c r="Y5" s="94" t="n"/>
+      <c r="Z5" s="94" t="n"/>
       <c r="AA5" s="1" t="n"/>
       <c r="AB5" s="1" t="n"/>
       <c r="AC5" s="1" t="n"/>
@@ -2263,53 +2817,53 @@
       <c r="BF5" s="1" t="n"/>
       <c r="BG5" s="1" t="n"/>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="1" t="n"/>
-      <c r="B6" s="4" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="94" t="n"/>
+      <c r="B6" s="97" t="inlineStr">
         <is>
           <t>LEFT FOR BUDGETING</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="1" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="C6" s="97" t="n"/>
+      <c r="D6" s="97" t="n"/>
+      <c r="E6" s="97" t="n"/>
+      <c r="F6" s="97" t="n"/>
+      <c r="G6" s="98" t="inlineStr">
         <is>
           <t>TOTAL BUDGETED</t>
         </is>
       </c>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="1" t="n"/>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="H6" s="98" t="n"/>
+      <c r="I6" s="98" t="n"/>
+      <c r="J6" s="98" t="n"/>
+      <c r="K6" s="98" t="n"/>
+      <c r="L6" s="99" t="inlineStr">
         <is>
           <t>LEFT TO SPEND</t>
         </is>
       </c>
-      <c r="M6" s="7" t="n"/>
-      <c r="N6" s="7" t="n"/>
-      <c r="O6" s="7" t="n"/>
-      <c r="P6" s="1" t="n"/>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="M6" s="99" t="n"/>
+      <c r="N6" s="99" t="n"/>
+      <c r="O6" s="99" t="n"/>
+      <c r="P6" s="99" t="n"/>
+      <c r="Q6" s="100" t="inlineStr">
         <is>
           <t>TOTAL SPENT</t>
         </is>
       </c>
-      <c r="R6" s="9" t="n"/>
-      <c r="S6" s="9" t="n"/>
-      <c r="T6" s="9" t="n"/>
-      <c r="U6" s="1" t="n"/>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="R6" s="100" t="n"/>
+      <c r="S6" s="100" t="n"/>
+      <c r="T6" s="100" t="n"/>
+      <c r="U6" s="100" t="n"/>
+      <c r="V6" s="97" t="inlineStr">
         <is>
           <t>ENDING BALANCE</t>
         </is>
       </c>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-      <c r="Y6" s="5" t="n"/>
-      <c r="Z6" s="10" t="inlineStr">
+      <c r="W6" s="97" t="n"/>
+      <c r="X6" s="97" t="n"/>
+      <c r="Y6" s="97" t="n"/>
+      <c r="Z6" s="99" t="inlineStr">
         <is>
           <t>CURRENCY</t>
         </is>
@@ -2349,52 +2903,52 @@
       <c r="BG6" s="1" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="A7" s="94" t="n"/>
+      <c r="B7" s="101" t="inlineStr">
         <is>
           <t>+$1,149</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="1" t="n"/>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="C7" s="102" t="n"/>
+      <c r="D7" s="102" t="n"/>
+      <c r="E7" s="102" t="n"/>
+      <c r="F7" s="102" t="n"/>
+      <c r="G7" s="103" t="inlineStr">
         <is>
           <t>$1,914</t>
         </is>
       </c>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="1" t="n"/>
-      <c r="L7" s="12" t="inlineStr">
+      <c r="H7" s="102" t="n"/>
+      <c r="I7" s="102" t="n"/>
+      <c r="J7" s="102" t="n"/>
+      <c r="K7" s="102" t="n"/>
+      <c r="L7" s="101" t="inlineStr">
         <is>
           <t>$64</t>
         </is>
       </c>
-      <c r="M7" s="7" t="n"/>
-      <c r="N7" s="7" t="n"/>
-      <c r="O7" s="7" t="n"/>
-      <c r="P7" s="1" t="n"/>
-      <c r="Q7" s="13" t="inlineStr">
+      <c r="M7" s="102" t="n"/>
+      <c r="N7" s="102" t="n"/>
+      <c r="O7" s="102" t="n"/>
+      <c r="P7" s="102" t="n"/>
+      <c r="Q7" s="103" t="inlineStr">
         <is>
           <t>$2,012</t>
         </is>
       </c>
-      <c r="R7" s="9" t="n"/>
-      <c r="S7" s="9" t="n"/>
-      <c r="T7" s="9" t="n"/>
-      <c r="U7" s="1" t="n"/>
-      <c r="V7" s="11" t="inlineStr">
+      <c r="R7" s="102" t="n"/>
+      <c r="S7" s="102" t="n"/>
+      <c r="T7" s="102" t="n"/>
+      <c r="U7" s="102" t="n"/>
+      <c r="V7" s="101" t="inlineStr">
         <is>
           <t>+$1,149</t>
         </is>
       </c>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-      <c r="Y7" s="5" t="n"/>
-      <c r="Z7" s="14" t="inlineStr">
+      <c r="W7" s="102" t="n"/>
+      <c r="X7" s="102" t="n"/>
+      <c r="Y7" s="102" t="n"/>
+      <c r="Z7" s="103" t="inlineStr">
         <is>
           <t>$</t>
         </is>
@@ -2434,32 +2988,32 @@
       <c r="BG7" s="1" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="1" t="n"/>
-      <c r="B8" s="15" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="1" t="n"/>
-      <c r="G8" s="16" t="inlineStr"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="1" t="n"/>
-      <c r="L8" s="16" t="inlineStr"/>
-      <c r="M8" s="7" t="n"/>
-      <c r="N8" s="7" t="n"/>
-      <c r="O8" s="7" t="n"/>
-      <c r="P8" s="1" t="n"/>
-      <c r="Q8" s="17" t="inlineStr"/>
-      <c r="R8" s="9" t="n"/>
-      <c r="S8" s="9" t="n"/>
-      <c r="T8" s="9" t="n"/>
-      <c r="U8" s="1" t="n"/>
-      <c r="V8" s="15" t="inlineStr"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-      <c r="Y8" s="5" t="n"/>
-      <c r="Z8" s="18" t="inlineStr"/>
+      <c r="A8" s="94" t="n"/>
+      <c r="B8" s="104" t="inlineStr"/>
+      <c r="C8" s="105" t="n"/>
+      <c r="D8" s="105" t="n"/>
+      <c r="E8" s="105" t="n"/>
+      <c r="F8" s="94" t="n"/>
+      <c r="G8" s="106" t="inlineStr"/>
+      <c r="H8" s="105" t="n"/>
+      <c r="I8" s="105" t="n"/>
+      <c r="J8" s="105" t="n"/>
+      <c r="K8" s="94" t="n"/>
+      <c r="L8" s="106" t="inlineStr"/>
+      <c r="M8" s="105" t="n"/>
+      <c r="N8" s="105" t="n"/>
+      <c r="O8" s="105" t="n"/>
+      <c r="P8" s="94" t="n"/>
+      <c r="Q8" s="107" t="inlineStr"/>
+      <c r="R8" s="105" t="n"/>
+      <c r="S8" s="105" t="n"/>
+      <c r="T8" s="105" t="n"/>
+      <c r="U8" s="94" t="n"/>
+      <c r="V8" s="104" t="inlineStr"/>
+      <c r="W8" s="105" t="n"/>
+      <c r="X8" s="105" t="n"/>
+      <c r="Y8" s="105" t="n"/>
+      <c r="Z8" s="108" t="inlineStr"/>
       <c r="AA8" s="1" t="n"/>
       <c r="AB8" s="1" t="n"/>
       <c r="AC8" s="1" t="n"/>
@@ -2495,32 +3049,32 @@
       <c r="BG8" s="1" t="n"/>
     </row>
     <row r="9" ht="6" customHeight="1">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="1" t="n"/>
-      <c r="C9" s="1" t="n"/>
-      <c r="D9" s="1" t="n"/>
-      <c r="E9" s="1" t="n"/>
-      <c r="F9" s="1" t="n"/>
-      <c r="G9" s="1" t="n"/>
-      <c r="H9" s="1" t="n"/>
-      <c r="I9" s="1" t="n"/>
-      <c r="J9" s="1" t="n"/>
-      <c r="K9" s="1" t="n"/>
-      <c r="L9" s="1" t="n"/>
-      <c r="M9" s="1" t="n"/>
-      <c r="N9" s="1" t="n"/>
-      <c r="O9" s="1" t="n"/>
-      <c r="P9" s="1" t="n"/>
-      <c r="Q9" s="1" t="n"/>
-      <c r="R9" s="1" t="n"/>
-      <c r="S9" s="1" t="n"/>
-      <c r="T9" s="1" t="n"/>
-      <c r="U9" s="1" t="n"/>
-      <c r="V9" s="1" t="n"/>
-      <c r="W9" s="1" t="n"/>
-      <c r="X9" s="1" t="n"/>
-      <c r="Y9" s="1" t="n"/>
-      <c r="Z9" s="1" t="n"/>
+      <c r="A9" s="94" t="n"/>
+      <c r="B9" s="94" t="n"/>
+      <c r="C9" s="94" t="n"/>
+      <c r="D9" s="94" t="n"/>
+      <c r="E9" s="94" t="n"/>
+      <c r="F9" s="94" t="n"/>
+      <c r="G9" s="94" t="n"/>
+      <c r="H9" s="94" t="n"/>
+      <c r="I9" s="94" t="n"/>
+      <c r="J9" s="94" t="n"/>
+      <c r="K9" s="94" t="n"/>
+      <c r="L9" s="94" t="n"/>
+      <c r="M9" s="94" t="n"/>
+      <c r="N9" s="94" t="n"/>
+      <c r="O9" s="94" t="n"/>
+      <c r="P9" s="94" t="n"/>
+      <c r="Q9" s="94" t="n"/>
+      <c r="R9" s="94" t="n"/>
+      <c r="S9" s="94" t="n"/>
+      <c r="T9" s="94" t="n"/>
+      <c r="U9" s="94" t="n"/>
+      <c r="V9" s="94" t="n"/>
+      <c r="W9" s="94" t="n"/>
+      <c r="X9" s="94" t="n"/>
+      <c r="Y9" s="94" t="n"/>
+      <c r="Z9" s="94" t="n"/>
       <c r="AA9" s="1" t="n"/>
       <c r="AB9" s="1" t="n"/>
       <c r="AC9" s="1" t="n"/>
@@ -2556,32 +3110,32 @@
       <c r="BG9" s="1" t="n"/>
     </row>
     <row r="10" ht="8" customHeight="1">
-      <c r="A10" s="1" t="n"/>
-      <c r="B10" s="1" t="n"/>
-      <c r="C10" s="1" t="n"/>
-      <c r="D10" s="1" t="n"/>
-      <c r="E10" s="1" t="n"/>
-      <c r="F10" s="1" t="n"/>
-      <c r="G10" s="1" t="n"/>
-      <c r="H10" s="1" t="n"/>
-      <c r="I10" s="1" t="n"/>
-      <c r="J10" s="1" t="n"/>
-      <c r="K10" s="1" t="n"/>
-      <c r="L10" s="1" t="n"/>
-      <c r="M10" s="1" t="n"/>
-      <c r="N10" s="1" t="n"/>
-      <c r="O10" s="1" t="n"/>
-      <c r="P10" s="1" t="n"/>
-      <c r="Q10" s="1" t="n"/>
-      <c r="R10" s="1" t="n"/>
-      <c r="S10" s="1" t="n"/>
-      <c r="T10" s="1" t="n"/>
-      <c r="U10" s="1" t="n"/>
-      <c r="V10" s="1" t="n"/>
-      <c r="W10" s="1" t="n"/>
-      <c r="X10" s="1" t="n"/>
-      <c r="Y10" s="1" t="n"/>
-      <c r="Z10" s="1" t="n"/>
+      <c r="A10" s="94" t="n"/>
+      <c r="B10" s="94" t="n"/>
+      <c r="C10" s="94" t="n"/>
+      <c r="D10" s="94" t="n"/>
+      <c r="E10" s="94" t="n"/>
+      <c r="F10" s="94" t="n"/>
+      <c r="G10" s="94" t="n"/>
+      <c r="H10" s="94" t="n"/>
+      <c r="I10" s="94" t="n"/>
+      <c r="J10" s="94" t="n"/>
+      <c r="K10" s="94" t="n"/>
+      <c r="L10" s="94" t="n"/>
+      <c r="M10" s="94" t="n"/>
+      <c r="N10" s="94" t="n"/>
+      <c r="O10" s="94" t="n"/>
+      <c r="P10" s="94" t="n"/>
+      <c r="Q10" s="94" t="n"/>
+      <c r="R10" s="94" t="n"/>
+      <c r="S10" s="94" t="n"/>
+      <c r="T10" s="94" t="n"/>
+      <c r="U10" s="94" t="n"/>
+      <c r="V10" s="94" t="n"/>
+      <c r="W10" s="94" t="n"/>
+      <c r="X10" s="94" t="n"/>
+      <c r="Y10" s="94" t="n"/>
+      <c r="Z10" s="94" t="n"/>
       <c r="AA10" s="1" t="n"/>
       <c r="AB10" s="1" t="n"/>
       <c r="AC10" s="1" t="n"/>
@@ -2617,32 +3171,36 @@
       <c r="BG10" s="1" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="A11" s="94" t="n"/>
+      <c r="B11" s="109" t="inlineStr">
         <is>
           <t>To get started, set your start date and starting balance</t>
         </is>
       </c>
-      <c r="G11" s="1" t="n"/>
-      <c r="H11" s="1" t="n"/>
-      <c r="I11" s="1" t="n"/>
-      <c r="J11" s="1" t="n"/>
-      <c r="K11" s="1" t="n"/>
-      <c r="L11" s="1" t="n"/>
-      <c r="M11" s="1" t="n"/>
-      <c r="N11" s="1" t="n"/>
-      <c r="O11" s="1" t="n"/>
-      <c r="P11" s="1" t="n"/>
-      <c r="Q11" s="1" t="n"/>
-      <c r="R11" s="1" t="n"/>
-      <c r="S11" s="1" t="n"/>
-      <c r="T11" s="1" t="n"/>
-      <c r="U11" s="1" t="n"/>
-      <c r="V11" s="1" t="n"/>
-      <c r="W11" s="1" t="n"/>
-      <c r="X11" s="1" t="n"/>
-      <c r="Y11" s="1" t="n"/>
-      <c r="Z11" s="1" t="n"/>
+      <c r="C11" s="109" t="n"/>
+      <c r="D11" s="109" t="n"/>
+      <c r="E11" s="109" t="n"/>
+      <c r="F11" s="109" t="n"/>
+      <c r="G11" s="94" t="n"/>
+      <c r="H11" s="94" t="n"/>
+      <c r="I11" s="94" t="n"/>
+      <c r="J11" s="94" t="n"/>
+      <c r="K11" s="94" t="n"/>
+      <c r="L11" s="94" t="n"/>
+      <c r="M11" s="94" t="n"/>
+      <c r="N11" s="94" t="n"/>
+      <c r="O11" s="94" t="n"/>
+      <c r="P11" s="94" t="n"/>
+      <c r="Q11" s="94" t="n"/>
+      <c r="R11" s="94" t="n"/>
+      <c r="S11" s="94" t="n"/>
+      <c r="T11" s="94" t="n"/>
+      <c r="U11" s="94" t="n"/>
+      <c r="V11" s="94" t="n"/>
+      <c r="W11" s="94" t="n"/>
+      <c r="X11" s="94" t="n"/>
+      <c r="Y11" s="94" t="n"/>
+      <c r="Z11" s="94" t="n"/>
       <c r="AA11" s="1" t="n"/>
       <c r="AB11" s="1" t="n"/>
       <c r="AC11" s="1" t="n"/>
@@ -2678,40 +3236,40 @@
       <c r="BG11" s="1" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="1" t="n"/>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="A12" s="94" t="n"/>
+      <c r="B12" s="110" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="C12" s="110" t="n"/>
+      <c r="D12" s="102" t="inlineStr">
         <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="E12" s="23" t="n"/>
-      <c r="F12" s="21" t="n"/>
-      <c r="G12" s="1" t="n"/>
-      <c r="H12" s="1" t="n"/>
-      <c r="I12" s="1" t="n"/>
-      <c r="J12" s="1" t="n"/>
-      <c r="K12" s="1" t="n"/>
-      <c r="L12" s="1" t="n"/>
-      <c r="M12" s="1" t="n"/>
-      <c r="N12" s="1" t="n"/>
-      <c r="O12" s="1" t="n"/>
-      <c r="P12" s="1" t="n"/>
-      <c r="Q12" s="1" t="n"/>
-      <c r="R12" s="1" t="n"/>
-      <c r="S12" s="1" t="n"/>
-      <c r="T12" s="1" t="n"/>
-      <c r="U12" s="1" t="n"/>
-      <c r="V12" s="1" t="n"/>
-      <c r="W12" s="1" t="n"/>
-      <c r="X12" s="1" t="n"/>
-      <c r="Y12" s="1" t="n"/>
-      <c r="Z12" s="1" t="n"/>
+      <c r="E12" s="102" t="n"/>
+      <c r="F12" s="111" t="n"/>
+      <c r="G12" s="94" t="n"/>
+      <c r="H12" s="94" t="n"/>
+      <c r="I12" s="94" t="n"/>
+      <c r="J12" s="94" t="n"/>
+      <c r="K12" s="94" t="n"/>
+      <c r="L12" s="94" t="n"/>
+      <c r="M12" s="94" t="n"/>
+      <c r="N12" s="94" t="n"/>
+      <c r="O12" s="94" t="n"/>
+      <c r="P12" s="94" t="n"/>
+      <c r="Q12" s="94" t="n"/>
+      <c r="R12" s="94" t="n"/>
+      <c r="S12" s="94" t="n"/>
+      <c r="T12" s="94" t="n"/>
+      <c r="U12" s="94" t="n"/>
+      <c r="V12" s="94" t="n"/>
+      <c r="W12" s="94" t="n"/>
+      <c r="X12" s="94" t="n"/>
+      <c r="Y12" s="94" t="n"/>
+      <c r="Z12" s="94" t="n"/>
       <c r="AA12" s="1" t="n"/>
       <c r="AB12" s="1" t="n"/>
       <c r="AC12" s="1" t="n"/>
@@ -2747,40 +3305,40 @@
       <c r="BG12" s="1" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="A13" s="94" t="n"/>
+      <c r="B13" s="110" t="inlineStr">
         <is>
           <t>End Date (Max 31 Days)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="n"/>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="C13" s="110" t="n"/>
+      <c r="D13" s="102" t="inlineStr">
         <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="E13" s="23" t="n"/>
-      <c r="F13" s="21" t="n"/>
-      <c r="G13" s="1" t="n"/>
-      <c r="H13" s="1" t="n"/>
-      <c r="I13" s="1" t="n"/>
-      <c r="J13" s="1" t="n"/>
-      <c r="K13" s="1" t="n"/>
-      <c r="L13" s="1" t="n"/>
-      <c r="M13" s="1" t="n"/>
-      <c r="N13" s="1" t="n"/>
-      <c r="O13" s="1" t="n"/>
-      <c r="P13" s="1" t="n"/>
-      <c r="Q13" s="1" t="n"/>
-      <c r="R13" s="1" t="n"/>
-      <c r="S13" s="1" t="n"/>
-      <c r="T13" s="1" t="n"/>
-      <c r="U13" s="1" t="n"/>
-      <c r="V13" s="1" t="n"/>
-      <c r="W13" s="1" t="n"/>
-      <c r="X13" s="1" t="n"/>
-      <c r="Y13" s="1" t="n"/>
-      <c r="Z13" s="1" t="n"/>
+      <c r="E13" s="102" t="n"/>
+      <c r="F13" s="111" t="n"/>
+      <c r="G13" s="94" t="n"/>
+      <c r="H13" s="94" t="n"/>
+      <c r="I13" s="94" t="n"/>
+      <c r="J13" s="94" t="n"/>
+      <c r="K13" s="94" t="n"/>
+      <c r="L13" s="94" t="n"/>
+      <c r="M13" s="94" t="n"/>
+      <c r="N13" s="94" t="n"/>
+      <c r="O13" s="94" t="n"/>
+      <c r="P13" s="94" t="n"/>
+      <c r="Q13" s="94" t="n"/>
+      <c r="R13" s="94" t="n"/>
+      <c r="S13" s="94" t="n"/>
+      <c r="T13" s="94" t="n"/>
+      <c r="U13" s="94" t="n"/>
+      <c r="V13" s="94" t="n"/>
+      <c r="W13" s="94" t="n"/>
+      <c r="X13" s="94" t="n"/>
+      <c r="Y13" s="94" t="n"/>
+      <c r="Z13" s="94" t="n"/>
       <c r="AA13" s="1" t="n"/>
       <c r="AB13" s="1" t="n"/>
       <c r="AC13" s="1" t="n"/>
@@ -2816,40 +3374,40 @@
       <c r="BG13" s="1" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="A14" s="94" t="n"/>
+      <c r="B14" s="110" t="inlineStr">
         <is>
           <t>Starting Balance</t>
         </is>
       </c>
-      <c r="C14" s="21" t="n"/>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="C14" s="110" t="n"/>
+      <c r="D14" s="102" t="inlineStr">
         <is>
           <t>$0.00</t>
         </is>
       </c>
-      <c r="E14" s="23" t="n"/>
-      <c r="F14" s="21" t="n"/>
-      <c r="G14" s="1" t="n"/>
-      <c r="H14" s="1" t="n"/>
-      <c r="I14" s="1" t="n"/>
-      <c r="J14" s="1" t="n"/>
-      <c r="K14" s="1" t="n"/>
-      <c r="L14" s="1" t="n"/>
-      <c r="M14" s="1" t="n"/>
-      <c r="N14" s="1" t="n"/>
-      <c r="O14" s="1" t="n"/>
-      <c r="P14" s="1" t="n"/>
-      <c r="Q14" s="1" t="n"/>
-      <c r="R14" s="1" t="n"/>
-      <c r="S14" s="1" t="n"/>
-      <c r="T14" s="1" t="n"/>
-      <c r="U14" s="1" t="n"/>
-      <c r="V14" s="1" t="n"/>
-      <c r="W14" s="1" t="n"/>
-      <c r="X14" s="1" t="n"/>
-      <c r="Y14" s="1" t="n"/>
-      <c r="Z14" s="1" t="n"/>
+      <c r="E14" s="102" t="n"/>
+      <c r="F14" s="111" t="n"/>
+      <c r="G14" s="94" t="n"/>
+      <c r="H14" s="94" t="n"/>
+      <c r="I14" s="94" t="n"/>
+      <c r="J14" s="94" t="n"/>
+      <c r="K14" s="94" t="n"/>
+      <c r="L14" s="94" t="n"/>
+      <c r="M14" s="94" t="n"/>
+      <c r="N14" s="94" t="n"/>
+      <c r="O14" s="94" t="n"/>
+      <c r="P14" s="94" t="n"/>
+      <c r="Q14" s="94" t="n"/>
+      <c r="R14" s="94" t="n"/>
+      <c r="S14" s="94" t="n"/>
+      <c r="T14" s="94" t="n"/>
+      <c r="U14" s="94" t="n"/>
+      <c r="V14" s="94" t="n"/>
+      <c r="W14" s="94" t="n"/>
+      <c r="X14" s="94" t="n"/>
+      <c r="Y14" s="94" t="n"/>
+      <c r="Z14" s="94" t="n"/>
       <c r="AA14" s="1" t="n"/>
       <c r="AB14" s="1" t="n"/>
       <c r="AC14" s="1" t="n"/>
@@ -2885,32 +3443,32 @@
       <c r="BG14" s="1" t="n"/>
     </row>
     <row r="15" ht="8" customHeight="1">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="1" t="n"/>
-      <c r="C15" s="1" t="n"/>
-      <c r="D15" s="1" t="n"/>
-      <c r="E15" s="1" t="n"/>
-      <c r="F15" s="1" t="n"/>
-      <c r="G15" s="1" t="n"/>
-      <c r="H15" s="1" t="n"/>
-      <c r="I15" s="1" t="n"/>
-      <c r="J15" s="1" t="n"/>
-      <c r="K15" s="1" t="n"/>
-      <c r="L15" s="1" t="n"/>
-      <c r="M15" s="1" t="n"/>
-      <c r="N15" s="1" t="n"/>
-      <c r="O15" s="1" t="n"/>
-      <c r="P15" s="1" t="n"/>
-      <c r="Q15" s="1" t="n"/>
-      <c r="R15" s="1" t="n"/>
-      <c r="S15" s="1" t="n"/>
-      <c r="T15" s="1" t="n"/>
-      <c r="U15" s="1" t="n"/>
-      <c r="V15" s="1" t="n"/>
-      <c r="W15" s="1" t="n"/>
-      <c r="X15" s="1" t="n"/>
-      <c r="Y15" s="1" t="n"/>
-      <c r="Z15" s="1" t="n"/>
+      <c r="A15" s="94" t="n"/>
+      <c r="B15" s="111" t="n"/>
+      <c r="C15" s="111" t="n"/>
+      <c r="D15" s="111" t="n"/>
+      <c r="E15" s="111" t="n"/>
+      <c r="F15" s="111" t="n"/>
+      <c r="G15" s="94" t="n"/>
+      <c r="H15" s="94" t="n"/>
+      <c r="I15" s="94" t="n"/>
+      <c r="J15" s="94" t="n"/>
+      <c r="K15" s="94" t="n"/>
+      <c r="L15" s="94" t="n"/>
+      <c r="M15" s="94" t="n"/>
+      <c r="N15" s="94" t="n"/>
+      <c r="O15" s="94" t="n"/>
+      <c r="P15" s="94" t="n"/>
+      <c r="Q15" s="94" t="n"/>
+      <c r="R15" s="94" t="n"/>
+      <c r="S15" s="94" t="n"/>
+      <c r="T15" s="94" t="n"/>
+      <c r="U15" s="94" t="n"/>
+      <c r="V15" s="94" t="n"/>
+      <c r="W15" s="94" t="n"/>
+      <c r="X15" s="94" t="n"/>
+      <c r="Y15" s="94" t="n"/>
+      <c r="Z15" s="94" t="n"/>
       <c r="AA15" s="1" t="n"/>
       <c r="AB15" s="1" t="n"/>
       <c r="AC15" s="1" t="n"/>
@@ -2946,32 +3504,36 @@
       <c r="BG15" s="1" t="n"/>
     </row>
     <row r="16" ht="14" customHeight="1">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="A16" s="94" t="n"/>
+      <c r="B16" s="112" t="inlineStr">
         <is>
           <t>Set your starting balance to 0 if you want to budget solely on income.</t>
         </is>
       </c>
-      <c r="G16" s="1" t="n"/>
-      <c r="H16" s="1" t="n"/>
-      <c r="I16" s="1" t="n"/>
-      <c r="J16" s="1" t="n"/>
-      <c r="K16" s="1" t="n"/>
-      <c r="L16" s="1" t="n"/>
-      <c r="M16" s="1" t="n"/>
-      <c r="N16" s="1" t="n"/>
-      <c r="O16" s="1" t="n"/>
-      <c r="P16" s="1" t="n"/>
-      <c r="Q16" s="1" t="n"/>
-      <c r="R16" s="1" t="n"/>
-      <c r="S16" s="1" t="n"/>
-      <c r="T16" s="1" t="n"/>
-      <c r="U16" s="1" t="n"/>
-      <c r="V16" s="1" t="n"/>
-      <c r="W16" s="1" t="n"/>
-      <c r="X16" s="1" t="n"/>
-      <c r="Y16" s="1" t="n"/>
-      <c r="Z16" s="1" t="n"/>
+      <c r="C16" s="112" t="n"/>
+      <c r="D16" s="112" t="n"/>
+      <c r="E16" s="112" t="n"/>
+      <c r="F16" s="112" t="n"/>
+      <c r="G16" s="94" t="n"/>
+      <c r="H16" s="94" t="n"/>
+      <c r="I16" s="94" t="n"/>
+      <c r="J16" s="94" t="n"/>
+      <c r="K16" s="94" t="n"/>
+      <c r="L16" s="94" t="n"/>
+      <c r="M16" s="94" t="n"/>
+      <c r="N16" s="94" t="n"/>
+      <c r="O16" s="94" t="n"/>
+      <c r="P16" s="94" t="n"/>
+      <c r="Q16" s="94" t="n"/>
+      <c r="R16" s="94" t="n"/>
+      <c r="S16" s="94" t="n"/>
+      <c r="T16" s="94" t="n"/>
+      <c r="U16" s="94" t="n"/>
+      <c r="V16" s="94" t="n"/>
+      <c r="W16" s="94" t="n"/>
+      <c r="X16" s="94" t="n"/>
+      <c r="Y16" s="94" t="n"/>
+      <c r="Z16" s="94" t="n"/>
       <c r="AA16" s="1" t="n"/>
       <c r="AB16" s="1" t="n"/>
       <c r="AC16" s="1" t="n"/>
@@ -3007,32 +3569,32 @@
       <c r="BG16" s="1" t="n"/>
     </row>
     <row r="17" ht="8" customHeight="1">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="1" t="n"/>
-      <c r="C17" s="1" t="n"/>
-      <c r="D17" s="1" t="n"/>
-      <c r="E17" s="1" t="n"/>
-      <c r="F17" s="1" t="n"/>
-      <c r="G17" s="1" t="n"/>
-      <c r="H17" s="1" t="n"/>
-      <c r="I17" s="1" t="n"/>
-      <c r="J17" s="1" t="n"/>
-      <c r="K17" s="1" t="n"/>
-      <c r="L17" s="1" t="n"/>
-      <c r="M17" s="1" t="n"/>
-      <c r="N17" s="1" t="n"/>
-      <c r="O17" s="1" t="n"/>
-      <c r="P17" s="1" t="n"/>
-      <c r="Q17" s="1" t="n"/>
-      <c r="R17" s="1" t="n"/>
-      <c r="S17" s="1" t="n"/>
-      <c r="T17" s="1" t="n"/>
-      <c r="U17" s="1" t="n"/>
-      <c r="V17" s="1" t="n"/>
-      <c r="W17" s="1" t="n"/>
-      <c r="X17" s="1" t="n"/>
-      <c r="Y17" s="1" t="n"/>
-      <c r="Z17" s="1" t="n"/>
+      <c r="A17" s="94" t="n"/>
+      <c r="B17" s="94" t="n"/>
+      <c r="C17" s="94" t="n"/>
+      <c r="D17" s="94" t="n"/>
+      <c r="E17" s="94" t="n"/>
+      <c r="F17" s="94" t="n"/>
+      <c r="G17" s="94" t="n"/>
+      <c r="H17" s="94" t="n"/>
+      <c r="I17" s="94" t="n"/>
+      <c r="J17" s="94" t="n"/>
+      <c r="K17" s="94" t="n"/>
+      <c r="L17" s="94" t="n"/>
+      <c r="M17" s="94" t="n"/>
+      <c r="N17" s="94" t="n"/>
+      <c r="O17" s="94" t="n"/>
+      <c r="P17" s="94" t="n"/>
+      <c r="Q17" s="94" t="n"/>
+      <c r="R17" s="94" t="n"/>
+      <c r="S17" s="94" t="n"/>
+      <c r="T17" s="94" t="n"/>
+      <c r="U17" s="94" t="n"/>
+      <c r="V17" s="94" t="n"/>
+      <c r="W17" s="94" t="n"/>
+      <c r="X17" s="94" t="n"/>
+      <c r="Y17" s="94" t="n"/>
+      <c r="Z17" s="94" t="n"/>
       <c r="AA17" s="1" t="n"/>
       <c r="AB17" s="1" t="n"/>
       <c r="AC17" s="1" t="n"/>
@@ -3067,33 +3629,37 @@
       <c r="BF17" s="1" t="n"/>
       <c r="BG17" s="1" t="n"/>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="25" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="94" t="n"/>
+      <c r="B18" s="113" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="G18" s="1" t="n"/>
-      <c r="H18" s="1" t="n"/>
-      <c r="I18" s="1" t="n"/>
-      <c r="J18" s="1" t="n"/>
-      <c r="K18" s="1" t="n"/>
-      <c r="L18" s="1" t="n"/>
-      <c r="M18" s="1" t="n"/>
-      <c r="N18" s="1" t="n"/>
-      <c r="O18" s="1" t="n"/>
-      <c r="P18" s="1" t="n"/>
-      <c r="Q18" s="1" t="n"/>
-      <c r="R18" s="1" t="n"/>
-      <c r="S18" s="1" t="n"/>
-      <c r="T18" s="1" t="n"/>
-      <c r="U18" s="1" t="n"/>
-      <c r="V18" s="1" t="n"/>
-      <c r="W18" s="1" t="n"/>
-      <c r="X18" s="1" t="n"/>
-      <c r="Y18" s="1" t="n"/>
-      <c r="Z18" s="1" t="n"/>
+      <c r="C18" s="113" t="n"/>
+      <c r="D18" s="113" t="n"/>
+      <c r="E18" s="113" t="n"/>
+      <c r="F18" s="105" t="n"/>
+      <c r="G18" s="94" t="n"/>
+      <c r="H18" s="94" t="n"/>
+      <c r="I18" s="94" t="n"/>
+      <c r="J18" s="94" t="n"/>
+      <c r="K18" s="94" t="n"/>
+      <c r="L18" s="94" t="n"/>
+      <c r="M18" s="94" t="n"/>
+      <c r="N18" s="94" t="n"/>
+      <c r="O18" s="94" t="n"/>
+      <c r="P18" s="94" t="n"/>
+      <c r="Q18" s="94" t="n"/>
+      <c r="R18" s="94" t="n"/>
+      <c r="S18" s="94" t="n"/>
+      <c r="T18" s="94" t="n"/>
+      <c r="U18" s="94" t="n"/>
+      <c r="V18" s="94" t="n"/>
+      <c r="W18" s="94" t="n"/>
+      <c r="X18" s="94" t="n"/>
+      <c r="Y18" s="94" t="n"/>
+      <c r="Z18" s="94" t="n"/>
       <c r="AA18" s="1" t="n"/>
       <c r="AB18" s="1" t="n"/>
       <c r="AC18" s="1" t="n"/>
@@ -3129,40 +3695,40 @@
       <c r="BG18" s="1" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="10" t="inlineStr"/>
-      <c r="C19" s="10" t="inlineStr"/>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="A19" s="94" t="n"/>
+      <c r="B19" s="114" t="inlineStr"/>
+      <c r="C19" s="114" t="inlineStr"/>
+      <c r="D19" s="115" t="inlineStr">
         <is>
           <t>BUDGET</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="115" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr"/>
-      <c r="G19" s="1" t="n"/>
-      <c r="H19" s="1" t="n"/>
-      <c r="I19" s="1" t="n"/>
-      <c r="J19" s="1" t="n"/>
-      <c r="K19" s="1" t="n"/>
-      <c r="L19" s="1" t="n"/>
-      <c r="M19" s="1" t="n"/>
-      <c r="N19" s="1" t="n"/>
-      <c r="O19" s="1" t="n"/>
-      <c r="P19" s="1" t="n"/>
-      <c r="Q19" s="1" t="n"/>
-      <c r="R19" s="1" t="n"/>
-      <c r="S19" s="1" t="n"/>
-      <c r="T19" s="1" t="n"/>
-      <c r="U19" s="1" t="n"/>
-      <c r="V19" s="1" t="n"/>
-      <c r="W19" s="1" t="n"/>
-      <c r="X19" s="1" t="n"/>
-      <c r="Y19" s="1" t="n"/>
-      <c r="Z19" s="1" t="n"/>
+      <c r="F19" s="116" t="inlineStr"/>
+      <c r="G19" s="94" t="n"/>
+      <c r="H19" s="94" t="n"/>
+      <c r="I19" s="94" t="n"/>
+      <c r="J19" s="94" t="n"/>
+      <c r="K19" s="94" t="n"/>
+      <c r="L19" s="94" t="n"/>
+      <c r="M19" s="94" t="n"/>
+      <c r="N19" s="94" t="n"/>
+      <c r="O19" s="94" t="n"/>
+      <c r="P19" s="94" t="n"/>
+      <c r="Q19" s="94" t="n"/>
+      <c r="R19" s="94" t="n"/>
+      <c r="S19" s="94" t="n"/>
+      <c r="T19" s="94" t="n"/>
+      <c r="U19" s="94" t="n"/>
+      <c r="V19" s="94" t="n"/>
+      <c r="W19" s="94" t="n"/>
+      <c r="X19" s="94" t="n"/>
+      <c r="Y19" s="94" t="n"/>
+      <c r="Z19" s="94" t="n"/>
       <c r="AA19" s="1" t="n"/>
       <c r="AB19" s="1" t="n"/>
       <c r="AC19" s="1" t="n"/>
@@ -3198,40 +3764,40 @@
       <c r="BG19" s="1" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="A20" s="94" t="n"/>
+      <c r="B20" s="110" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="C20" s="21" t="n"/>
-      <c r="D20" s="27" t="n">
+      <c r="C20" s="117" t="n"/>
+      <c r="D20" s="118" t="n">
         <v>1914.8</v>
       </c>
-      <c r="E20" s="28" t="n">
+      <c r="E20" s="118" t="n">
         <v>1850.07</v>
       </c>
-      <c r="F20" s="29" t="n"/>
-      <c r="G20" s="1" t="n"/>
-      <c r="H20" s="1" t="n"/>
-      <c r="I20" s="1" t="n"/>
-      <c r="J20" s="1" t="n"/>
-      <c r="K20" s="1" t="n"/>
-      <c r="L20" s="1" t="n"/>
-      <c r="M20" s="1" t="n"/>
-      <c r="N20" s="1" t="n"/>
-      <c r="O20" s="1" t="n"/>
-      <c r="P20" s="1" t="n"/>
-      <c r="Q20" s="1" t="n"/>
-      <c r="R20" s="1" t="n"/>
-      <c r="S20" s="1" t="n"/>
-      <c r="T20" s="1" t="n"/>
-      <c r="U20" s="1" t="n"/>
-      <c r="V20" s="1" t="n"/>
-      <c r="W20" s="1" t="n"/>
-      <c r="X20" s="1" t="n"/>
-      <c r="Y20" s="1" t="n"/>
-      <c r="Z20" s="1" t="n"/>
+      <c r="F20" s="94" t="n"/>
+      <c r="G20" s="94" t="n"/>
+      <c r="H20" s="94" t="n"/>
+      <c r="I20" s="94" t="n"/>
+      <c r="J20" s="94" t="n"/>
+      <c r="K20" s="94" t="n"/>
+      <c r="L20" s="94" t="n"/>
+      <c r="M20" s="94" t="n"/>
+      <c r="N20" s="94" t="n"/>
+      <c r="O20" s="94" t="n"/>
+      <c r="P20" s="94" t="n"/>
+      <c r="Q20" s="94" t="n"/>
+      <c r="R20" s="94" t="n"/>
+      <c r="S20" s="94" t="n"/>
+      <c r="T20" s="94" t="n"/>
+      <c r="U20" s="94" t="n"/>
+      <c r="V20" s="94" t="n"/>
+      <c r="W20" s="94" t="n"/>
+      <c r="X20" s="94" t="n"/>
+      <c r="Y20" s="94" t="n"/>
+      <c r="Z20" s="94" t="n"/>
       <c r="AA20" s="1" t="n"/>
       <c r="AB20" s="1" t="n"/>
       <c r="AC20" s="1" t="n"/>
@@ -3267,40 +3833,40 @@
       <c r="BG20" s="1" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="30" t="inlineStr">
+      <c r="A21" s="94" t="n"/>
+      <c r="B21" s="110" t="inlineStr">
         <is>
           <t>Bills</t>
         </is>
       </c>
-      <c r="C21" s="21" t="n"/>
-      <c r="D21" s="31" t="n">
+      <c r="C21" s="117" t="n"/>
+      <c r="D21" s="118" t="n">
         <v>766.15</v>
       </c>
-      <c r="E21" s="32" t="n">
+      <c r="E21" s="118" t="n">
         <v>766.15</v>
       </c>
-      <c r="F21" s="33" t="n"/>
-      <c r="G21" s="1" t="n"/>
-      <c r="H21" s="1" t="n"/>
-      <c r="I21" s="1" t="n"/>
-      <c r="J21" s="1" t="n"/>
-      <c r="K21" s="1" t="n"/>
-      <c r="L21" s="1" t="n"/>
-      <c r="M21" s="1" t="n"/>
-      <c r="N21" s="1" t="n"/>
-      <c r="O21" s="1" t="n"/>
-      <c r="P21" s="1" t="n"/>
-      <c r="Q21" s="1" t="n"/>
-      <c r="R21" s="1" t="n"/>
-      <c r="S21" s="1" t="n"/>
-      <c r="T21" s="1" t="n"/>
-      <c r="U21" s="1" t="n"/>
-      <c r="V21" s="1" t="n"/>
-      <c r="W21" s="1" t="n"/>
-      <c r="X21" s="1" t="n"/>
-      <c r="Y21" s="1" t="n"/>
-      <c r="Z21" s="1" t="n"/>
+      <c r="F21" s="94" t="n"/>
+      <c r="G21" s="94" t="n"/>
+      <c r="H21" s="94" t="n"/>
+      <c r="I21" s="94" t="n"/>
+      <c r="J21" s="94" t="n"/>
+      <c r="K21" s="94" t="n"/>
+      <c r="L21" s="94" t="n"/>
+      <c r="M21" s="94" t="n"/>
+      <c r="N21" s="94" t="n"/>
+      <c r="O21" s="94" t="n"/>
+      <c r="P21" s="94" t="n"/>
+      <c r="Q21" s="94" t="n"/>
+      <c r="R21" s="94" t="n"/>
+      <c r="S21" s="94" t="n"/>
+      <c r="T21" s="94" t="n"/>
+      <c r="U21" s="94" t="n"/>
+      <c r="V21" s="94" t="n"/>
+      <c r="W21" s="94" t="n"/>
+      <c r="X21" s="94" t="n"/>
+      <c r="Y21" s="94" t="n"/>
+      <c r="Z21" s="94" t="n"/>
       <c r="AA21" s="1" t="n"/>
       <c r="AB21" s="1" t="n"/>
       <c r="AC21" s="1" t="n"/>
@@ -3336,40 +3902,40 @@
       <c r="BG21" s="1" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="1" t="n"/>
-      <c r="B22" s="34" t="inlineStr">
+      <c r="A22" s="94" t="n"/>
+      <c r="B22" s="110" t="inlineStr">
         <is>
           <t>Debt</t>
         </is>
       </c>
-      <c r="C22" s="21" t="n"/>
-      <c r="D22" s="27" t="n">
+      <c r="C22" s="117" t="n"/>
+      <c r="D22" s="118" t="n">
         <v>8175</v>
       </c>
-      <c r="E22" s="28" t="n">
+      <c r="E22" s="118" t="n">
         <v>8175</v>
       </c>
-      <c r="F22" s="29" t="n"/>
-      <c r="G22" s="1" t="n"/>
-      <c r="H22" s="1" t="n"/>
-      <c r="I22" s="1" t="n"/>
-      <c r="J22" s="1" t="n"/>
-      <c r="K22" s="1" t="n"/>
-      <c r="L22" s="1" t="n"/>
-      <c r="M22" s="1" t="n"/>
-      <c r="N22" s="1" t="n"/>
-      <c r="O22" s="1" t="n"/>
-      <c r="P22" s="1" t="n"/>
-      <c r="Q22" s="1" t="n"/>
-      <c r="R22" s="1" t="n"/>
-      <c r="S22" s="1" t="n"/>
-      <c r="T22" s="1" t="n"/>
-      <c r="U22" s="1" t="n"/>
-      <c r="V22" s="1" t="n"/>
-      <c r="W22" s="1" t="n"/>
-      <c r="X22" s="1" t="n"/>
-      <c r="Y22" s="1" t="n"/>
-      <c r="Z22" s="1" t="n"/>
+      <c r="F22" s="94" t="n"/>
+      <c r="G22" s="94" t="n"/>
+      <c r="H22" s="94" t="n"/>
+      <c r="I22" s="94" t="n"/>
+      <c r="J22" s="94" t="n"/>
+      <c r="K22" s="94" t="n"/>
+      <c r="L22" s="94" t="n"/>
+      <c r="M22" s="94" t="n"/>
+      <c r="N22" s="94" t="n"/>
+      <c r="O22" s="94" t="n"/>
+      <c r="P22" s="94" t="n"/>
+      <c r="Q22" s="94" t="n"/>
+      <c r="R22" s="94" t="n"/>
+      <c r="S22" s="94" t="n"/>
+      <c r="T22" s="94" t="n"/>
+      <c r="U22" s="94" t="n"/>
+      <c r="V22" s="94" t="n"/>
+      <c r="W22" s="94" t="n"/>
+      <c r="X22" s="94" t="n"/>
+      <c r="Y22" s="94" t="n"/>
+      <c r="Z22" s="94" t="n"/>
       <c r="AA22" s="1" t="n"/>
       <c r="AB22" s="1" t="n"/>
       <c r="AC22" s="1" t="n"/>
@@ -3405,40 +3971,40 @@
       <c r="BG22" s="1" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="35" t="inlineStr">
+      <c r="A23" s="94" t="n"/>
+      <c r="B23" s="110" t="inlineStr">
         <is>
           <t>Savings</t>
         </is>
       </c>
-      <c r="C23" s="21" t="n"/>
-      <c r="D23" s="31" t="n">
+      <c r="C23" s="117" t="n"/>
+      <c r="D23" s="118" t="n">
         <v>5668</v>
       </c>
-      <c r="E23" s="32" t="n">
+      <c r="E23" s="118" t="n">
         <v>982</v>
       </c>
-      <c r="F23" s="33" t="n"/>
-      <c r="G23" s="1" t="n"/>
-      <c r="H23" s="1" t="n"/>
-      <c r="I23" s="1" t="n"/>
-      <c r="J23" s="1" t="n"/>
-      <c r="K23" s="1" t="n"/>
-      <c r="L23" s="1" t="n"/>
-      <c r="M23" s="1" t="n"/>
-      <c r="N23" s="1" t="n"/>
-      <c r="O23" s="1" t="n"/>
-      <c r="P23" s="1" t="n"/>
-      <c r="Q23" s="1" t="n"/>
-      <c r="R23" s="1" t="n"/>
-      <c r="S23" s="1" t="n"/>
-      <c r="T23" s="1" t="n"/>
-      <c r="U23" s="1" t="n"/>
-      <c r="V23" s="1" t="n"/>
-      <c r="W23" s="1" t="n"/>
-      <c r="X23" s="1" t="n"/>
-      <c r="Y23" s="1" t="n"/>
-      <c r="Z23" s="1" t="n"/>
+      <c r="F23" s="94" t="n"/>
+      <c r="G23" s="94" t="n"/>
+      <c r="H23" s="94" t="n"/>
+      <c r="I23" s="94" t="n"/>
+      <c r="J23" s="94" t="n"/>
+      <c r="K23" s="94" t="n"/>
+      <c r="L23" s="94" t="n"/>
+      <c r="M23" s="94" t="n"/>
+      <c r="N23" s="94" t="n"/>
+      <c r="O23" s="94" t="n"/>
+      <c r="P23" s="94" t="n"/>
+      <c r="Q23" s="94" t="n"/>
+      <c r="R23" s="94" t="n"/>
+      <c r="S23" s="94" t="n"/>
+      <c r="T23" s="94" t="n"/>
+      <c r="U23" s="94" t="n"/>
+      <c r="V23" s="94" t="n"/>
+      <c r="W23" s="94" t="n"/>
+      <c r="X23" s="94" t="n"/>
+      <c r="Y23" s="94" t="n"/>
+      <c r="Z23" s="94" t="n"/>
       <c r="AA23" s="1" t="n"/>
       <c r="AB23" s="1" t="n"/>
       <c r="AC23" s="1" t="n"/>
@@ -3474,40 +4040,40 @@
       <c r="BG23" s="1" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="36" t="inlineStr">
+      <c r="A24" s="94" t="n"/>
+      <c r="B24" s="110" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="27" t="n">
+      <c r="C24" s="117" t="n"/>
+      <c r="D24" s="118" t="n">
         <v>3161</v>
       </c>
-      <c r="E24" s="28" t="n">
+      <c r="E24" s="118" t="n">
         <v>3161</v>
       </c>
-      <c r="F24" s="29" t="n"/>
-      <c r="G24" s="1" t="n"/>
-      <c r="H24" s="1" t="n"/>
-      <c r="I24" s="1" t="n"/>
-      <c r="J24" s="1" t="n"/>
-      <c r="K24" s="1" t="n"/>
-      <c r="L24" s="1" t="n"/>
-      <c r="M24" s="1" t="n"/>
-      <c r="N24" s="1" t="n"/>
-      <c r="O24" s="1" t="n"/>
-      <c r="P24" s="1" t="n"/>
-      <c r="Q24" s="1" t="n"/>
-      <c r="R24" s="1" t="n"/>
-      <c r="S24" s="1" t="n"/>
-      <c r="T24" s="1" t="n"/>
-      <c r="U24" s="1" t="n"/>
-      <c r="V24" s="1" t="n"/>
-      <c r="W24" s="1" t="n"/>
-      <c r="X24" s="1" t="n"/>
-      <c r="Y24" s="1" t="n"/>
-      <c r="Z24" s="1" t="n"/>
+      <c r="F24" s="94" t="n"/>
+      <c r="G24" s="94" t="n"/>
+      <c r="H24" s="94" t="n"/>
+      <c r="I24" s="94" t="n"/>
+      <c r="J24" s="94" t="n"/>
+      <c r="K24" s="94" t="n"/>
+      <c r="L24" s="94" t="n"/>
+      <c r="M24" s="94" t="n"/>
+      <c r="N24" s="94" t="n"/>
+      <c r="O24" s="94" t="n"/>
+      <c r="P24" s="94" t="n"/>
+      <c r="Q24" s="94" t="n"/>
+      <c r="R24" s="94" t="n"/>
+      <c r="S24" s="94" t="n"/>
+      <c r="T24" s="94" t="n"/>
+      <c r="U24" s="94" t="n"/>
+      <c r="V24" s="94" t="n"/>
+      <c r="W24" s="94" t="n"/>
+      <c r="X24" s="94" t="n"/>
+      <c r="Y24" s="94" t="n"/>
+      <c r="Z24" s="94" t="n"/>
       <c r="AA24" s="1" t="n"/>
       <c r="AB24" s="1" t="n"/>
       <c r="AC24" s="1" t="n"/>
@@ -3543,40 +4109,40 @@
       <c r="BG24" s="1" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="1" t="n"/>
-      <c r="B25" s="37" t="inlineStr">
+      <c r="A25" s="94" t="n"/>
+      <c r="B25" s="119" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C25" s="38" t="n"/>
-      <c r="D25" s="39" t="n">
+      <c r="C25" s="119" t="n"/>
+      <c r="D25" s="120" t="n">
         <v>19685.95</v>
       </c>
-      <c r="E25" s="40" t="n">
+      <c r="E25" s="120" t="n">
         <v>14974.22</v>
       </c>
-      <c r="F25" s="41" t="n"/>
-      <c r="G25" s="1" t="n"/>
-      <c r="H25" s="1" t="n"/>
-      <c r="I25" s="1" t="n"/>
-      <c r="J25" s="1" t="n"/>
-      <c r="K25" s="1" t="n"/>
-      <c r="L25" s="1" t="n"/>
-      <c r="M25" s="1" t="n"/>
-      <c r="N25" s="1" t="n"/>
-      <c r="O25" s="1" t="n"/>
-      <c r="P25" s="1" t="n"/>
-      <c r="Q25" s="1" t="n"/>
-      <c r="R25" s="1" t="n"/>
-      <c r="S25" s="1" t="n"/>
-      <c r="T25" s="1" t="n"/>
-      <c r="U25" s="1" t="n"/>
-      <c r="V25" s="1" t="n"/>
-      <c r="W25" s="1" t="n"/>
-      <c r="X25" s="1" t="n"/>
-      <c r="Y25" s="1" t="n"/>
-      <c r="Z25" s="1" t="n"/>
+      <c r="F25" s="94" t="n"/>
+      <c r="G25" s="94" t="n"/>
+      <c r="H25" s="94" t="n"/>
+      <c r="I25" s="94" t="n"/>
+      <c r="J25" s="94" t="n"/>
+      <c r="K25" s="94" t="n"/>
+      <c r="L25" s="94" t="n"/>
+      <c r="M25" s="94" t="n"/>
+      <c r="N25" s="94" t="n"/>
+      <c r="O25" s="94" t="n"/>
+      <c r="P25" s="94" t="n"/>
+      <c r="Q25" s="94" t="n"/>
+      <c r="R25" s="94" t="n"/>
+      <c r="S25" s="94" t="n"/>
+      <c r="T25" s="94" t="n"/>
+      <c r="U25" s="94" t="n"/>
+      <c r="V25" s="94" t="n"/>
+      <c r="W25" s="94" t="n"/>
+      <c r="X25" s="94" t="n"/>
+      <c r="Y25" s="94" t="n"/>
+      <c r="Z25" s="94" t="n"/>
       <c r="AA25" s="1" t="n"/>
       <c r="AB25" s="1" t="n"/>
       <c r="AC25" s="1" t="n"/>
@@ -3612,32 +4178,32 @@
       <c r="BG25" s="1" t="n"/>
     </row>
     <row r="26" ht="8" customHeight="1">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="1" t="n"/>
-      <c r="C26" s="1" t="n"/>
-      <c r="D26" s="1" t="n"/>
-      <c r="E26" s="1" t="n"/>
-      <c r="F26" s="1" t="n"/>
-      <c r="G26" s="1" t="n"/>
-      <c r="H26" s="1" t="n"/>
-      <c r="I26" s="1" t="n"/>
-      <c r="J26" s="1" t="n"/>
-      <c r="K26" s="1" t="n"/>
-      <c r="L26" s="1" t="n"/>
-      <c r="M26" s="1" t="n"/>
-      <c r="N26" s="1" t="n"/>
-      <c r="O26" s="1" t="n"/>
-      <c r="P26" s="1" t="n"/>
-      <c r="Q26" s="1" t="n"/>
-      <c r="R26" s="1" t="n"/>
-      <c r="S26" s="1" t="n"/>
-      <c r="T26" s="1" t="n"/>
-      <c r="U26" s="1" t="n"/>
-      <c r="V26" s="1" t="n"/>
-      <c r="W26" s="1" t="n"/>
-      <c r="X26" s="1" t="n"/>
-      <c r="Y26" s="1" t="n"/>
-      <c r="Z26" s="1" t="n"/>
+      <c r="A26" s="94" t="n"/>
+      <c r="B26" s="94" t="n"/>
+      <c r="C26" s="94" t="n"/>
+      <c r="D26" s="94" t="n"/>
+      <c r="E26" s="94" t="n"/>
+      <c r="F26" s="94" t="n"/>
+      <c r="G26" s="94" t="n"/>
+      <c r="H26" s="94" t="n"/>
+      <c r="I26" s="94" t="n"/>
+      <c r="J26" s="94" t="n"/>
+      <c r="K26" s="94" t="n"/>
+      <c r="L26" s="94" t="n"/>
+      <c r="M26" s="94" t="n"/>
+      <c r="N26" s="94" t="n"/>
+      <c r="O26" s="94" t="n"/>
+      <c r="P26" s="94" t="n"/>
+      <c r="Q26" s="94" t="n"/>
+      <c r="R26" s="94" t="n"/>
+      <c r="S26" s="94" t="n"/>
+      <c r="T26" s="94" t="n"/>
+      <c r="U26" s="94" t="n"/>
+      <c r="V26" s="94" t="n"/>
+      <c r="W26" s="94" t="n"/>
+      <c r="X26" s="94" t="n"/>
+      <c r="Y26" s="94" t="n"/>
+      <c r="Z26" s="94" t="n"/>
       <c r="AA26" s="1" t="n"/>
       <c r="AB26" s="1" t="n"/>
       <c r="AC26" s="1" t="n"/>
@@ -3673,32 +4239,36 @@
       <c r="BG26" s="1" t="n"/>
     </row>
     <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="A27" s="94" t="n"/>
+      <c r="B27" s="121" t="inlineStr">
         <is>
           <t>Add/edit subcategories in the 3 tables below</t>
         </is>
       </c>
-      <c r="G27" s="1" t="n"/>
-      <c r="H27" s="1" t="n"/>
-      <c r="I27" s="1" t="n"/>
-      <c r="J27" s="1" t="n"/>
-      <c r="K27" s="1" t="n"/>
-      <c r="L27" s="1" t="n"/>
-      <c r="M27" s="1" t="n"/>
-      <c r="N27" s="1" t="n"/>
-      <c r="O27" s="1" t="n"/>
-      <c r="P27" s="1" t="n"/>
-      <c r="Q27" s="1" t="n"/>
-      <c r="R27" s="1" t="n"/>
-      <c r="S27" s="1" t="n"/>
-      <c r="T27" s="1" t="n"/>
-      <c r="U27" s="1" t="n"/>
-      <c r="V27" s="1" t="n"/>
-      <c r="W27" s="1" t="n"/>
-      <c r="X27" s="1" t="n"/>
-      <c r="Y27" s="1" t="n"/>
-      <c r="Z27" s="1" t="n"/>
+      <c r="C27" s="121" t="n"/>
+      <c r="D27" s="121" t="n"/>
+      <c r="E27" s="121" t="n"/>
+      <c r="F27" s="121" t="n"/>
+      <c r="G27" s="121" t="n"/>
+      <c r="H27" s="121" t="n"/>
+      <c r="I27" s="121" t="n"/>
+      <c r="J27" s="121" t="n"/>
+      <c r="K27" s="121" t="n"/>
+      <c r="L27" s="121" t="n"/>
+      <c r="M27" s="121" t="n"/>
+      <c r="N27" s="121" t="n"/>
+      <c r="O27" s="121" t="n"/>
+      <c r="P27" s="121" t="n"/>
+      <c r="Q27" s="121" t="n"/>
+      <c r="R27" s="121" t="n"/>
+      <c r="S27" s="121" t="n"/>
+      <c r="T27" s="121" t="n"/>
+      <c r="U27" s="121" t="n"/>
+      <c r="V27" s="121" t="n"/>
+      <c r="W27" s="121" t="n"/>
+      <c r="X27" s="121" t="n"/>
+      <c r="Y27" s="121" t="n"/>
+      <c r="Z27" s="94" t="n"/>
       <c r="AA27" s="1" t="n"/>
       <c r="AB27" s="1" t="n"/>
       <c r="AC27" s="1" t="n"/>
@@ -3734,32 +4304,32 @@
       <c r="BG27" s="1" t="n"/>
     </row>
     <row r="28" ht="8" customHeight="1">
-      <c r="A28" s="1" t="n"/>
-      <c r="B28" s="1" t="n"/>
-      <c r="C28" s="1" t="n"/>
-      <c r="D28" s="1" t="n"/>
-      <c r="E28" s="1" t="n"/>
-      <c r="F28" s="1" t="n"/>
-      <c r="G28" s="1" t="n"/>
-      <c r="H28" s="1" t="n"/>
-      <c r="I28" s="1" t="n"/>
-      <c r="J28" s="1" t="n"/>
-      <c r="K28" s="1" t="n"/>
-      <c r="L28" s="1" t="n"/>
-      <c r="M28" s="1" t="n"/>
-      <c r="N28" s="1" t="n"/>
-      <c r="O28" s="1" t="n"/>
-      <c r="P28" s="1" t="n"/>
-      <c r="Q28" s="1" t="n"/>
-      <c r="R28" s="1" t="n"/>
-      <c r="S28" s="1" t="n"/>
-      <c r="T28" s="1" t="n"/>
-      <c r="U28" s="1" t="n"/>
-      <c r="V28" s="1" t="n"/>
-      <c r="W28" s="1" t="n"/>
-      <c r="X28" s="1" t="n"/>
-      <c r="Y28" s="1" t="n"/>
-      <c r="Z28" s="1" t="n"/>
+      <c r="A28" s="94" t="n"/>
+      <c r="B28" s="94" t="n"/>
+      <c r="C28" s="94" t="n"/>
+      <c r="D28" s="94" t="n"/>
+      <c r="E28" s="94" t="n"/>
+      <c r="F28" s="94" t="n"/>
+      <c r="G28" s="94" t="n"/>
+      <c r="H28" s="94" t="n"/>
+      <c r="I28" s="94" t="n"/>
+      <c r="J28" s="94" t="n"/>
+      <c r="K28" s="94" t="n"/>
+      <c r="L28" s="94" t="n"/>
+      <c r="M28" s="94" t="n"/>
+      <c r="N28" s="94" t="n"/>
+      <c r="O28" s="94" t="n"/>
+      <c r="P28" s="94" t="n"/>
+      <c r="Q28" s="94" t="n"/>
+      <c r="R28" s="94" t="n"/>
+      <c r="S28" s="94" t="n"/>
+      <c r="T28" s="94" t="n"/>
+      <c r="U28" s="94" t="n"/>
+      <c r="V28" s="94" t="n"/>
+      <c r="W28" s="94" t="n"/>
+      <c r="X28" s="94" t="n"/>
+      <c r="Y28" s="94" t="n"/>
+      <c r="Z28" s="94" t="n"/>
       <c r="AA28" s="1" t="n"/>
       <c r="AB28" s="1" t="n"/>
       <c r="AC28" s="1" t="n"/>
@@ -3794,32 +4364,49 @@
       <c r="BF28" s="1" t="n"/>
       <c r="BG28" s="1" t="n"/>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="42" t="inlineStr">
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="94" t="n"/>
+      <c r="B29" s="122" t="inlineStr">
         <is>
           <t>INCOME</t>
         </is>
       </c>
-      <c r="G29" s="1" t="n"/>
-      <c r="H29" s="43" t="inlineStr">
+      <c r="C29" s="122" t="n"/>
+      <c r="D29" s="122" t="n"/>
+      <c r="E29" s="122" t="n"/>
+      <c r="F29" s="122" t="n"/>
+      <c r="G29" s="122" t="n"/>
+      <c r="H29" s="122" t="inlineStr">
         <is>
           <t>EXPENSES</t>
         </is>
       </c>
-      <c r="N29" s="1" t="n"/>
-      <c r="O29" s="44" t="inlineStr">
+      <c r="I29" s="122" t="n"/>
+      <c r="J29" s="122" t="n"/>
+      <c r="K29" s="122" t="n"/>
+      <c r="L29" s="122" t="n"/>
+      <c r="M29" s="122" t="n"/>
+      <c r="N29" s="122" t="n"/>
+      <c r="O29" s="122" t="inlineStr">
         <is>
           <t>BILLS</t>
         </is>
       </c>
-      <c r="U29" s="1" t="n"/>
-      <c r="V29" s="45" t="inlineStr">
+      <c r="P29" s="122" t="n"/>
+      <c r="Q29" s="122" t="n"/>
+      <c r="R29" s="122" t="n"/>
+      <c r="S29" s="122" t="n"/>
+      <c r="T29" s="122" t="n"/>
+      <c r="U29" s="122" t="n"/>
+      <c r="V29" s="122" t="inlineStr">
         <is>
           <t>DEBTS</t>
         </is>
       </c>
-      <c r="Z29" s="1" t="n"/>
+      <c r="W29" s="122" t="n"/>
+      <c r="X29" s="122" t="n"/>
+      <c r="Y29" s="122" t="n"/>
+      <c r="Z29" s="94" t="n"/>
       <c r="AA29" s="1" t="n"/>
       <c r="AB29" s="1" t="n"/>
       <c r="AC29" s="1" t="n"/>
@@ -3854,93 +4441,93 @@
       <c r="BF29" s="1" t="n"/>
       <c r="BG29" s="1" t="n"/>
     </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="46" t="inlineStr">
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="94" t="n"/>
+      <c r="B30" s="123" t="inlineStr">
         <is>
           <t>SOURCE/ITEM</t>
         </is>
       </c>
-      <c r="C30" s="47" t="inlineStr"/>
-      <c r="D30" s="47" t="inlineStr">
+      <c r="C30" s="123" t="inlineStr"/>
+      <c r="D30" s="123" t="inlineStr">
         <is>
           <t>EXPECTED</t>
         </is>
       </c>
-      <c r="E30" s="47" t="inlineStr">
+      <c r="E30" s="123" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="F30" s="47" t="inlineStr"/>
-      <c r="G30" s="1" t="n"/>
-      <c r="H30" s="46" t="inlineStr">
+      <c r="F30" s="116" t="inlineStr"/>
+      <c r="G30" s="94" t="n"/>
+      <c r="H30" s="123" t="inlineStr">
         <is>
           <t>CATEGORY</t>
         </is>
       </c>
-      <c r="I30" s="47" t="inlineStr">
+      <c r="I30" s="123" t="inlineStr">
         <is>
           <t>BUDGET</t>
         </is>
       </c>
-      <c r="J30" s="47" t="inlineStr">
+      <c r="J30" s="123" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="K30" s="47" t="inlineStr">
+      <c r="K30" s="123" t="inlineStr">
         <is>
           <t>LEFT TO SPEND</t>
         </is>
       </c>
-      <c r="L30" s="47" t="inlineStr"/>
-      <c r="M30" s="47" t="inlineStr"/>
-      <c r="N30" s="1" t="n"/>
-      <c r="O30" s="46" t="inlineStr">
+      <c r="L30" s="116" t="inlineStr"/>
+      <c r="M30" s="116" t="inlineStr"/>
+      <c r="N30" s="94" t="n"/>
+      <c r="O30" s="123" t="inlineStr">
         <is>
           <t>ACCOUNT</t>
         </is>
       </c>
-      <c r="P30" s="47" t="inlineStr">
+      <c r="P30" s="123" t="inlineStr">
         <is>
           <t>DUE</t>
         </is>
       </c>
-      <c r="Q30" s="47" t="inlineStr">
+      <c r="Q30" s="123" t="inlineStr">
         <is>
           <t>BUDGET</t>
         </is>
       </c>
-      <c r="R30" s="47" t="inlineStr">
+      <c r="R30" s="123" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="S30" s="47" t="inlineStr"/>
-      <c r="T30" s="47" t="inlineStr"/>
-      <c r="U30" s="1" t="n"/>
-      <c r="V30" s="46" t="inlineStr">
+      <c r="S30" s="123" t="inlineStr"/>
+      <c r="T30" s="116" t="inlineStr"/>
+      <c r="U30" s="94" t="n"/>
+      <c r="V30" s="123" t="inlineStr">
         <is>
           <t>DEBT</t>
         </is>
       </c>
-      <c r="W30" s="47" t="inlineStr">
+      <c r="W30" s="123" t="inlineStr">
         <is>
           <t>DUE</t>
         </is>
       </c>
-      <c r="X30" s="47" t="inlineStr">
+      <c r="X30" s="123" t="inlineStr">
         <is>
           <t>BUDGET</t>
         </is>
       </c>
-      <c r="Y30" s="47" t="inlineStr">
+      <c r="Y30" s="123" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="Z30" s="1" t="n"/>
+      <c r="Z30" s="94" t="n"/>
       <c r="AA30" s="1" t="n"/>
       <c r="AB30" s="1" t="n"/>
       <c r="AC30" s="1" t="n"/>
@@ -3975,79 +4562,79 @@
       <c r="BF30" s="1" t="n"/>
       <c r="BG30" s="1" t="n"/>
     </row>
-    <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="48" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="94" t="n"/>
+      <c r="B31" s="124" t="inlineStr">
         <is>
           <t>Salary / Trabalho</t>
         </is>
       </c>
-      <c r="C31" s="21" t="n"/>
-      <c r="D31" s="49" t="n">
+      <c r="C31" s="125" t="n"/>
+      <c r="D31" s="126" t="n">
         <v>3161</v>
       </c>
-      <c r="E31" s="50" t="n">
+      <c r="E31" s="126" t="n">
         <v>3161</v>
       </c>
-      <c r="F31" s="51" t="n"/>
-      <c r="G31" s="1" t="n"/>
-      <c r="H31" s="48" t="inlineStr">
+      <c r="F31" s="127" t="n"/>
+      <c r="G31" s="94" t="n"/>
+      <c r="H31" s="124" t="inlineStr">
         <is>
           <t>Housing</t>
         </is>
       </c>
-      <c r="I31" s="49" t="n">
+      <c r="I31" s="126" t="n">
         <v>763</v>
       </c>
-      <c r="J31" s="52" t="n">
+      <c r="J31" s="126" t="n">
         <v>708.5</v>
       </c>
-      <c r="K31" s="53" t="n">
+      <c r="K31" s="128" t="n">
         <v>54.5</v>
       </c>
-      <c r="L31" s="51" t="n"/>
-      <c r="M31" s="21" t="n"/>
-      <c r="N31" s="1" t="n"/>
-      <c r="O31" s="54" t="inlineStr">
+      <c r="L31" s="127" t="n"/>
+      <c r="M31" s="105" t="n"/>
+      <c r="N31" s="94" t="n"/>
+      <c r="O31" s="129" t="inlineStr">
         <is>
           <t>☑</t>
         </is>
       </c>
-      <c r="P31" s="48" t="inlineStr">
+      <c r="P31" s="124" t="inlineStr">
         <is>
           <t>Gym</t>
         </is>
       </c>
-      <c r="Q31" s="18" t="inlineStr">
+      <c r="Q31" s="130" t="inlineStr">
         <is>
           <t>10/01</t>
         </is>
       </c>
-      <c r="R31" s="49" t="n">
+      <c r="R31" s="126" t="n">
         <v>32.59</v>
       </c>
-      <c r="S31" s="50" t="n">
+      <c r="S31" s="126" t="n">
         <v>32.59</v>
       </c>
-      <c r="T31" s="21" t="n"/>
-      <c r="U31" s="1" t="n"/>
-      <c r="V31" s="55" t="inlineStr">
+      <c r="T31" s="105" t="n"/>
+      <c r="U31" s="94" t="n"/>
+      <c r="V31" s="129" t="inlineStr">
         <is>
           <t>☑</t>
         </is>
       </c>
-      <c r="W31" s="48" t="inlineStr">
+      <c r="W31" s="124" t="inlineStr">
         <is>
           <t>Banco / Crédito</t>
         </is>
       </c>
-      <c r="X31" s="49" t="n">
+      <c r="X31" s="126" t="n">
         <v>400</v>
       </c>
-      <c r="Y31" s="56" t="n">
+      <c r="Y31" s="126" t="n">
         <v>3500</v>
       </c>
-      <c r="Z31" s="1" t="n"/>
+      <c r="Z31" s="94" t="n"/>
       <c r="AA31" s="1" t="n"/>
       <c r="AB31" s="1" t="n"/>
       <c r="AC31" s="1" t="n"/>
@@ -4082,79 +4669,79 @@
       <c r="BF31" s="1" t="n"/>
       <c r="BG31" s="1" t="n"/>
     </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="1" t="n"/>
-      <c r="B32" s="57" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="94" t="n"/>
+      <c r="B32" s="131" t="inlineStr">
         <is>
           <t>Side Hustle</t>
         </is>
       </c>
-      <c r="C32" s="21" t="n"/>
-      <c r="D32" s="58" t="n">
+      <c r="C32" s="132" t="n"/>
+      <c r="D32" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="59" t="n">
+      <c r="E32" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="60" t="n"/>
-      <c r="G32" s="1" t="n"/>
-      <c r="H32" s="57" t="inlineStr">
+      <c r="F32" s="134" t="n"/>
+      <c r="G32" s="94" t="n"/>
+      <c r="H32" s="131" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="I32" s="58" t="n">
+      <c r="I32" s="133" t="n">
         <v>490.5</v>
       </c>
-      <c r="J32" s="61" t="n">
+      <c r="J32" s="133" t="n">
         <v>433.28</v>
       </c>
-      <c r="K32" s="62" t="n">
+      <c r="K32" s="135" t="n">
         <v>57.23</v>
       </c>
-      <c r="L32" s="60" t="n"/>
-      <c r="M32" s="21" t="n"/>
-      <c r="N32" s="1" t="n"/>
-      <c r="O32" s="63" t="inlineStr">
+      <c r="L32" s="134" t="n"/>
+      <c r="M32" s="105" t="n"/>
+      <c r="N32" s="94" t="n"/>
+      <c r="O32" s="136" t="inlineStr">
         <is>
           <t>☑</t>
         </is>
       </c>
-      <c r="P32" s="57" t="inlineStr">
+      <c r="P32" s="131" t="inlineStr">
         <is>
           <t>ChatGPT</t>
         </is>
       </c>
-      <c r="Q32" s="64" t="inlineStr">
+      <c r="Q32" s="137" t="inlineStr">
         <is>
           <t>03/01</t>
         </is>
       </c>
-      <c r="R32" s="58" t="n">
+      <c r="R32" s="133" t="n">
         <v>21.8</v>
       </c>
-      <c r="S32" s="65" t="n">
+      <c r="S32" s="133" t="n">
         <v>21.8</v>
       </c>
-      <c r="T32" s="21" t="n"/>
-      <c r="U32" s="1" t="n"/>
-      <c r="V32" s="66" t="inlineStr">
+      <c r="T32" s="105" t="n"/>
+      <c r="U32" s="94" t="n"/>
+      <c r="V32" s="138" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="W32" s="57" t="inlineStr">
+      <c r="W32" s="131" t="inlineStr">
         <is>
           <t>Mortgage</t>
         </is>
       </c>
-      <c r="X32" s="58" t="n">
+      <c r="X32" s="133" t="n">
         <v>250</v>
       </c>
-      <c r="Y32" s="59" t="n">
+      <c r="Y32" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="Z32" s="1" t="n"/>
+      <c r="Z32" s="94" t="n"/>
       <c r="AA32" s="1" t="n"/>
       <c r="AB32" s="1" t="n"/>
       <c r="AC32" s="1" t="n"/>
@@ -4189,79 +4776,79 @@
       <c r="BF32" s="1" t="n"/>
       <c r="BG32" s="1" t="n"/>
     </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="1" t="n"/>
-      <c r="B33" s="48" t="inlineStr">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="94" t="n"/>
+      <c r="B33" s="124" t="inlineStr">
         <is>
           <t>Dividends</t>
         </is>
       </c>
-      <c r="C33" s="21" t="n"/>
-      <c r="D33" s="49" t="n">
+      <c r="C33" s="125" t="n"/>
+      <c r="D33" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="67" t="n">
+      <c r="E33" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="51" t="n"/>
-      <c r="G33" s="1" t="n"/>
-      <c r="H33" s="48" t="inlineStr">
+      <c r="F33" s="127" t="n"/>
+      <c r="G33" s="94" t="n"/>
+      <c r="H33" s="124" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="I33" s="49" t="n">
+      <c r="I33" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="52" t="n">
+      <c r="J33" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="49" t="n">
+      <c r="K33" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="51" t="n"/>
-      <c r="M33" s="21" t="n"/>
-      <c r="N33" s="1" t="n"/>
-      <c r="O33" s="54" t="inlineStr">
+      <c r="L33" s="127" t="n"/>
+      <c r="M33" s="105" t="n"/>
+      <c r="N33" s="94" t="n"/>
+      <c r="O33" s="129" t="inlineStr">
         <is>
           <t>☑</t>
         </is>
       </c>
-      <c r="P33" s="48" t="inlineStr">
+      <c r="P33" s="124" t="inlineStr">
         <is>
           <t>Google Drive</t>
         </is>
       </c>
-      <c r="Q33" s="18" t="inlineStr">
+      <c r="Q33" s="130" t="inlineStr">
         <is>
           <t>20/01</t>
         </is>
       </c>
-      <c r="R33" s="49" t="n">
+      <c r="R33" s="126" t="n">
         <v>3.26</v>
       </c>
-      <c r="S33" s="50" t="n">
+      <c r="S33" s="126" t="n">
         <v>3.26</v>
       </c>
-      <c r="T33" s="21" t="n"/>
-      <c r="U33" s="1" t="n"/>
-      <c r="V33" s="68" t="inlineStr">
+      <c r="T33" s="105" t="n"/>
+      <c r="U33" s="94" t="n"/>
+      <c r="V33" s="139" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="W33" s="48" t="inlineStr">
+      <c r="W33" s="124" t="inlineStr">
         <is>
           <t>Student Loan</t>
         </is>
       </c>
-      <c r="X33" s="49" t="n">
+      <c r="X33" s="126" t="n">
         <v>50</v>
       </c>
-      <c r="Y33" s="67" t="n">
+      <c r="Y33" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="1" t="n"/>
+      <c r="Z33" s="94" t="n"/>
       <c r="AA33" s="1" t="n"/>
       <c r="AB33" s="1" t="n"/>
       <c r="AC33" s="1" t="n"/>
@@ -4296,79 +4883,79 @@
       <c r="BF33" s="1" t="n"/>
       <c r="BG33" s="1" t="n"/>
     </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="1" t="n"/>
-      <c r="B34" s="57" t="inlineStr">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="94" t="n"/>
+      <c r="B34" s="131" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="C34" s="21" t="n"/>
-      <c r="D34" s="58" t="n">
+      <c r="C34" s="132" t="n"/>
+      <c r="D34" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="59" t="n">
+      <c r="E34" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="60" t="n"/>
-      <c r="G34" s="1" t="n"/>
-      <c r="H34" s="57" t="inlineStr">
+      <c r="F34" s="134" t="n"/>
+      <c r="G34" s="94" t="n"/>
+      <c r="H34" s="131" t="inlineStr">
         <is>
           <t>Rent (included</t>
         </is>
       </c>
-      <c r="I34" s="58" t="n">
+      <c r="I34" s="133" t="n">
         <v>763</v>
       </c>
-      <c r="J34" s="61" t="n">
+      <c r="J34" s="133" t="n">
         <v>708.5</v>
       </c>
-      <c r="K34" s="62" t="n">
+      <c r="K34" s="135" t="n">
         <v>54.5</v>
       </c>
-      <c r="L34" s="60" t="n"/>
-      <c r="M34" s="21" t="n"/>
-      <c r="N34" s="1" t="n"/>
-      <c r="O34" s="63" t="inlineStr">
+      <c r="L34" s="134" t="n"/>
+      <c r="M34" s="105" t="n"/>
+      <c r="N34" s="94" t="n"/>
+      <c r="O34" s="136" t="inlineStr">
         <is>
           <t>☑</t>
         </is>
       </c>
-      <c r="P34" s="57" t="inlineStr">
+      <c r="P34" s="131" t="inlineStr">
         <is>
           <t>Renda/Housing</t>
         </is>
       </c>
-      <c r="Q34" s="64" t="inlineStr">
+      <c r="Q34" s="137" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R34" s="58" t="n">
+      <c r="R34" s="133" t="n">
         <v>708.5</v>
       </c>
-      <c r="S34" s="65" t="n">
+      <c r="S34" s="133" t="n">
         <v>708.5</v>
       </c>
-      <c r="T34" s="21" t="n"/>
-      <c r="U34" s="1" t="n"/>
-      <c r="V34" s="66" t="inlineStr">
+      <c r="T34" s="105" t="n"/>
+      <c r="U34" s="94" t="n"/>
+      <c r="V34" s="138" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="W34" s="57" t="inlineStr">
+      <c r="W34" s="131" t="inlineStr">
         <is>
           <t>Car</t>
         </is>
       </c>
-      <c r="X34" s="58" t="n">
+      <c r="X34" s="133" t="n">
         <v>50</v>
       </c>
-      <c r="Y34" s="59" t="n">
+      <c r="Y34" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="1" t="n"/>
+      <c r="Z34" s="94" t="n"/>
       <c r="AA34" s="1" t="n"/>
       <c r="AB34" s="1" t="n"/>
       <c r="AC34" s="1" t="n"/>
@@ -4403,75 +4990,75 @@
       <c r="BF34" s="1" t="n"/>
       <c r="BG34" s="1" t="n"/>
     </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="1" t="n"/>
-      <c r="B35" s="48" t="inlineStr"/>
-      <c r="C35" s="21" t="n"/>
-      <c r="D35" s="49" t="n">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="94" t="n"/>
+      <c r="B35" s="124" t="inlineStr"/>
+      <c r="C35" s="125" t="n"/>
+      <c r="D35" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="67" t="n">
+      <c r="E35" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="F35" s="51" t="n"/>
-      <c r="G35" s="1" t="n"/>
-      <c r="H35" s="48" t="inlineStr">
+      <c r="F35" s="127" t="n"/>
+      <c r="G35" s="94" t="n"/>
+      <c r="H35" s="124" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="I35" s="49" t="n">
+      <c r="I35" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="52" t="n">
+      <c r="J35" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="K35" s="49" t="n">
+      <c r="K35" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="51" t="n"/>
-      <c r="M35" s="21" t="n"/>
-      <c r="N35" s="1" t="n"/>
-      <c r="O35" s="68" t="inlineStr">
+      <c r="L35" s="127" t="n"/>
+      <c r="M35" s="105" t="n"/>
+      <c r="N35" s="94" t="n"/>
+      <c r="O35" s="139" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P35" s="48" t="inlineStr">
+      <c r="P35" s="124" t="inlineStr">
         <is>
           <t>Home Insurance</t>
         </is>
       </c>
-      <c r="Q35" s="18" t="inlineStr">
+      <c r="Q35" s="130" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R35" s="49" t="n">
+      <c r="R35" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="S35" s="67" t="n">
+      <c r="S35" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="T35" s="21" t="n"/>
-      <c r="U35" s="1" t="n"/>
-      <c r="V35" s="55" t="inlineStr">
+      <c r="T35" s="105" t="n"/>
+      <c r="U35" s="94" t="n"/>
+      <c r="V35" s="129" t="inlineStr">
         <is>
           <t>☑</t>
         </is>
       </c>
-      <c r="W35" s="48" t="inlineStr">
+      <c r="W35" s="124" t="inlineStr">
         <is>
           <t>Personal Loan</t>
         </is>
       </c>
-      <c r="X35" s="49" t="n">
+      <c r="X35" s="126" t="n">
         <v>25</v>
       </c>
-      <c r="Y35" s="56" t="n">
+      <c r="Y35" s="126" t="n">
         <v>4675</v>
       </c>
-      <c r="Z35" s="1" t="n"/>
+      <c r="Z35" s="94" t="n"/>
       <c r="AA35" s="1" t="n"/>
       <c r="AB35" s="1" t="n"/>
       <c r="AC35" s="1" t="n"/>
@@ -4506,71 +5093,71 @@
       <c r="BF35" s="1" t="n"/>
       <c r="BG35" s="1" t="n"/>
     </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="1" t="n"/>
-      <c r="B36" s="57" t="inlineStr"/>
-      <c r="C36" s="21" t="n"/>
-      <c r="D36" s="58" t="n">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="94" t="n"/>
+      <c r="B36" s="131" t="inlineStr"/>
+      <c r="C36" s="132" t="n"/>
+      <c r="D36" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="59" t="n">
+      <c r="E36" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="60" t="n"/>
-      <c r="G36" s="1" t="n"/>
-      <c r="H36" s="57" t="inlineStr">
+      <c r="F36" s="134" t="n"/>
+      <c r="G36" s="94" t="n"/>
+      <c r="H36" s="131" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="I36" s="58" t="n">
+      <c r="I36" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="61" t="n">
+      <c r="J36" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="K36" s="58" t="n">
+      <c r="K36" s="135" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="60" t="n"/>
-      <c r="M36" s="21" t="n"/>
-      <c r="N36" s="1" t="n"/>
-      <c r="O36" s="66" t="inlineStr">
+      <c r="L36" s="134" t="n"/>
+      <c r="M36" s="105" t="n"/>
+      <c r="N36" s="94" t="n"/>
+      <c r="O36" s="138" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P36" s="57" t="inlineStr">
+      <c r="P36" s="131" t="inlineStr">
         <is>
           <t>Internet</t>
         </is>
       </c>
-      <c r="Q36" s="64" t="inlineStr">
+      <c r="Q36" s="137" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R36" s="58" t="n">
+      <c r="R36" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="S36" s="59" t="n">
+      <c r="S36" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="T36" s="21" t="n"/>
-      <c r="U36" s="1" t="n"/>
-      <c r="V36" s="66" t="inlineStr">
+      <c r="T36" s="105" t="n"/>
+      <c r="U36" s="94" t="n"/>
+      <c r="V36" s="138" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="W36" s="57" t="inlineStr"/>
-      <c r="X36" s="58" t="n">
+      <c r="W36" s="131" t="inlineStr"/>
+      <c r="X36" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="Y36" s="59" t="n">
+      <c r="Y36" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="1" t="n"/>
+      <c r="Z36" s="94" t="n"/>
       <c r="AA36" s="1" t="n"/>
       <c r="AB36" s="1" t="n"/>
       <c r="AC36" s="1" t="n"/>
@@ -4605,63 +5192,63 @@
       <c r="BF36" s="1" t="n"/>
       <c r="BG36" s="1" t="n"/>
     </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="1" t="n"/>
-      <c r="B37" s="51" t="n"/>
-      <c r="C37" s="51" t="n"/>
-      <c r="D37" s="51" t="n"/>
-      <c r="E37" s="51" t="n"/>
-      <c r="F37" s="51" t="n"/>
-      <c r="G37" s="1" t="n"/>
-      <c r="H37" s="48" t="inlineStr">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="94" t="n"/>
+      <c r="B37" s="124" t="n"/>
+      <c r="C37" s="140" t="n"/>
+      <c r="D37" s="130" t="n"/>
+      <c r="E37" s="130" t="n"/>
+      <c r="F37" s="141" t="n"/>
+      <c r="G37" s="94" t="n"/>
+      <c r="H37" s="124" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="I37" s="49" t="n">
+      <c r="I37" s="126" t="n">
         <v>174.4</v>
       </c>
-      <c r="J37" s="52" t="n">
+      <c r="J37" s="126" t="n">
         <v>51.99</v>
       </c>
-      <c r="K37" s="53" t="n">
+      <c r="K37" s="128" t="n">
         <v>122.41</v>
       </c>
-      <c r="L37" s="51" t="n"/>
-      <c r="M37" s="21" t="n"/>
-      <c r="N37" s="1" t="n"/>
-      <c r="O37" s="68" t="inlineStr">
+      <c r="L37" s="127" t="n"/>
+      <c r="M37" s="105" t="n"/>
+      <c r="N37" s="94" t="n"/>
+      <c r="O37" s="139" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P37" s="48" t="inlineStr"/>
-      <c r="Q37" s="18" t="inlineStr">
+      <c r="P37" s="124" t="inlineStr"/>
+      <c r="Q37" s="130" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R37" s="49" t="n">
+      <c r="R37" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="S37" s="67" t="n">
+      <c r="S37" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="T37" s="21" t="n"/>
-      <c r="U37" s="1" t="n"/>
-      <c r="V37" s="68" t="inlineStr">
+      <c r="T37" s="105" t="n"/>
+      <c r="U37" s="94" t="n"/>
+      <c r="V37" s="139" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="W37" s="48" t="inlineStr"/>
-      <c r="X37" s="49" t="n">
+      <c r="W37" s="124" t="inlineStr"/>
+      <c r="X37" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="Y37" s="67" t="n">
+      <c r="Y37" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="1" t="n"/>
+      <c r="Z37" s="94" t="n"/>
       <c r="AA37" s="1" t="n"/>
       <c r="AB37" s="1" t="n"/>
       <c r="AC37" s="1" t="n"/>
@@ -4696,63 +5283,63 @@
       <c r="BF37" s="1" t="n"/>
       <c r="BG37" s="1" t="n"/>
     </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="1" t="n"/>
-      <c r="B38" s="60" t="n"/>
-      <c r="C38" s="60" t="n"/>
-      <c r="D38" s="60" t="n"/>
-      <c r="E38" s="60" t="n"/>
-      <c r="F38" s="60" t="n"/>
-      <c r="G38" s="1" t="n"/>
-      <c r="H38" s="57" t="inlineStr">
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="94" t="n"/>
+      <c r="B38" s="131" t="n"/>
+      <c r="C38" s="142" t="n"/>
+      <c r="D38" s="137" t="n"/>
+      <c r="E38" s="137" t="n"/>
+      <c r="F38" s="141" t="n"/>
+      <c r="G38" s="94" t="n"/>
+      <c r="H38" s="131" t="inlineStr">
         <is>
           <t>Holidays</t>
         </is>
       </c>
-      <c r="I38" s="58" t="n">
+      <c r="I38" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="61" t="n">
+      <c r="J38" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="K38" s="58" t="n">
+      <c r="K38" s="135" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="60" t="n"/>
-      <c r="M38" s="21" t="n"/>
-      <c r="N38" s="1" t="n"/>
-      <c r="O38" s="66" t="inlineStr">
+      <c r="L38" s="134" t="n"/>
+      <c r="M38" s="105" t="n"/>
+      <c r="N38" s="94" t="n"/>
+      <c r="O38" s="138" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P38" s="57" t="inlineStr"/>
-      <c r="Q38" s="64" t="inlineStr">
+      <c r="P38" s="131" t="inlineStr"/>
+      <c r="Q38" s="137" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R38" s="58" t="n">
+      <c r="R38" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="S38" s="59" t="n">
+      <c r="S38" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="T38" s="21" t="n"/>
-      <c r="U38" s="1" t="n"/>
-      <c r="V38" s="66" t="inlineStr">
+      <c r="T38" s="105" t="n"/>
+      <c r="U38" s="94" t="n"/>
+      <c r="V38" s="138" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="W38" s="57" t="inlineStr"/>
-      <c r="X38" s="58" t="n">
+      <c r="W38" s="131" t="inlineStr"/>
+      <c r="X38" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="Y38" s="59" t="n">
+      <c r="Y38" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="Z38" s="1" t="n"/>
+      <c r="Z38" s="94" t="n"/>
       <c r="AA38" s="1" t="n"/>
       <c r="AB38" s="1" t="n"/>
       <c r="AC38" s="1" t="n"/>
@@ -4787,63 +5374,63 @@
       <c r="BF38" s="1" t="n"/>
       <c r="BG38" s="1" t="n"/>
     </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="1" t="n"/>
-      <c r="B39" s="51" t="n"/>
-      <c r="C39" s="51" t="n"/>
-      <c r="D39" s="51" t="n"/>
-      <c r="E39" s="51" t="n"/>
-      <c r="F39" s="51" t="n"/>
-      <c r="G39" s="1" t="n"/>
-      <c r="H39" s="48" t="inlineStr">
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="94" t="n"/>
+      <c r="B39" s="124" t="n"/>
+      <c r="C39" s="140" t="n"/>
+      <c r="D39" s="130" t="n"/>
+      <c r="E39" s="130" t="n"/>
+      <c r="F39" s="141" t="n"/>
+      <c r="G39" s="94" t="n"/>
+      <c r="H39" s="124" t="inlineStr">
         <is>
           <t>Leisure</t>
         </is>
       </c>
-      <c r="I39" s="49" t="n">
+      <c r="I39" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="52" t="n">
+      <c r="J39" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="K39" s="49" t="n">
+      <c r="K39" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="51" t="n"/>
-      <c r="M39" s="21" t="n"/>
-      <c r="N39" s="1" t="n"/>
-      <c r="O39" s="68" t="inlineStr">
+      <c r="L39" s="127" t="n"/>
+      <c r="M39" s="105" t="n"/>
+      <c r="N39" s="94" t="n"/>
+      <c r="O39" s="139" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P39" s="48" t="inlineStr"/>
-      <c r="Q39" s="18" t="inlineStr">
+      <c r="P39" s="124" t="inlineStr"/>
+      <c r="Q39" s="130" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R39" s="49" t="n">
+      <c r="R39" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="S39" s="67" t="n">
+      <c r="S39" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="T39" s="21" t="n"/>
-      <c r="U39" s="1" t="n"/>
-      <c r="V39" s="68" t="inlineStr">
+      <c r="T39" s="105" t="n"/>
+      <c r="U39" s="94" t="n"/>
+      <c r="V39" s="139" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="W39" s="48" t="inlineStr"/>
-      <c r="X39" s="49" t="n">
+      <c r="W39" s="124" t="inlineStr"/>
+      <c r="X39" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="Y39" s="67" t="n">
+      <c r="Y39" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="1" t="n"/>
+      <c r="Z39" s="94" t="n"/>
       <c r="AA39" s="1" t="n"/>
       <c r="AB39" s="1" t="n"/>
       <c r="AC39" s="1" t="n"/>
@@ -4878,63 +5465,63 @@
       <c r="BF39" s="1" t="n"/>
       <c r="BG39" s="1" t="n"/>
     </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="1" t="n"/>
-      <c r="B40" s="60" t="n"/>
-      <c r="C40" s="60" t="n"/>
-      <c r="D40" s="60" t="n"/>
-      <c r="E40" s="60" t="n"/>
-      <c r="F40" s="60" t="n"/>
-      <c r="G40" s="1" t="n"/>
-      <c r="H40" s="57" t="inlineStr">
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="94" t="n"/>
+      <c r="B40" s="131" t="n"/>
+      <c r="C40" s="142" t="n"/>
+      <c r="D40" s="137" t="n"/>
+      <c r="E40" s="137" t="n"/>
+      <c r="F40" s="141" t="n"/>
+      <c r="G40" s="94" t="n"/>
+      <c r="H40" s="131" t="inlineStr">
         <is>
           <t>Misc</t>
         </is>
       </c>
-      <c r="I40" s="58" t="n">
+      <c r="I40" s="133" t="n">
         <v>163.5</v>
       </c>
-      <c r="J40" s="61" t="n">
+      <c r="J40" s="133" t="n">
         <v>103.99</v>
       </c>
-      <c r="K40" s="62" t="n">
+      <c r="K40" s="135" t="n">
         <v>59.51</v>
       </c>
-      <c r="L40" s="60" t="n"/>
-      <c r="M40" s="21" t="n"/>
-      <c r="N40" s="1" t="n"/>
-      <c r="O40" s="66" t="inlineStr">
+      <c r="L40" s="134" t="n"/>
+      <c r="M40" s="105" t="n"/>
+      <c r="N40" s="94" t="n"/>
+      <c r="O40" s="138" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P40" s="57" t="inlineStr"/>
-      <c r="Q40" s="64" t="inlineStr">
+      <c r="P40" s="131" t="inlineStr"/>
+      <c r="Q40" s="137" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R40" s="58" t="n">
+      <c r="R40" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="S40" s="59" t="n">
+      <c r="S40" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="T40" s="21" t="n"/>
-      <c r="U40" s="1" t="n"/>
-      <c r="V40" s="66" t="inlineStr">
+      <c r="T40" s="105" t="n"/>
+      <c r="U40" s="94" t="n"/>
+      <c r="V40" s="138" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="W40" s="57" t="inlineStr"/>
-      <c r="X40" s="58" t="n">
+      <c r="W40" s="131" t="inlineStr"/>
+      <c r="X40" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="Y40" s="59" t="n">
+      <c r="Y40" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="1" t="n"/>
+      <c r="Z40" s="94" t="n"/>
       <c r="AA40" s="1" t="n"/>
       <c r="AB40" s="1" t="n"/>
       <c r="AC40" s="1" t="n"/>
@@ -4969,63 +5556,63 @@
       <c r="BF40" s="1" t="n"/>
       <c r="BG40" s="1" t="n"/>
     </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="51" t="n"/>
-      <c r="C41" s="51" t="n"/>
-      <c r="D41" s="51" t="n"/>
-      <c r="E41" s="51" t="n"/>
-      <c r="F41" s="51" t="n"/>
-      <c r="G41" s="1" t="n"/>
-      <c r="H41" s="48" t="inlineStr">
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="94" t="n"/>
+      <c r="B41" s="124" t="n"/>
+      <c r="C41" s="140" t="n"/>
+      <c r="D41" s="130" t="n"/>
+      <c r="E41" s="130" t="n"/>
+      <c r="F41" s="141" t="n"/>
+      <c r="G41" s="94" t="n"/>
+      <c r="H41" s="124" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="I41" s="49" t="n">
+      <c r="I41" s="126" t="n">
         <v>283.4</v>
       </c>
-      <c r="J41" s="52" t="n">
+      <c r="J41" s="126" t="n">
         <v>202.2</v>
       </c>
-      <c r="K41" s="53" t="n">
+      <c r="K41" s="128" t="n">
         <v>81.20999999999999</v>
       </c>
-      <c r="L41" s="51" t="n"/>
-      <c r="M41" s="21" t="n"/>
-      <c r="N41" s="1" t="n"/>
-      <c r="O41" s="68" t="inlineStr">
+      <c r="L41" s="127" t="n"/>
+      <c r="M41" s="105" t="n"/>
+      <c r="N41" s="94" t="n"/>
+      <c r="O41" s="139" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P41" s="48" t="inlineStr"/>
-      <c r="Q41" s="18" t="inlineStr">
+      <c r="P41" s="124" t="inlineStr"/>
+      <c r="Q41" s="130" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R41" s="49" t="n">
+      <c r="R41" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="S41" s="67" t="n">
+      <c r="S41" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="T41" s="21" t="n"/>
-      <c r="U41" s="1" t="n"/>
-      <c r="V41" s="68" t="inlineStr">
+      <c r="T41" s="105" t="n"/>
+      <c r="U41" s="94" t="n"/>
+      <c r="V41" s="139" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="W41" s="48" t="inlineStr"/>
-      <c r="X41" s="49" t="n">
+      <c r="W41" s="124" t="inlineStr"/>
+      <c r="X41" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="Y41" s="67" t="n">
+      <c r="Y41" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="1" t="n"/>
+      <c r="Z41" s="94" t="n"/>
       <c r="AA41" s="1" t="n"/>
       <c r="AB41" s="1" t="n"/>
       <c r="AC41" s="1" t="n"/>
@@ -5060,63 +5647,63 @@
       <c r="BF41" s="1" t="n"/>
       <c r="BG41" s="1" t="n"/>
     </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="60" t="n"/>
-      <c r="C42" s="60" t="n"/>
-      <c r="D42" s="60" t="n"/>
-      <c r="E42" s="60" t="n"/>
-      <c r="F42" s="60" t="n"/>
-      <c r="G42" s="1" t="n"/>
-      <c r="H42" s="57" t="inlineStr">
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="94" t="n"/>
+      <c r="B42" s="131" t="n"/>
+      <c r="C42" s="142" t="n"/>
+      <c r="D42" s="137" t="n"/>
+      <c r="E42" s="137" t="n"/>
+      <c r="F42" s="141" t="n"/>
+      <c r="G42" s="94" t="n"/>
+      <c r="H42" s="131" t="inlineStr">
         <is>
           <t>Shopping</t>
         </is>
       </c>
-      <c r="I42" s="58" t="n">
+      <c r="I42" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="61" t="n">
+      <c r="J42" s="133" t="n">
         <v>161.76</v>
       </c>
-      <c r="K42" s="69" t="n">
+      <c r="K42" s="143" t="n">
         <v>-161.76</v>
       </c>
-      <c r="L42" s="60" t="n"/>
-      <c r="M42" s="21" t="n"/>
-      <c r="N42" s="1" t="n"/>
-      <c r="O42" s="66" t="inlineStr">
+      <c r="L42" s="134" t="n"/>
+      <c r="M42" s="105" t="n"/>
+      <c r="N42" s="94" t="n"/>
+      <c r="O42" s="138" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P42" s="57" t="inlineStr"/>
-      <c r="Q42" s="64" t="inlineStr">
+      <c r="P42" s="131" t="inlineStr"/>
+      <c r="Q42" s="137" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R42" s="58" t="n">
+      <c r="R42" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="S42" s="59" t="n">
+      <c r="S42" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="T42" s="21" t="n"/>
-      <c r="U42" s="1" t="n"/>
-      <c r="V42" s="66" t="inlineStr">
+      <c r="T42" s="105" t="n"/>
+      <c r="U42" s="94" t="n"/>
+      <c r="V42" s="138" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="W42" s="57" t="inlineStr"/>
-      <c r="X42" s="58" t="n">
+      <c r="W42" s="131" t="inlineStr"/>
+      <c r="X42" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="Y42" s="59" t="n">
+      <c r="Y42" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="1" t="n"/>
+      <c r="Z42" s="94" t="n"/>
       <c r="AA42" s="1" t="n"/>
       <c r="AB42" s="1" t="n"/>
       <c r="AC42" s="1" t="n"/>
@@ -5151,63 +5738,63 @@
       <c r="BF42" s="1" t="n"/>
       <c r="BG42" s="1" t="n"/>
     </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="51" t="n"/>
-      <c r="C43" s="51" t="n"/>
-      <c r="D43" s="51" t="n"/>
-      <c r="E43" s="51" t="n"/>
-      <c r="F43" s="51" t="n"/>
-      <c r="G43" s="1" t="n"/>
-      <c r="H43" s="48" t="inlineStr">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="94" t="n"/>
+      <c r="B43" s="124" t="n"/>
+      <c r="C43" s="140" t="n"/>
+      <c r="D43" s="130" t="n"/>
+      <c r="E43" s="130" t="n"/>
+      <c r="F43" s="141" t="n"/>
+      <c r="G43" s="94" t="n"/>
+      <c r="H43" s="124" t="inlineStr">
         <is>
           <t>Pets</t>
         </is>
       </c>
-      <c r="I43" s="49" t="n">
+      <c r="I43" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="52" t="n">
+      <c r="J43" s="126" t="n">
         <v>40.44</v>
       </c>
-      <c r="K43" s="70" t="n">
+      <c r="K43" s="144" t="n">
         <v>-40.44</v>
       </c>
-      <c r="L43" s="51" t="n"/>
-      <c r="M43" s="21" t="n"/>
-      <c r="N43" s="1" t="n"/>
-      <c r="O43" s="68" t="inlineStr">
+      <c r="L43" s="127" t="n"/>
+      <c r="M43" s="105" t="n"/>
+      <c r="N43" s="94" t="n"/>
+      <c r="O43" s="139" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P43" s="48" t="inlineStr"/>
-      <c r="Q43" s="18" t="inlineStr">
+      <c r="P43" s="124" t="inlineStr"/>
+      <c r="Q43" s="130" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R43" s="49" t="n">
+      <c r="R43" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="S43" s="67" t="n">
+      <c r="S43" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="T43" s="21" t="n"/>
-      <c r="U43" s="1" t="n"/>
-      <c r="V43" s="68" t="inlineStr">
+      <c r="T43" s="105" t="n"/>
+      <c r="U43" s="94" t="n"/>
+      <c r="V43" s="139" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="W43" s="48" t="inlineStr"/>
-      <c r="X43" s="49" t="n">
+      <c r="W43" s="124" t="inlineStr"/>
+      <c r="X43" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="Y43" s="67" t="n">
+      <c r="Y43" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="1" t="n"/>
+      <c r="Z43" s="94" t="n"/>
       <c r="AA43" s="1" t="n"/>
       <c r="AB43" s="1" t="n"/>
       <c r="AC43" s="1" t="n"/>
@@ -5242,63 +5829,63 @@
       <c r="BF43" s="1" t="n"/>
       <c r="BG43" s="1" t="n"/>
     </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="60" t="n"/>
-      <c r="C44" s="60" t="n"/>
-      <c r="D44" s="60" t="n"/>
-      <c r="E44" s="60" t="n"/>
-      <c r="F44" s="60" t="n"/>
-      <c r="G44" s="1" t="n"/>
-      <c r="H44" s="57" t="inlineStr">
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="94" t="n"/>
+      <c r="B44" s="131" t="n"/>
+      <c r="C44" s="142" t="n"/>
+      <c r="D44" s="137" t="n"/>
+      <c r="E44" s="137" t="n"/>
+      <c r="F44" s="141" t="n"/>
+      <c r="G44" s="94" t="n"/>
+      <c r="H44" s="131" t="inlineStr">
         <is>
           <t>Bills</t>
         </is>
       </c>
-      <c r="I44" s="58" t="n">
+      <c r="I44" s="133" t="n">
         <v>283.4</v>
       </c>
-      <c r="J44" s="61" t="n">
+      <c r="J44" s="133" t="n">
         <v>147.91</v>
       </c>
-      <c r="K44" s="62" t="n">
+      <c r="K44" s="135" t="n">
         <v>135.49</v>
       </c>
-      <c r="L44" s="60" t="n"/>
-      <c r="M44" s="21" t="n"/>
-      <c r="N44" s="1" t="n"/>
-      <c r="O44" s="66" t="inlineStr">
+      <c r="L44" s="134" t="n"/>
+      <c r="M44" s="105" t="n"/>
+      <c r="N44" s="94" t="n"/>
+      <c r="O44" s="138" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P44" s="57" t="inlineStr"/>
-      <c r="Q44" s="64" t="inlineStr">
+      <c r="P44" s="131" t="inlineStr"/>
+      <c r="Q44" s="137" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R44" s="58" t="n">
+      <c r="R44" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="S44" s="59" t="n">
+      <c r="S44" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="T44" s="21" t="n"/>
-      <c r="U44" s="1" t="n"/>
-      <c r="V44" s="66" t="inlineStr">
+      <c r="T44" s="105" t="n"/>
+      <c r="U44" s="94" t="n"/>
+      <c r="V44" s="138" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="W44" s="57" t="inlineStr"/>
-      <c r="X44" s="58" t="n">
+      <c r="W44" s="131" t="inlineStr"/>
+      <c r="X44" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="Y44" s="59" t="n">
+      <c r="Y44" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="1" t="n"/>
+      <c r="Z44" s="94" t="n"/>
       <c r="AA44" s="1" t="n"/>
       <c r="AB44" s="1" t="n"/>
       <c r="AC44" s="1" t="n"/>
@@ -5333,59 +5920,59 @@
       <c r="BF44" s="1" t="n"/>
       <c r="BG44" s="1" t="n"/>
     </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="51" t="n"/>
-      <c r="C45" s="51" t="n"/>
-      <c r="D45" s="51" t="n"/>
-      <c r="E45" s="51" t="n"/>
-      <c r="F45" s="51" t="n"/>
-      <c r="G45" s="1" t="n"/>
-      <c r="H45" s="48" t="inlineStr"/>
-      <c r="I45" s="49" t="n">
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="94" t="n"/>
+      <c r="B45" s="124" t="n"/>
+      <c r="C45" s="140" t="n"/>
+      <c r="D45" s="130" t="n"/>
+      <c r="E45" s="130" t="n"/>
+      <c r="F45" s="141" t="n"/>
+      <c r="G45" s="94" t="n"/>
+      <c r="H45" s="124" t="inlineStr"/>
+      <c r="I45" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="52" t="n">
+      <c r="J45" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="K45" s="49" t="n">
+      <c r="K45" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="L45" s="51" t="n"/>
-      <c r="M45" s="21" t="n"/>
-      <c r="N45" s="1" t="n"/>
-      <c r="O45" s="68" t="inlineStr">
+      <c r="L45" s="127" t="n"/>
+      <c r="M45" s="105" t="n"/>
+      <c r="N45" s="94" t="n"/>
+      <c r="O45" s="139" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="P45" s="48" t="inlineStr"/>
-      <c r="Q45" s="18" t="inlineStr">
+      <c r="P45" s="124" t="inlineStr"/>
+      <c r="Q45" s="130" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R45" s="49" t="n">
+      <c r="R45" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="S45" s="67" t="n">
+      <c r="S45" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="T45" s="21" t="n"/>
-      <c r="U45" s="1" t="n"/>
-      <c r="V45" s="68" t="inlineStr">
+      <c r="T45" s="105" t="n"/>
+      <c r="U45" s="94" t="n"/>
+      <c r="V45" s="139" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="W45" s="48" t="inlineStr"/>
-      <c r="X45" s="49" t="n">
+      <c r="W45" s="124" t="inlineStr"/>
+      <c r="X45" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="Y45" s="67" t="n">
+      <c r="Y45" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="1" t="n"/>
+      <c r="Z45" s="94" t="n"/>
       <c r="AA45" s="1" t="n"/>
       <c r="AB45" s="1" t="n"/>
       <c r="AC45" s="1" t="n"/>
@@ -5420,67 +6007,67 @@
       <c r="BF45" s="1" t="n"/>
       <c r="BG45" s="1" t="n"/>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="1" t="n"/>
-      <c r="B46" s="71" t="inlineStr">
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="94" t="n"/>
+      <c r="B46" s="145" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C46" s="38" t="n"/>
-      <c r="D46" s="72" t="n">
+      <c r="C46" s="145" t="n"/>
+      <c r="D46" s="146" t="n">
         <v>3161</v>
       </c>
-      <c r="E46" s="73" t="n">
+      <c r="E46" s="146" t="n">
         <v>3161</v>
       </c>
-      <c r="F46" s="41" t="n"/>
-      <c r="G46" s="41" t="n"/>
-      <c r="H46" s="74" t="inlineStr">
+      <c r="F46" s="94" t="n"/>
+      <c r="G46" s="94" t="n"/>
+      <c r="H46" s="145" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="I46" s="72" t="n">
+      <c r="I46" s="146" t="n">
         <v>1914.8</v>
       </c>
-      <c r="J46" s="75" t="n">
+      <c r="J46" s="146" t="n">
         <v>1850.07</v>
       </c>
-      <c r="K46" s="73" t="n">
+      <c r="K46" s="146" t="n">
         <v>64.73</v>
       </c>
-      <c r="L46" s="41" t="n"/>
-      <c r="M46" s="41" t="n"/>
-      <c r="N46" s="41" t="n"/>
-      <c r="O46" s="41" t="n"/>
-      <c r="P46" s="76" t="inlineStr">
+      <c r="L46" s="94" t="n"/>
+      <c r="M46" s="94" t="n"/>
+      <c r="N46" s="94" t="n"/>
+      <c r="O46" s="145" t="n"/>
+      <c r="P46" s="145" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="Q46" s="41" t="n"/>
-      <c r="R46" s="72" t="n">
+      <c r="Q46" s="145" t="n"/>
+      <c r="R46" s="146" t="n">
         <v>766.15</v>
       </c>
-      <c r="S46" s="73" t="n">
+      <c r="S46" s="146" t="n">
         <v>766.15</v>
       </c>
-      <c r="T46" s="41" t="n"/>
-      <c r="U46" s="41" t="n"/>
-      <c r="V46" s="41" t="n"/>
-      <c r="W46" s="77" t="inlineStr">
+      <c r="T46" s="94" t="n"/>
+      <c r="U46" s="94" t="n"/>
+      <c r="V46" s="145" t="n"/>
+      <c r="W46" s="145" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="X46" s="72" t="n">
+      <c r="X46" s="146" t="n">
         <v>775</v>
       </c>
-      <c r="Y46" s="78" t="n">
+      <c r="Y46" s="146" t="n">
         <v>8175</v>
       </c>
-      <c r="Z46" s="1" t="n"/>
+      <c r="Z46" s="94" t="n"/>
       <c r="AA46" s="1" t="n"/>
       <c r="AB46" s="1" t="n"/>
       <c r="AC46" s="1" t="n"/>
@@ -5516,32 +6103,32 @@
       <c r="BG46" s="1" t="n"/>
     </row>
     <row r="47" ht="8" customHeight="1">
-      <c r="A47" s="1" t="n"/>
-      <c r="B47" s="1" t="n"/>
-      <c r="C47" s="1" t="n"/>
-      <c r="D47" s="1" t="n"/>
-      <c r="E47" s="1" t="n"/>
-      <c r="F47" s="1" t="n"/>
-      <c r="G47" s="1" t="n"/>
-      <c r="H47" s="1" t="n"/>
-      <c r="I47" s="1" t="n"/>
-      <c r="J47" s="1" t="n"/>
-      <c r="K47" s="1" t="n"/>
-      <c r="L47" s="1" t="n"/>
-      <c r="M47" s="1" t="n"/>
-      <c r="N47" s="1" t="n"/>
-      <c r="O47" s="1" t="n"/>
-      <c r="P47" s="1" t="n"/>
-      <c r="Q47" s="1" t="n"/>
-      <c r="R47" s="1" t="n"/>
-      <c r="S47" s="1" t="n"/>
-      <c r="T47" s="1" t="n"/>
-      <c r="U47" s="1" t="n"/>
-      <c r="V47" s="1" t="n"/>
-      <c r="W47" s="1" t="n"/>
-      <c r="X47" s="1" t="n"/>
-      <c r="Y47" s="1" t="n"/>
-      <c r="Z47" s="1" t="n"/>
+      <c r="A47" s="94" t="n"/>
+      <c r="B47" s="94" t="n"/>
+      <c r="C47" s="94" t="n"/>
+      <c r="D47" s="94" t="n"/>
+      <c r="E47" s="94" t="n"/>
+      <c r="F47" s="94" t="n"/>
+      <c r="G47" s="94" t="n"/>
+      <c r="H47" s="94" t="n"/>
+      <c r="I47" s="94" t="n"/>
+      <c r="J47" s="94" t="n"/>
+      <c r="K47" s="94" t="n"/>
+      <c r="L47" s="94" t="n"/>
+      <c r="M47" s="94" t="n"/>
+      <c r="N47" s="94" t="n"/>
+      <c r="O47" s="94" t="n"/>
+      <c r="P47" s="94" t="n"/>
+      <c r="Q47" s="94" t="n"/>
+      <c r="R47" s="94" t="n"/>
+      <c r="S47" s="94" t="n"/>
+      <c r="T47" s="94" t="n"/>
+      <c r="U47" s="94" t="n"/>
+      <c r="V47" s="94" t="n"/>
+      <c r="W47" s="94" t="n"/>
+      <c r="X47" s="94" t="n"/>
+      <c r="Y47" s="94" t="n"/>
+      <c r="Z47" s="94" t="n"/>
       <c r="AA47" s="1" t="n"/>
       <c r="AB47" s="1" t="n"/>
       <c r="AC47" s="1" t="n"/>
@@ -5576,33 +6163,37 @@
       <c r="BF47" s="1" t="n"/>
       <c r="BG47" s="1" t="n"/>
     </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="1" t="n"/>
-      <c r="B48" s="79" t="inlineStr">
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="94" t="n"/>
+      <c r="B48" s="113" t="inlineStr">
         <is>
           <t>SAVINGS</t>
         </is>
       </c>
-      <c r="G48" s="1" t="n"/>
-      <c r="H48" s="1" t="n"/>
-      <c r="I48" s="1" t="n"/>
-      <c r="J48" s="1" t="n"/>
-      <c r="K48" s="1" t="n"/>
-      <c r="L48" s="1" t="n"/>
-      <c r="M48" s="1" t="n"/>
-      <c r="N48" s="1" t="n"/>
-      <c r="O48" s="1" t="n"/>
-      <c r="P48" s="1" t="n"/>
-      <c r="Q48" s="1" t="n"/>
-      <c r="R48" s="1" t="n"/>
-      <c r="S48" s="1" t="n"/>
-      <c r="T48" s="1" t="n"/>
-      <c r="U48" s="1" t="n"/>
-      <c r="V48" s="1" t="n"/>
-      <c r="W48" s="1" t="n"/>
-      <c r="X48" s="1" t="n"/>
-      <c r="Y48" s="1" t="n"/>
-      <c r="Z48" s="1" t="n"/>
+      <c r="C48" s="113" t="n"/>
+      <c r="D48" s="113" t="n"/>
+      <c r="E48" s="113" t="n"/>
+      <c r="F48" s="105" t="n"/>
+      <c r="G48" s="94" t="n"/>
+      <c r="H48" s="94" t="n"/>
+      <c r="I48" s="94" t="n"/>
+      <c r="J48" s="94" t="n"/>
+      <c r="K48" s="94" t="n"/>
+      <c r="L48" s="94" t="n"/>
+      <c r="M48" s="94" t="n"/>
+      <c r="N48" s="94" t="n"/>
+      <c r="O48" s="94" t="n"/>
+      <c r="P48" s="94" t="n"/>
+      <c r="Q48" s="94" t="n"/>
+      <c r="R48" s="94" t="n"/>
+      <c r="S48" s="94" t="n"/>
+      <c r="T48" s="94" t="n"/>
+      <c r="U48" s="94" t="n"/>
+      <c r="V48" s="94" t="n"/>
+      <c r="W48" s="94" t="n"/>
+      <c r="X48" s="94" t="n"/>
+      <c r="Y48" s="94" t="n"/>
+      <c r="Z48" s="94" t="n"/>
       <c r="AA48" s="1" t="n"/>
       <c r="AB48" s="1" t="n"/>
       <c r="AC48" s="1" t="n"/>
@@ -5637,41 +6228,41 @@
       <c r="BF48" s="1" t="n"/>
       <c r="BG48" s="1" t="n"/>
     </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="1" t="n"/>
-      <c r="B49" s="47" t="inlineStr"/>
-      <c r="C49" s="47" t="inlineStr"/>
-      <c r="D49" s="47" t="inlineStr">
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="94" t="n"/>
+      <c r="B49" s="147" t="inlineStr"/>
+      <c r="C49" s="147" t="inlineStr"/>
+      <c r="D49" s="147" t="inlineStr">
         <is>
           <t>EXPECTED</t>
         </is>
       </c>
-      <c r="E49" s="47" t="inlineStr">
+      <c r="E49" s="147" t="inlineStr">
         <is>
           <t>ACTUAL</t>
         </is>
       </c>
-      <c r="F49" s="47" t="inlineStr"/>
-      <c r="G49" s="1" t="n"/>
-      <c r="H49" s="1" t="n"/>
-      <c r="I49" s="1" t="n"/>
-      <c r="J49" s="1" t="n"/>
-      <c r="K49" s="1" t="n"/>
-      <c r="L49" s="1" t="n"/>
-      <c r="M49" s="1" t="n"/>
-      <c r="N49" s="1" t="n"/>
-      <c r="O49" s="1" t="n"/>
-      <c r="P49" s="1" t="n"/>
-      <c r="Q49" s="1" t="n"/>
-      <c r="R49" s="1" t="n"/>
-      <c r="S49" s="1" t="n"/>
-      <c r="T49" s="1" t="n"/>
-      <c r="U49" s="1" t="n"/>
-      <c r="V49" s="1" t="n"/>
-      <c r="W49" s="1" t="n"/>
-      <c r="X49" s="1" t="n"/>
-      <c r="Y49" s="1" t="n"/>
-      <c r="Z49" s="1" t="n"/>
+      <c r="F49" s="116" t="inlineStr"/>
+      <c r="G49" s="94" t="n"/>
+      <c r="H49" s="94" t="n"/>
+      <c r="I49" s="94" t="n"/>
+      <c r="J49" s="94" t="n"/>
+      <c r="K49" s="94" t="n"/>
+      <c r="L49" s="94" t="n"/>
+      <c r="M49" s="94" t="n"/>
+      <c r="N49" s="94" t="n"/>
+      <c r="O49" s="94" t="n"/>
+      <c r="P49" s="94" t="n"/>
+      <c r="Q49" s="94" t="n"/>
+      <c r="R49" s="94" t="n"/>
+      <c r="S49" s="94" t="n"/>
+      <c r="T49" s="94" t="n"/>
+      <c r="U49" s="94" t="n"/>
+      <c r="V49" s="94" t="n"/>
+      <c r="W49" s="94" t="n"/>
+      <c r="X49" s="94" t="n"/>
+      <c r="Y49" s="94" t="n"/>
+      <c r="Z49" s="94" t="n"/>
       <c r="AA49" s="1" t="n"/>
       <c r="AB49" s="1" t="n"/>
       <c r="AC49" s="1" t="n"/>
@@ -5707,40 +6298,40 @@
       <c r="BG49" s="1" t="n"/>
     </row>
     <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="1" t="n"/>
-      <c r="B50" s="48" t="inlineStr">
+      <c r="A50" s="94" t="n"/>
+      <c r="B50" s="131" t="inlineStr">
         <is>
           <t>New Laptop</t>
         </is>
       </c>
-      <c r="C50" s="21" t="n"/>
-      <c r="D50" s="49" t="n">
+      <c r="C50" s="142" t="n"/>
+      <c r="D50" s="133" t="n">
         <v>2398</v>
       </c>
-      <c r="E50" s="80" t="n">
+      <c r="E50" s="133" t="n">
         <v>982</v>
       </c>
-      <c r="F50" s="29" t="n"/>
-      <c r="G50" s="1" t="n"/>
-      <c r="H50" s="1" t="n"/>
-      <c r="I50" s="1" t="n"/>
-      <c r="J50" s="1" t="n"/>
-      <c r="K50" s="1" t="n"/>
-      <c r="L50" s="1" t="n"/>
-      <c r="M50" s="1" t="n"/>
-      <c r="N50" s="1" t="n"/>
-      <c r="O50" s="1" t="n"/>
-      <c r="P50" s="1" t="n"/>
-      <c r="Q50" s="1" t="n"/>
-      <c r="R50" s="1" t="n"/>
-      <c r="S50" s="1" t="n"/>
-      <c r="T50" s="1" t="n"/>
-      <c r="U50" s="1" t="n"/>
-      <c r="V50" s="1" t="n"/>
-      <c r="W50" s="1" t="n"/>
-      <c r="X50" s="1" t="n"/>
-      <c r="Y50" s="1" t="n"/>
-      <c r="Z50" s="1" t="n"/>
+      <c r="F50" s="94" t="n"/>
+      <c r="G50" s="94" t="n"/>
+      <c r="H50" s="94" t="n"/>
+      <c r="I50" s="94" t="n"/>
+      <c r="J50" s="94" t="n"/>
+      <c r="K50" s="94" t="n"/>
+      <c r="L50" s="94" t="n"/>
+      <c r="M50" s="94" t="n"/>
+      <c r="N50" s="94" t="n"/>
+      <c r="O50" s="94" t="n"/>
+      <c r="P50" s="94" t="n"/>
+      <c r="Q50" s="94" t="n"/>
+      <c r="R50" s="94" t="n"/>
+      <c r="S50" s="94" t="n"/>
+      <c r="T50" s="94" t="n"/>
+      <c r="U50" s="94" t="n"/>
+      <c r="V50" s="94" t="n"/>
+      <c r="W50" s="94" t="n"/>
+      <c r="X50" s="94" t="n"/>
+      <c r="Y50" s="94" t="n"/>
+      <c r="Z50" s="94" t="n"/>
       <c r="AA50" s="1" t="n"/>
       <c r="AB50" s="1" t="n"/>
       <c r="AC50" s="1" t="n"/>
@@ -5776,40 +6367,40 @@
       <c r="BG50" s="1" t="n"/>
     </row>
     <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="1" t="n"/>
-      <c r="B51" s="57" t="inlineStr">
+      <c r="A51" s="94" t="n"/>
+      <c r="B51" s="124" t="inlineStr">
         <is>
           <t>Vacation</t>
         </is>
       </c>
-      <c r="C51" s="21" t="n"/>
-      <c r="D51" s="58" t="n">
+      <c r="C51" s="140" t="n"/>
+      <c r="D51" s="126" t="n">
         <v>3270</v>
       </c>
-      <c r="E51" s="81" t="n">
+      <c r="E51" s="126" t="n">
         <v>1308</v>
       </c>
-      <c r="F51" s="33" t="n"/>
-      <c r="G51" s="1" t="n"/>
-      <c r="H51" s="1" t="n"/>
-      <c r="I51" s="1" t="n"/>
-      <c r="J51" s="1" t="n"/>
-      <c r="K51" s="1" t="n"/>
-      <c r="L51" s="1" t="n"/>
-      <c r="M51" s="1" t="n"/>
-      <c r="N51" s="1" t="n"/>
-      <c r="O51" s="1" t="n"/>
-      <c r="P51" s="1" t="n"/>
-      <c r="Q51" s="1" t="n"/>
-      <c r="R51" s="1" t="n"/>
-      <c r="S51" s="1" t="n"/>
-      <c r="T51" s="1" t="n"/>
-      <c r="U51" s="1" t="n"/>
-      <c r="V51" s="1" t="n"/>
-      <c r="W51" s="1" t="n"/>
-      <c r="X51" s="1" t="n"/>
-      <c r="Y51" s="1" t="n"/>
-      <c r="Z51" s="1" t="n"/>
+      <c r="F51" s="94" t="n"/>
+      <c r="G51" s="94" t="n"/>
+      <c r="H51" s="94" t="n"/>
+      <c r="I51" s="94" t="n"/>
+      <c r="J51" s="94" t="n"/>
+      <c r="K51" s="94" t="n"/>
+      <c r="L51" s="94" t="n"/>
+      <c r="M51" s="94" t="n"/>
+      <c r="N51" s="94" t="n"/>
+      <c r="O51" s="94" t="n"/>
+      <c r="P51" s="94" t="n"/>
+      <c r="Q51" s="94" t="n"/>
+      <c r="R51" s="94" t="n"/>
+      <c r="S51" s="94" t="n"/>
+      <c r="T51" s="94" t="n"/>
+      <c r="U51" s="94" t="n"/>
+      <c r="V51" s="94" t="n"/>
+      <c r="W51" s="94" t="n"/>
+      <c r="X51" s="94" t="n"/>
+      <c r="Y51" s="94" t="n"/>
+      <c r="Z51" s="94" t="n"/>
       <c r="AA51" s="1" t="n"/>
       <c r="AB51" s="1" t="n"/>
       <c r="AC51" s="1" t="n"/>
@@ -5845,40 +6436,40 @@
       <c r="BG51" s="1" t="n"/>
     </row>
     <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="1" t="n"/>
-      <c r="B52" s="48" t="inlineStr">
+      <c r="A52" s="94" t="n"/>
+      <c r="B52" s="131" t="inlineStr">
         <is>
           <t>Emergency</t>
         </is>
       </c>
-      <c r="C52" s="21" t="n"/>
-      <c r="D52" s="49" t="n">
+      <c r="C52" s="142" t="n"/>
+      <c r="D52" s="133" t="n">
         <v>1000</v>
       </c>
-      <c r="E52" s="80" t="n">
+      <c r="E52" s="133" t="n">
         <v>200</v>
       </c>
-      <c r="F52" s="29" t="n"/>
-      <c r="G52" s="1" t="n"/>
-      <c r="H52" s="1" t="n"/>
-      <c r="I52" s="1" t="n"/>
-      <c r="J52" s="1" t="n"/>
-      <c r="K52" s="1" t="n"/>
-      <c r="L52" s="1" t="n"/>
-      <c r="M52" s="1" t="n"/>
-      <c r="N52" s="1" t="n"/>
-      <c r="O52" s="1" t="n"/>
-      <c r="P52" s="1" t="n"/>
-      <c r="Q52" s="1" t="n"/>
-      <c r="R52" s="1" t="n"/>
-      <c r="S52" s="1" t="n"/>
-      <c r="T52" s="1" t="n"/>
-      <c r="U52" s="1" t="n"/>
-      <c r="V52" s="1" t="n"/>
-      <c r="W52" s="1" t="n"/>
-      <c r="X52" s="1" t="n"/>
-      <c r="Y52" s="1" t="n"/>
-      <c r="Z52" s="1" t="n"/>
+      <c r="F52" s="94" t="n"/>
+      <c r="G52" s="94" t="n"/>
+      <c r="H52" s="94" t="n"/>
+      <c r="I52" s="94" t="n"/>
+      <c r="J52" s="94" t="n"/>
+      <c r="K52" s="94" t="n"/>
+      <c r="L52" s="94" t="n"/>
+      <c r="M52" s="94" t="n"/>
+      <c r="N52" s="94" t="n"/>
+      <c r="O52" s="94" t="n"/>
+      <c r="P52" s="94" t="n"/>
+      <c r="Q52" s="94" t="n"/>
+      <c r="R52" s="94" t="n"/>
+      <c r="S52" s="94" t="n"/>
+      <c r="T52" s="94" t="n"/>
+      <c r="U52" s="94" t="n"/>
+      <c r="V52" s="94" t="n"/>
+      <c r="W52" s="94" t="n"/>
+      <c r="X52" s="94" t="n"/>
+      <c r="Y52" s="94" t="n"/>
+      <c r="Z52" s="94" t="n"/>
       <c r="AA52" s="1" t="n"/>
       <c r="AB52" s="1" t="n"/>
       <c r="AC52" s="1" t="n"/>
@@ -5914,36 +6505,36 @@
       <c r="BG52" s="1" t="n"/>
     </row>
     <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="1" t="n"/>
-      <c r="B53" s="57" t="inlineStr"/>
-      <c r="C53" s="21" t="n"/>
-      <c r="D53" s="58" t="n">
+      <c r="A53" s="94" t="n"/>
+      <c r="B53" s="124" t="inlineStr"/>
+      <c r="C53" s="140" t="n"/>
+      <c r="D53" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="81" t="n">
+      <c r="E53" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="33" t="n"/>
-      <c r="G53" s="1" t="n"/>
-      <c r="H53" s="1" t="n"/>
-      <c r="I53" s="1" t="n"/>
-      <c r="J53" s="1" t="n"/>
-      <c r="K53" s="1" t="n"/>
-      <c r="L53" s="1" t="n"/>
-      <c r="M53" s="1" t="n"/>
-      <c r="N53" s="1" t="n"/>
-      <c r="O53" s="1" t="n"/>
-      <c r="P53" s="1" t="n"/>
-      <c r="Q53" s="1" t="n"/>
-      <c r="R53" s="1" t="n"/>
-      <c r="S53" s="1" t="n"/>
-      <c r="T53" s="1" t="n"/>
-      <c r="U53" s="1" t="n"/>
-      <c r="V53" s="1" t="n"/>
-      <c r="W53" s="1" t="n"/>
-      <c r="X53" s="1" t="n"/>
-      <c r="Y53" s="1" t="n"/>
-      <c r="Z53" s="1" t="n"/>
+      <c r="F53" s="94" t="n"/>
+      <c r="G53" s="94" t="n"/>
+      <c r="H53" s="94" t="n"/>
+      <c r="I53" s="94" t="n"/>
+      <c r="J53" s="94" t="n"/>
+      <c r="K53" s="94" t="n"/>
+      <c r="L53" s="94" t="n"/>
+      <c r="M53" s="94" t="n"/>
+      <c r="N53" s="94" t="n"/>
+      <c r="O53" s="94" t="n"/>
+      <c r="P53" s="94" t="n"/>
+      <c r="Q53" s="94" t="n"/>
+      <c r="R53" s="94" t="n"/>
+      <c r="S53" s="94" t="n"/>
+      <c r="T53" s="94" t="n"/>
+      <c r="U53" s="94" t="n"/>
+      <c r="V53" s="94" t="n"/>
+      <c r="W53" s="94" t="n"/>
+      <c r="X53" s="94" t="n"/>
+      <c r="Y53" s="94" t="n"/>
+      <c r="Z53" s="94" t="n"/>
       <c r="AA53" s="1" t="n"/>
       <c r="AB53" s="1" t="n"/>
       <c r="AC53" s="1" t="n"/>
@@ -5979,36 +6570,36 @@
       <c r="BG53" s="1" t="n"/>
     </row>
     <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="1" t="n"/>
-      <c r="B54" s="48" t="inlineStr"/>
-      <c r="C54" s="21" t="n"/>
-      <c r="D54" s="49" t="n">
+      <c r="A54" s="94" t="n"/>
+      <c r="B54" s="131" t="inlineStr"/>
+      <c r="C54" s="142" t="n"/>
+      <c r="D54" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="80" t="n">
+      <c r="E54" s="133" t="n">
         <v>0</v>
       </c>
-      <c r="F54" s="29" t="n"/>
-      <c r="G54" s="1" t="n"/>
-      <c r="H54" s="1" t="n"/>
-      <c r="I54" s="1" t="n"/>
-      <c r="J54" s="1" t="n"/>
-      <c r="K54" s="1" t="n"/>
-      <c r="L54" s="1" t="n"/>
-      <c r="M54" s="1" t="n"/>
-      <c r="N54" s="1" t="n"/>
-      <c r="O54" s="1" t="n"/>
-      <c r="P54" s="1" t="n"/>
-      <c r="Q54" s="1" t="n"/>
-      <c r="R54" s="1" t="n"/>
-      <c r="S54" s="1" t="n"/>
-      <c r="T54" s="1" t="n"/>
-      <c r="U54" s="1" t="n"/>
-      <c r="V54" s="1" t="n"/>
-      <c r="W54" s="1" t="n"/>
-      <c r="X54" s="1" t="n"/>
-      <c r="Y54" s="1" t="n"/>
-      <c r="Z54" s="1" t="n"/>
+      <c r="F54" s="94" t="n"/>
+      <c r="G54" s="94" t="n"/>
+      <c r="H54" s="94" t="n"/>
+      <c r="I54" s="94" t="n"/>
+      <c r="J54" s="94" t="n"/>
+      <c r="K54" s="94" t="n"/>
+      <c r="L54" s="94" t="n"/>
+      <c r="M54" s="94" t="n"/>
+      <c r="N54" s="94" t="n"/>
+      <c r="O54" s="94" t="n"/>
+      <c r="P54" s="94" t="n"/>
+      <c r="Q54" s="94" t="n"/>
+      <c r="R54" s="94" t="n"/>
+      <c r="S54" s="94" t="n"/>
+      <c r="T54" s="94" t="n"/>
+      <c r="U54" s="94" t="n"/>
+      <c r="V54" s="94" t="n"/>
+      <c r="W54" s="94" t="n"/>
+      <c r="X54" s="94" t="n"/>
+      <c r="Y54" s="94" t="n"/>
+      <c r="Z54" s="94" t="n"/>
       <c r="AA54" s="1" t="n"/>
       <c r="AB54" s="1" t="n"/>
       <c r="AC54" s="1" t="n"/>
@@ -6044,36 +6635,36 @@
       <c r="BG54" s="1" t="n"/>
     </row>
     <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="1" t="n"/>
-      <c r="B55" s="57" t="inlineStr"/>
-      <c r="C55" s="21" t="n"/>
-      <c r="D55" s="58" t="n">
+      <c r="A55" s="94" t="n"/>
+      <c r="B55" s="124" t="inlineStr"/>
+      <c r="C55" s="140" t="n"/>
+      <c r="D55" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="E55" s="81" t="n">
+      <c r="E55" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="F55" s="33" t="n"/>
-      <c r="G55" s="1" t="n"/>
-      <c r="H55" s="1" t="n"/>
-      <c r="I55" s="1" t="n"/>
-      <c r="J55" s="1" t="n"/>
-      <c r="K55" s="1" t="n"/>
-      <c r="L55" s="1" t="n"/>
-      <c r="M55" s="1" t="n"/>
-      <c r="N55" s="1" t="n"/>
-      <c r="O55" s="1" t="n"/>
-      <c r="P55" s="1" t="n"/>
-      <c r="Q55" s="1" t="n"/>
-      <c r="R55" s="1" t="n"/>
-      <c r="S55" s="1" t="n"/>
-      <c r="T55" s="1" t="n"/>
-      <c r="U55" s="1" t="n"/>
-      <c r="V55" s="1" t="n"/>
-      <c r="W55" s="1" t="n"/>
-      <c r="X55" s="1" t="n"/>
-      <c r="Y55" s="1" t="n"/>
-      <c r="Z55" s="1" t="n"/>
+      <c r="F55" s="94" t="n"/>
+      <c r="G55" s="94" t="n"/>
+      <c r="H55" s="94" t="n"/>
+      <c r="I55" s="94" t="n"/>
+      <c r="J55" s="94" t="n"/>
+      <c r="K55" s="94" t="n"/>
+      <c r="L55" s="94" t="n"/>
+      <c r="M55" s="94" t="n"/>
+      <c r="N55" s="94" t="n"/>
+      <c r="O55" s="94" t="n"/>
+      <c r="P55" s="94" t="n"/>
+      <c r="Q55" s="94" t="n"/>
+      <c r="R55" s="94" t="n"/>
+      <c r="S55" s="94" t="n"/>
+      <c r="T55" s="94" t="n"/>
+      <c r="U55" s="94" t="n"/>
+      <c r="V55" s="94" t="n"/>
+      <c r="W55" s="94" t="n"/>
+      <c r="X55" s="94" t="n"/>
+      <c r="Y55" s="94" t="n"/>
+      <c r="Z55" s="94" t="n"/>
       <c r="AA55" s="1" t="n"/>
       <c r="AB55" s="1" t="n"/>
       <c r="AC55" s="1" t="n"/>
@@ -6108,41 +6699,41 @@
       <c r="BF55" s="1" t="n"/>
       <c r="BG55" s="1" t="n"/>
     </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="1" t="n"/>
-      <c r="B56" s="82" t="inlineStr">
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="94" t="n"/>
+      <c r="B56" s="145" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C56" s="38" t="n"/>
-      <c r="D56" s="72" t="n">
+      <c r="C56" s="145" t="n"/>
+      <c r="D56" s="146" t="n">
         <v>6668</v>
       </c>
-      <c r="E56" s="83" t="n">
+      <c r="E56" s="146" t="n">
         <v>2490</v>
       </c>
-      <c r="F56" s="41" t="n"/>
-      <c r="G56" s="1" t="n"/>
-      <c r="H56" s="1" t="n"/>
-      <c r="I56" s="1" t="n"/>
-      <c r="J56" s="1" t="n"/>
-      <c r="K56" s="1" t="n"/>
-      <c r="L56" s="1" t="n"/>
-      <c r="M56" s="1" t="n"/>
-      <c r="N56" s="1" t="n"/>
-      <c r="O56" s="1" t="n"/>
-      <c r="P56" s="1" t="n"/>
-      <c r="Q56" s="1" t="n"/>
-      <c r="R56" s="1" t="n"/>
-      <c r="S56" s="1" t="n"/>
-      <c r="T56" s="1" t="n"/>
-      <c r="U56" s="1" t="n"/>
-      <c r="V56" s="1" t="n"/>
-      <c r="W56" s="1" t="n"/>
-      <c r="X56" s="1" t="n"/>
-      <c r="Y56" s="1" t="n"/>
-      <c r="Z56" s="1" t="n"/>
+      <c r="F56" s="94" t="n"/>
+      <c r="G56" s="94" t="n"/>
+      <c r="H56" s="94" t="n"/>
+      <c r="I56" s="94" t="n"/>
+      <c r="J56" s="94" t="n"/>
+      <c r="K56" s="94" t="n"/>
+      <c r="L56" s="94" t="n"/>
+      <c r="M56" s="94" t="n"/>
+      <c r="N56" s="94" t="n"/>
+      <c r="O56" s="94" t="n"/>
+      <c r="P56" s="94" t="n"/>
+      <c r="Q56" s="94" t="n"/>
+      <c r="R56" s="94" t="n"/>
+      <c r="S56" s="94" t="n"/>
+      <c r="T56" s="94" t="n"/>
+      <c r="U56" s="94" t="n"/>
+      <c r="V56" s="94" t="n"/>
+      <c r="W56" s="94" t="n"/>
+      <c r="X56" s="94" t="n"/>
+      <c r="Y56" s="94" t="n"/>
+      <c r="Z56" s="94" t="n"/>
       <c r="AA56" s="1" t="n"/>
       <c r="AB56" s="1" t="n"/>
       <c r="AC56" s="1" t="n"/>
@@ -6178,32 +6769,32 @@
       <c r="BG56" s="1" t="n"/>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="1" t="n"/>
-      <c r="B57" s="1" t="n"/>
-      <c r="C57" s="1" t="n"/>
-      <c r="D57" s="1" t="n"/>
-      <c r="E57" s="1" t="n"/>
-      <c r="F57" s="1" t="n"/>
-      <c r="G57" s="1" t="n"/>
-      <c r="H57" s="1" t="n"/>
-      <c r="I57" s="1" t="n"/>
-      <c r="J57" s="1" t="n"/>
-      <c r="K57" s="1" t="n"/>
-      <c r="L57" s="1" t="n"/>
-      <c r="M57" s="1" t="n"/>
-      <c r="N57" s="1" t="n"/>
-      <c r="O57" s="1" t="n"/>
-      <c r="P57" s="1" t="n"/>
-      <c r="Q57" s="1" t="n"/>
-      <c r="R57" s="1" t="n"/>
-      <c r="S57" s="1" t="n"/>
-      <c r="T57" s="1" t="n"/>
-      <c r="U57" s="1" t="n"/>
-      <c r="V57" s="1" t="n"/>
-      <c r="W57" s="1" t="n"/>
-      <c r="X57" s="1" t="n"/>
-      <c r="Y57" s="1" t="n"/>
-      <c r="Z57" s="1" t="n"/>
+      <c r="A57" s="94" t="n"/>
+      <c r="B57" s="94" t="n"/>
+      <c r="C57" s="94" t="n"/>
+      <c r="D57" s="94" t="n"/>
+      <c r="E57" s="94" t="n"/>
+      <c r="F57" s="94" t="n"/>
+      <c r="G57" s="94" t="n"/>
+      <c r="H57" s="94" t="n"/>
+      <c r="I57" s="94" t="n"/>
+      <c r="J57" s="94" t="n"/>
+      <c r="K57" s="94" t="n"/>
+      <c r="L57" s="94" t="n"/>
+      <c r="M57" s="94" t="n"/>
+      <c r="N57" s="94" t="n"/>
+      <c r="O57" s="94" t="n"/>
+      <c r="P57" s="94" t="n"/>
+      <c r="Q57" s="94" t="n"/>
+      <c r="R57" s="94" t="n"/>
+      <c r="S57" s="94" t="n"/>
+      <c r="T57" s="94" t="n"/>
+      <c r="U57" s="94" t="n"/>
+      <c r="V57" s="94" t="n"/>
+      <c r="W57" s="94" t="n"/>
+      <c r="X57" s="94" t="n"/>
+      <c r="Y57" s="94" t="n"/>
+      <c r="Z57" s="94" t="n"/>
       <c r="AA57" s="1" t="n"/>
       <c r="AB57" s="1" t="n"/>
       <c r="AC57" s="1" t="n"/>
@@ -6239,32 +6830,32 @@
       <c r="BG57" s="1" t="n"/>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="1" t="n"/>
-      <c r="B58" s="1" t="n"/>
-      <c r="C58" s="1" t="n"/>
-      <c r="D58" s="1" t="n"/>
-      <c r="E58" s="1" t="n"/>
-      <c r="F58" s="1" t="n"/>
-      <c r="G58" s="1" t="n"/>
-      <c r="H58" s="1" t="n"/>
-      <c r="I58" s="1" t="n"/>
-      <c r="J58" s="1" t="n"/>
-      <c r="K58" s="1" t="n"/>
-      <c r="L58" s="1" t="n"/>
-      <c r="M58" s="1" t="n"/>
-      <c r="N58" s="1" t="n"/>
-      <c r="O58" s="1" t="n"/>
-      <c r="P58" s="1" t="n"/>
-      <c r="Q58" s="1" t="n"/>
-      <c r="R58" s="1" t="n"/>
-      <c r="S58" s="1" t="n"/>
-      <c r="T58" s="1" t="n"/>
-      <c r="U58" s="1" t="n"/>
-      <c r="V58" s="1" t="n"/>
-      <c r="W58" s="1" t="n"/>
-      <c r="X58" s="1" t="n"/>
-      <c r="Y58" s="1" t="n"/>
-      <c r="Z58" s="1" t="n"/>
+      <c r="A58" s="94" t="n"/>
+      <c r="B58" s="94" t="n"/>
+      <c r="C58" s="94" t="n"/>
+      <c r="D58" s="94" t="n"/>
+      <c r="E58" s="94" t="n"/>
+      <c r="F58" s="94" t="n"/>
+      <c r="G58" s="94" t="n"/>
+      <c r="H58" s="94" t="n"/>
+      <c r="I58" s="94" t="n"/>
+      <c r="J58" s="94" t="n"/>
+      <c r="K58" s="94" t="n"/>
+      <c r="L58" s="94" t="n"/>
+      <c r="M58" s="94" t="n"/>
+      <c r="N58" s="94" t="n"/>
+      <c r="O58" s="94" t="n"/>
+      <c r="P58" s="94" t="n"/>
+      <c r="Q58" s="94" t="n"/>
+      <c r="R58" s="94" t="n"/>
+      <c r="S58" s="94" t="n"/>
+      <c r="T58" s="94" t="n"/>
+      <c r="U58" s="94" t="n"/>
+      <c r="V58" s="94" t="n"/>
+      <c r="W58" s="94" t="n"/>
+      <c r="X58" s="94" t="n"/>
+      <c r="Y58" s="94" t="n"/>
+      <c r="Z58" s="94" t="n"/>
       <c r="AA58" s="1" t="n"/>
       <c r="AB58" s="1" t="n"/>
       <c r="AC58" s="1" t="n"/>
@@ -6300,32 +6891,32 @@
       <c r="BG58" s="1" t="n"/>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="1" t="n"/>
-      <c r="B59" s="1" t="n"/>
-      <c r="C59" s="1" t="n"/>
-      <c r="D59" s="1" t="n"/>
-      <c r="E59" s="1" t="n"/>
-      <c r="F59" s="1" t="n"/>
-      <c r="G59" s="1" t="n"/>
-      <c r="H59" s="1" t="n"/>
-      <c r="I59" s="1" t="n"/>
-      <c r="J59" s="1" t="n"/>
-      <c r="K59" s="1" t="n"/>
-      <c r="L59" s="1" t="n"/>
-      <c r="M59" s="1" t="n"/>
-      <c r="N59" s="1" t="n"/>
-      <c r="O59" s="1" t="n"/>
-      <c r="P59" s="1" t="n"/>
-      <c r="Q59" s="1" t="n"/>
-      <c r="R59" s="1" t="n"/>
-      <c r="S59" s="1" t="n"/>
-      <c r="T59" s="1" t="n"/>
-      <c r="U59" s="1" t="n"/>
-      <c r="V59" s="1" t="n"/>
-      <c r="W59" s="1" t="n"/>
-      <c r="X59" s="1" t="n"/>
-      <c r="Y59" s="1" t="n"/>
-      <c r="Z59" s="1" t="n"/>
+      <c r="A59" s="94" t="n"/>
+      <c r="B59" s="94" t="n"/>
+      <c r="C59" s="94" t="n"/>
+      <c r="D59" s="94" t="n"/>
+      <c r="E59" s="94" t="n"/>
+      <c r="F59" s="94" t="n"/>
+      <c r="G59" s="94" t="n"/>
+      <c r="H59" s="94" t="n"/>
+      <c r="I59" s="94" t="n"/>
+      <c r="J59" s="94" t="n"/>
+      <c r="K59" s="94" t="n"/>
+      <c r="L59" s="94" t="n"/>
+      <c r="M59" s="94" t="n"/>
+      <c r="N59" s="94" t="n"/>
+      <c r="O59" s="94" t="n"/>
+      <c r="P59" s="94" t="n"/>
+      <c r="Q59" s="94" t="n"/>
+      <c r="R59" s="94" t="n"/>
+      <c r="S59" s="94" t="n"/>
+      <c r="T59" s="94" t="n"/>
+      <c r="U59" s="94" t="n"/>
+      <c r="V59" s="94" t="n"/>
+      <c r="W59" s="94" t="n"/>
+      <c r="X59" s="94" t="n"/>
+      <c r="Y59" s="94" t="n"/>
+      <c r="Z59" s="94" t="n"/>
       <c r="AA59" s="1" t="n"/>
       <c r="AB59" s="1" t="n"/>
       <c r="AC59" s="1" t="n"/>
@@ -6361,32 +6952,32 @@
       <c r="BG59" s="1" t="n"/>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="1" t="n"/>
-      <c r="B60" s="1" t="n"/>
-      <c r="C60" s="1" t="n"/>
-      <c r="D60" s="1" t="n"/>
-      <c r="E60" s="1" t="n"/>
-      <c r="F60" s="1" t="n"/>
-      <c r="G60" s="1" t="n"/>
-      <c r="H60" s="1" t="n"/>
-      <c r="I60" s="1" t="n"/>
-      <c r="J60" s="1" t="n"/>
-      <c r="K60" s="1" t="n"/>
-      <c r="L60" s="1" t="n"/>
-      <c r="M60" s="1" t="n"/>
-      <c r="N60" s="1" t="n"/>
-      <c r="O60" s="1" t="n"/>
-      <c r="P60" s="1" t="n"/>
-      <c r="Q60" s="1" t="n"/>
-      <c r="R60" s="1" t="n"/>
-      <c r="S60" s="1" t="n"/>
-      <c r="T60" s="1" t="n"/>
-      <c r="U60" s="1" t="n"/>
-      <c r="V60" s="1" t="n"/>
-      <c r="W60" s="1" t="n"/>
-      <c r="X60" s="1" t="n"/>
-      <c r="Y60" s="1" t="n"/>
-      <c r="Z60" s="1" t="n"/>
+      <c r="A60" s="94" t="n"/>
+      <c r="B60" s="94" t="n"/>
+      <c r="C60" s="94" t="n"/>
+      <c r="D60" s="94" t="n"/>
+      <c r="E60" s="94" t="n"/>
+      <c r="F60" s="94" t="n"/>
+      <c r="G60" s="94" t="n"/>
+      <c r="H60" s="94" t="n"/>
+      <c r="I60" s="94" t="n"/>
+      <c r="J60" s="94" t="n"/>
+      <c r="K60" s="94" t="n"/>
+      <c r="L60" s="94" t="n"/>
+      <c r="M60" s="94" t="n"/>
+      <c r="N60" s="94" t="n"/>
+      <c r="O60" s="94" t="n"/>
+      <c r="P60" s="94" t="n"/>
+      <c r="Q60" s="94" t="n"/>
+      <c r="R60" s="94" t="n"/>
+      <c r="S60" s="94" t="n"/>
+      <c r="T60" s="94" t="n"/>
+      <c r="U60" s="94" t="n"/>
+      <c r="V60" s="94" t="n"/>
+      <c r="W60" s="94" t="n"/>
+      <c r="X60" s="94" t="n"/>
+      <c r="Y60" s="94" t="n"/>
+      <c r="Z60" s="94" t="n"/>
       <c r="AA60" s="1" t="n"/>
       <c r="AB60" s="1" t="n"/>
       <c r="AC60" s="1" t="n"/>
@@ -6422,32 +7013,32 @@
       <c r="BG60" s="1" t="n"/>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="1" t="n"/>
-      <c r="B61" s="1" t="n"/>
-      <c r="C61" s="1" t="n"/>
-      <c r="D61" s="1" t="n"/>
-      <c r="E61" s="1" t="n"/>
-      <c r="F61" s="1" t="n"/>
-      <c r="G61" s="1" t="n"/>
-      <c r="H61" s="1" t="n"/>
-      <c r="I61" s="1" t="n"/>
-      <c r="J61" s="1" t="n"/>
-      <c r="K61" s="1" t="n"/>
-      <c r="L61" s="1" t="n"/>
-      <c r="M61" s="1" t="n"/>
-      <c r="N61" s="1" t="n"/>
-      <c r="O61" s="1" t="n"/>
-      <c r="P61" s="1" t="n"/>
-      <c r="Q61" s="1" t="n"/>
-      <c r="R61" s="1" t="n"/>
-      <c r="S61" s="1" t="n"/>
-      <c r="T61" s="1" t="n"/>
-      <c r="U61" s="1" t="n"/>
-      <c r="V61" s="1" t="n"/>
-      <c r="W61" s="1" t="n"/>
-      <c r="X61" s="1" t="n"/>
-      <c r="Y61" s="1" t="n"/>
-      <c r="Z61" s="1" t="n"/>
+      <c r="A61" s="94" t="n"/>
+      <c r="B61" s="94" t="n"/>
+      <c r="C61" s="94" t="n"/>
+      <c r="D61" s="94" t="n"/>
+      <c r="E61" s="94" t="n"/>
+      <c r="F61" s="94" t="n"/>
+      <c r="G61" s="94" t="n"/>
+      <c r="H61" s="94" t="n"/>
+      <c r="I61" s="94" t="n"/>
+      <c r="J61" s="94" t="n"/>
+      <c r="K61" s="94" t="n"/>
+      <c r="L61" s="94" t="n"/>
+      <c r="M61" s="94" t="n"/>
+      <c r="N61" s="94" t="n"/>
+      <c r="O61" s="94" t="n"/>
+      <c r="P61" s="94" t="n"/>
+      <c r="Q61" s="94" t="n"/>
+      <c r="R61" s="94" t="n"/>
+      <c r="S61" s="94" t="n"/>
+      <c r="T61" s="94" t="n"/>
+      <c r="U61" s="94" t="n"/>
+      <c r="V61" s="94" t="n"/>
+      <c r="W61" s="94" t="n"/>
+      <c r="X61" s="94" t="n"/>
+      <c r="Y61" s="94" t="n"/>
+      <c r="Z61" s="94" t="n"/>
       <c r="AA61" s="1" t="n"/>
       <c r="AB61" s="1" t="n"/>
       <c r="AC61" s="1" t="n"/>
@@ -6483,32 +7074,32 @@
       <c r="BG61" s="1" t="n"/>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="1" t="n"/>
-      <c r="B62" s="1" t="n"/>
-      <c r="C62" s="1" t="n"/>
-      <c r="D62" s="1" t="n"/>
-      <c r="E62" s="1" t="n"/>
-      <c r="F62" s="1" t="n"/>
-      <c r="G62" s="1" t="n"/>
-      <c r="H62" s="1" t="n"/>
-      <c r="I62" s="1" t="n"/>
-      <c r="J62" s="1" t="n"/>
-      <c r="K62" s="1" t="n"/>
-      <c r="L62" s="1" t="n"/>
-      <c r="M62" s="1" t="n"/>
-      <c r="N62" s="1" t="n"/>
-      <c r="O62" s="1" t="n"/>
-      <c r="P62" s="1" t="n"/>
-      <c r="Q62" s="1" t="n"/>
-      <c r="R62" s="1" t="n"/>
-      <c r="S62" s="1" t="n"/>
-      <c r="T62" s="1" t="n"/>
-      <c r="U62" s="1" t="n"/>
-      <c r="V62" s="1" t="n"/>
-      <c r="W62" s="1" t="n"/>
-      <c r="X62" s="1" t="n"/>
-      <c r="Y62" s="1" t="n"/>
-      <c r="Z62" s="1" t="n"/>
+      <c r="A62" s="94" t="n"/>
+      <c r="B62" s="94" t="n"/>
+      <c r="C62" s="94" t="n"/>
+      <c r="D62" s="94" t="n"/>
+      <c r="E62" s="94" t="n"/>
+      <c r="F62" s="94" t="n"/>
+      <c r="G62" s="94" t="n"/>
+      <c r="H62" s="94" t="n"/>
+      <c r="I62" s="94" t="n"/>
+      <c r="J62" s="94" t="n"/>
+      <c r="K62" s="94" t="n"/>
+      <c r="L62" s="94" t="n"/>
+      <c r="M62" s="94" t="n"/>
+      <c r="N62" s="94" t="n"/>
+      <c r="O62" s="94" t="n"/>
+      <c r="P62" s="94" t="n"/>
+      <c r="Q62" s="94" t="n"/>
+      <c r="R62" s="94" t="n"/>
+      <c r="S62" s="94" t="n"/>
+      <c r="T62" s="94" t="n"/>
+      <c r="U62" s="94" t="n"/>
+      <c r="V62" s="94" t="n"/>
+      <c r="W62" s="94" t="n"/>
+      <c r="X62" s="94" t="n"/>
+      <c r="Y62" s="94" t="n"/>
+      <c r="Z62" s="94" t="n"/>
       <c r="AA62" s="1" t="n"/>
       <c r="AB62" s="1" t="n"/>
       <c r="AC62" s="1" t="n"/>
@@ -6544,32 +7135,32 @@
       <c r="BG62" s="1" t="n"/>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="1" t="n"/>
-      <c r="B63" s="1" t="n"/>
-      <c r="C63" s="1" t="n"/>
-      <c r="D63" s="1" t="n"/>
-      <c r="E63" s="1" t="n"/>
-      <c r="F63" s="1" t="n"/>
-      <c r="G63" s="1" t="n"/>
-      <c r="H63" s="1" t="n"/>
-      <c r="I63" s="1" t="n"/>
-      <c r="J63" s="1" t="n"/>
-      <c r="K63" s="1" t="n"/>
-      <c r="L63" s="1" t="n"/>
-      <c r="M63" s="1" t="n"/>
-      <c r="N63" s="1" t="n"/>
-      <c r="O63" s="1" t="n"/>
-      <c r="P63" s="1" t="n"/>
-      <c r="Q63" s="1" t="n"/>
-      <c r="R63" s="1" t="n"/>
-      <c r="S63" s="1" t="n"/>
-      <c r="T63" s="1" t="n"/>
-      <c r="U63" s="1" t="n"/>
-      <c r="V63" s="1" t="n"/>
-      <c r="W63" s="1" t="n"/>
-      <c r="X63" s="1" t="n"/>
-      <c r="Y63" s="1" t="n"/>
-      <c r="Z63" s="1" t="n"/>
+      <c r="A63" s="94" t="n"/>
+      <c r="B63" s="94" t="n"/>
+      <c r="C63" s="94" t="n"/>
+      <c r="D63" s="94" t="n"/>
+      <c r="E63" s="94" t="n"/>
+      <c r="F63" s="94" t="n"/>
+      <c r="G63" s="94" t="n"/>
+      <c r="H63" s="94" t="n"/>
+      <c r="I63" s="94" t="n"/>
+      <c r="J63" s="94" t="n"/>
+      <c r="K63" s="94" t="n"/>
+      <c r="L63" s="94" t="n"/>
+      <c r="M63" s="94" t="n"/>
+      <c r="N63" s="94" t="n"/>
+      <c r="O63" s="94" t="n"/>
+      <c r="P63" s="94" t="n"/>
+      <c r="Q63" s="94" t="n"/>
+      <c r="R63" s="94" t="n"/>
+      <c r="S63" s="94" t="n"/>
+      <c r="T63" s="94" t="n"/>
+      <c r="U63" s="94" t="n"/>
+      <c r="V63" s="94" t="n"/>
+      <c r="W63" s="94" t="n"/>
+      <c r="X63" s="94" t="n"/>
+      <c r="Y63" s="94" t="n"/>
+      <c r="Z63" s="94" t="n"/>
       <c r="AA63" s="1" t="n"/>
       <c r="AB63" s="1" t="n"/>
       <c r="AC63" s="1" t="n"/>
@@ -6605,32 +7196,32 @@
       <c r="BG63" s="1" t="n"/>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="1" t="n"/>
-      <c r="B64" s="1" t="n"/>
-      <c r="C64" s="1" t="n"/>
-      <c r="D64" s="1" t="n"/>
-      <c r="E64" s="1" t="n"/>
-      <c r="F64" s="1" t="n"/>
-      <c r="G64" s="1" t="n"/>
-      <c r="H64" s="1" t="n"/>
-      <c r="I64" s="1" t="n"/>
-      <c r="J64" s="1" t="n"/>
-      <c r="K64" s="1" t="n"/>
-      <c r="L64" s="1" t="n"/>
-      <c r="M64" s="1" t="n"/>
-      <c r="N64" s="1" t="n"/>
-      <c r="O64" s="1" t="n"/>
-      <c r="P64" s="1" t="n"/>
-      <c r="Q64" s="1" t="n"/>
-      <c r="R64" s="1" t="n"/>
-      <c r="S64" s="1" t="n"/>
-      <c r="T64" s="1" t="n"/>
-      <c r="U64" s="1" t="n"/>
-      <c r="V64" s="1" t="n"/>
-      <c r="W64" s="1" t="n"/>
-      <c r="X64" s="1" t="n"/>
-      <c r="Y64" s="1" t="n"/>
-      <c r="Z64" s="1" t="n"/>
+      <c r="A64" s="94" t="n"/>
+      <c r="B64" s="94" t="n"/>
+      <c r="C64" s="94" t="n"/>
+      <c r="D64" s="94" t="n"/>
+      <c r="E64" s="94" t="n"/>
+      <c r="F64" s="94" t="n"/>
+      <c r="G64" s="94" t="n"/>
+      <c r="H64" s="94" t="n"/>
+      <c r="I64" s="94" t="n"/>
+      <c r="J64" s="94" t="n"/>
+      <c r="K64" s="94" t="n"/>
+      <c r="L64" s="94" t="n"/>
+      <c r="M64" s="94" t="n"/>
+      <c r="N64" s="94" t="n"/>
+      <c r="O64" s="94" t="n"/>
+      <c r="P64" s="94" t="n"/>
+      <c r="Q64" s="94" t="n"/>
+      <c r="R64" s="94" t="n"/>
+      <c r="S64" s="94" t="n"/>
+      <c r="T64" s="94" t="n"/>
+      <c r="U64" s="94" t="n"/>
+      <c r="V64" s="94" t="n"/>
+      <c r="W64" s="94" t="n"/>
+      <c r="X64" s="94" t="n"/>
+      <c r="Y64" s="94" t="n"/>
+      <c r="Z64" s="94" t="n"/>
       <c r="AA64" s="1" t="n"/>
       <c r="AB64" s="1" t="n"/>
       <c r="AC64" s="1" t="n"/>
@@ -6666,32 +7257,32 @@
       <c r="BG64" s="1" t="n"/>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="1" t="n"/>
-      <c r="B65" s="1" t="n"/>
-      <c r="C65" s="1" t="n"/>
-      <c r="D65" s="1" t="n"/>
-      <c r="E65" s="1" t="n"/>
-      <c r="F65" s="1" t="n"/>
-      <c r="G65" s="1" t="n"/>
-      <c r="H65" s="1" t="n"/>
-      <c r="I65" s="1" t="n"/>
-      <c r="J65" s="1" t="n"/>
-      <c r="K65" s="1" t="n"/>
-      <c r="L65" s="1" t="n"/>
-      <c r="M65" s="1" t="n"/>
-      <c r="N65" s="1" t="n"/>
-      <c r="O65" s="1" t="n"/>
-      <c r="P65" s="1" t="n"/>
-      <c r="Q65" s="1" t="n"/>
-      <c r="R65" s="1" t="n"/>
-      <c r="S65" s="1" t="n"/>
-      <c r="T65" s="1" t="n"/>
-      <c r="U65" s="1" t="n"/>
-      <c r="V65" s="1" t="n"/>
-      <c r="W65" s="1" t="n"/>
-      <c r="X65" s="1" t="n"/>
-      <c r="Y65" s="1" t="n"/>
-      <c r="Z65" s="1" t="n"/>
+      <c r="A65" s="94" t="n"/>
+      <c r="B65" s="94" t="n"/>
+      <c r="C65" s="94" t="n"/>
+      <c r="D65" s="94" t="n"/>
+      <c r="E65" s="94" t="n"/>
+      <c r="F65" s="94" t="n"/>
+      <c r="G65" s="94" t="n"/>
+      <c r="H65" s="94" t="n"/>
+      <c r="I65" s="94" t="n"/>
+      <c r="J65" s="94" t="n"/>
+      <c r="K65" s="94" t="n"/>
+      <c r="L65" s="94" t="n"/>
+      <c r="M65" s="94" t="n"/>
+      <c r="N65" s="94" t="n"/>
+      <c r="O65" s="94" t="n"/>
+      <c r="P65" s="94" t="n"/>
+      <c r="Q65" s="94" t="n"/>
+      <c r="R65" s="94" t="n"/>
+      <c r="S65" s="94" t="n"/>
+      <c r="T65" s="94" t="n"/>
+      <c r="U65" s="94" t="n"/>
+      <c r="V65" s="94" t="n"/>
+      <c r="W65" s="94" t="n"/>
+      <c r="X65" s="94" t="n"/>
+      <c r="Y65" s="94" t="n"/>
+      <c r="Z65" s="94" t="n"/>
       <c r="AA65" s="1" t="n"/>
       <c r="AB65" s="1" t="n"/>
       <c r="AC65" s="1" t="n"/>
@@ -6727,32 +7318,32 @@
       <c r="BG65" s="1" t="n"/>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="1" t="n"/>
-      <c r="B66" s="1" t="n"/>
-      <c r="C66" s="1" t="n"/>
-      <c r="D66" s="1" t="n"/>
-      <c r="E66" s="1" t="n"/>
-      <c r="F66" s="1" t="n"/>
-      <c r="G66" s="1" t="n"/>
-      <c r="H66" s="1" t="n"/>
-      <c r="I66" s="1" t="n"/>
-      <c r="J66" s="1" t="n"/>
-      <c r="K66" s="1" t="n"/>
-      <c r="L66" s="1" t="n"/>
-      <c r="M66" s="1" t="n"/>
-      <c r="N66" s="1" t="n"/>
-      <c r="O66" s="1" t="n"/>
-      <c r="P66" s="1" t="n"/>
-      <c r="Q66" s="1" t="n"/>
-      <c r="R66" s="1" t="n"/>
-      <c r="S66" s="1" t="n"/>
-      <c r="T66" s="1" t="n"/>
-      <c r="U66" s="1" t="n"/>
-      <c r="V66" s="1" t="n"/>
-      <c r="W66" s="1" t="n"/>
-      <c r="X66" s="1" t="n"/>
-      <c r="Y66" s="1" t="n"/>
-      <c r="Z66" s="1" t="n"/>
+      <c r="A66" s="94" t="n"/>
+      <c r="B66" s="94" t="n"/>
+      <c r="C66" s="94" t="n"/>
+      <c r="D66" s="94" t="n"/>
+      <c r="E66" s="94" t="n"/>
+      <c r="F66" s="94" t="n"/>
+      <c r="G66" s="94" t="n"/>
+      <c r="H66" s="94" t="n"/>
+      <c r="I66" s="94" t="n"/>
+      <c r="J66" s="94" t="n"/>
+      <c r="K66" s="94" t="n"/>
+      <c r="L66" s="94" t="n"/>
+      <c r="M66" s="94" t="n"/>
+      <c r="N66" s="94" t="n"/>
+      <c r="O66" s="94" t="n"/>
+      <c r="P66" s="94" t="n"/>
+      <c r="Q66" s="94" t="n"/>
+      <c r="R66" s="94" t="n"/>
+      <c r="S66" s="94" t="n"/>
+      <c r="T66" s="94" t="n"/>
+      <c r="U66" s="94" t="n"/>
+      <c r="V66" s="94" t="n"/>
+      <c r="W66" s="94" t="n"/>
+      <c r="X66" s="94" t="n"/>
+      <c r="Y66" s="94" t="n"/>
+      <c r="Z66" s="94" t="n"/>
       <c r="AA66" s="1" t="n"/>
       <c r="AB66" s="1" t="n"/>
       <c r="AC66" s="1" t="n"/>
@@ -6788,32 +7379,32 @@
       <c r="BG66" s="1" t="n"/>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="1" t="n"/>
-      <c r="B67" s="1" t="n"/>
-      <c r="C67" s="1" t="n"/>
-      <c r="D67" s="1" t="n"/>
-      <c r="E67" s="1" t="n"/>
-      <c r="F67" s="1" t="n"/>
-      <c r="G67" s="1" t="n"/>
-      <c r="H67" s="1" t="n"/>
-      <c r="I67" s="1" t="n"/>
-      <c r="J67" s="1" t="n"/>
-      <c r="K67" s="1" t="n"/>
-      <c r="L67" s="1" t="n"/>
-      <c r="M67" s="1" t="n"/>
-      <c r="N67" s="1" t="n"/>
-      <c r="O67" s="1" t="n"/>
-      <c r="P67" s="1" t="n"/>
-      <c r="Q67" s="1" t="n"/>
-      <c r="R67" s="1" t="n"/>
-      <c r="S67" s="1" t="n"/>
-      <c r="T67" s="1" t="n"/>
-      <c r="U67" s="1" t="n"/>
-      <c r="V67" s="1" t="n"/>
-      <c r="W67" s="1" t="n"/>
-      <c r="X67" s="1" t="n"/>
-      <c r="Y67" s="1" t="n"/>
-      <c r="Z67" s="1" t="n"/>
+      <c r="A67" s="94" t="n"/>
+      <c r="B67" s="94" t="n"/>
+      <c r="C67" s="94" t="n"/>
+      <c r="D67" s="94" t="n"/>
+      <c r="E67" s="94" t="n"/>
+      <c r="F67" s="94" t="n"/>
+      <c r="G67" s="94" t="n"/>
+      <c r="H67" s="94" t="n"/>
+      <c r="I67" s="94" t="n"/>
+      <c r="J67" s="94" t="n"/>
+      <c r="K67" s="94" t="n"/>
+      <c r="L67" s="94" t="n"/>
+      <c r="M67" s="94" t="n"/>
+      <c r="N67" s="94" t="n"/>
+      <c r="O67" s="94" t="n"/>
+      <c r="P67" s="94" t="n"/>
+      <c r="Q67" s="94" t="n"/>
+      <c r="R67" s="94" t="n"/>
+      <c r="S67" s="94" t="n"/>
+      <c r="T67" s="94" t="n"/>
+      <c r="U67" s="94" t="n"/>
+      <c r="V67" s="94" t="n"/>
+      <c r="W67" s="94" t="n"/>
+      <c r="X67" s="94" t="n"/>
+      <c r="Y67" s="94" t="n"/>
+      <c r="Z67" s="94" t="n"/>
       <c r="AA67" s="1" t="n"/>
       <c r="AB67" s="1" t="n"/>
       <c r="AC67" s="1" t="n"/>
@@ -6849,32 +7440,32 @@
       <c r="BG67" s="1" t="n"/>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="1" t="n"/>
-      <c r="B68" s="1" t="n"/>
-      <c r="C68" s="1" t="n"/>
-      <c r="D68" s="1" t="n"/>
-      <c r="E68" s="1" t="n"/>
-      <c r="F68" s="1" t="n"/>
-      <c r="G68" s="1" t="n"/>
-      <c r="H68" s="1" t="n"/>
-      <c r="I68" s="1" t="n"/>
-      <c r="J68" s="1" t="n"/>
-      <c r="K68" s="1" t="n"/>
-      <c r="L68" s="1" t="n"/>
-      <c r="M68" s="1" t="n"/>
-      <c r="N68" s="1" t="n"/>
-      <c r="O68" s="1" t="n"/>
-      <c r="P68" s="1" t="n"/>
-      <c r="Q68" s="1" t="n"/>
-      <c r="R68" s="1" t="n"/>
-      <c r="S68" s="1" t="n"/>
-      <c r="T68" s="1" t="n"/>
-      <c r="U68" s="1" t="n"/>
-      <c r="V68" s="1" t="n"/>
-      <c r="W68" s="1" t="n"/>
-      <c r="X68" s="1" t="n"/>
-      <c r="Y68" s="1" t="n"/>
-      <c r="Z68" s="1" t="n"/>
+      <c r="A68" s="94" t="n"/>
+      <c r="B68" s="94" t="n"/>
+      <c r="C68" s="94" t="n"/>
+      <c r="D68" s="94" t="n"/>
+      <c r="E68" s="94" t="n"/>
+      <c r="F68" s="94" t="n"/>
+      <c r="G68" s="94" t="n"/>
+      <c r="H68" s="94" t="n"/>
+      <c r="I68" s="94" t="n"/>
+      <c r="J68" s="94" t="n"/>
+      <c r="K68" s="94" t="n"/>
+      <c r="L68" s="94" t="n"/>
+      <c r="M68" s="94" t="n"/>
+      <c r="N68" s="94" t="n"/>
+      <c r="O68" s="94" t="n"/>
+      <c r="P68" s="94" t="n"/>
+      <c r="Q68" s="94" t="n"/>
+      <c r="R68" s="94" t="n"/>
+      <c r="S68" s="94" t="n"/>
+      <c r="T68" s="94" t="n"/>
+      <c r="U68" s="94" t="n"/>
+      <c r="V68" s="94" t="n"/>
+      <c r="W68" s="94" t="n"/>
+      <c r="X68" s="94" t="n"/>
+      <c r="Y68" s="94" t="n"/>
+      <c r="Z68" s="94" t="n"/>
       <c r="AA68" s="1" t="n"/>
       <c r="AB68" s="1" t="n"/>
       <c r="AC68" s="1" t="n"/>
@@ -6910,32 +7501,32 @@
       <c r="BG68" s="1" t="n"/>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="1" t="n"/>
-      <c r="B69" s="1" t="n"/>
-      <c r="C69" s="1" t="n"/>
-      <c r="D69" s="1" t="n"/>
-      <c r="E69" s="1" t="n"/>
-      <c r="F69" s="1" t="n"/>
-      <c r="G69" s="1" t="n"/>
-      <c r="H69" s="1" t="n"/>
-      <c r="I69" s="1" t="n"/>
-      <c r="J69" s="1" t="n"/>
-      <c r="K69" s="1" t="n"/>
-      <c r="L69" s="1" t="n"/>
-      <c r="M69" s="1" t="n"/>
-      <c r="N69" s="1" t="n"/>
-      <c r="O69" s="1" t="n"/>
-      <c r="P69" s="1" t="n"/>
-      <c r="Q69" s="1" t="n"/>
-      <c r="R69" s="1" t="n"/>
-      <c r="S69" s="1" t="n"/>
-      <c r="T69" s="1" t="n"/>
-      <c r="U69" s="1" t="n"/>
-      <c r="V69" s="1" t="n"/>
-      <c r="W69" s="1" t="n"/>
-      <c r="X69" s="1" t="n"/>
-      <c r="Y69" s="1" t="n"/>
-      <c r="Z69" s="1" t="n"/>
+      <c r="A69" s="94" t="n"/>
+      <c r="B69" s="94" t="n"/>
+      <c r="C69" s="94" t="n"/>
+      <c r="D69" s="94" t="n"/>
+      <c r="E69" s="94" t="n"/>
+      <c r="F69" s="94" t="n"/>
+      <c r="G69" s="94" t="n"/>
+      <c r="H69" s="94" t="n"/>
+      <c r="I69" s="94" t="n"/>
+      <c r="J69" s="94" t="n"/>
+      <c r="K69" s="94" t="n"/>
+      <c r="L69" s="94" t="n"/>
+      <c r="M69" s="94" t="n"/>
+      <c r="N69" s="94" t="n"/>
+      <c r="O69" s="94" t="n"/>
+      <c r="P69" s="94" t="n"/>
+      <c r="Q69" s="94" t="n"/>
+      <c r="R69" s="94" t="n"/>
+      <c r="S69" s="94" t="n"/>
+      <c r="T69" s="94" t="n"/>
+      <c r="U69" s="94" t="n"/>
+      <c r="V69" s="94" t="n"/>
+      <c r="W69" s="94" t="n"/>
+      <c r="X69" s="94" t="n"/>
+      <c r="Y69" s="94" t="n"/>
+      <c r="Z69" s="94" t="n"/>
       <c r="AA69" s="1" t="n"/>
       <c r="AB69" s="1" t="n"/>
       <c r="AC69" s="1" t="n"/>
@@ -6971,32 +7562,32 @@
       <c r="BG69" s="1" t="n"/>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="1" t="n"/>
-      <c r="B70" s="1" t="n"/>
-      <c r="C70" s="1" t="n"/>
-      <c r="D70" s="1" t="n"/>
-      <c r="E70" s="1" t="n"/>
-      <c r="F70" s="1" t="n"/>
-      <c r="G70" s="1" t="n"/>
-      <c r="H70" s="1" t="n"/>
-      <c r="I70" s="1" t="n"/>
-      <c r="J70" s="1" t="n"/>
-      <c r="K70" s="1" t="n"/>
-      <c r="L70" s="1" t="n"/>
-      <c r="M70" s="1" t="n"/>
-      <c r="N70" s="1" t="n"/>
-      <c r="O70" s="1" t="n"/>
-      <c r="P70" s="1" t="n"/>
-      <c r="Q70" s="1" t="n"/>
-      <c r="R70" s="1" t="n"/>
-      <c r="S70" s="1" t="n"/>
-      <c r="T70" s="1" t="n"/>
-      <c r="U70" s="1" t="n"/>
-      <c r="V70" s="1" t="n"/>
-      <c r="W70" s="1" t="n"/>
-      <c r="X70" s="1" t="n"/>
-      <c r="Y70" s="1" t="n"/>
-      <c r="Z70" s="1" t="n"/>
+      <c r="A70" s="94" t="n"/>
+      <c r="B70" s="94" t="n"/>
+      <c r="C70" s="94" t="n"/>
+      <c r="D70" s="94" t="n"/>
+      <c r="E70" s="94" t="n"/>
+      <c r="F70" s="94" t="n"/>
+      <c r="G70" s="94" t="n"/>
+      <c r="H70" s="94" t="n"/>
+      <c r="I70" s="94" t="n"/>
+      <c r="J70" s="94" t="n"/>
+      <c r="K70" s="94" t="n"/>
+      <c r="L70" s="94" t="n"/>
+      <c r="M70" s="94" t="n"/>
+      <c r="N70" s="94" t="n"/>
+      <c r="O70" s="94" t="n"/>
+      <c r="P70" s="94" t="n"/>
+      <c r="Q70" s="94" t="n"/>
+      <c r="R70" s="94" t="n"/>
+      <c r="S70" s="94" t="n"/>
+      <c r="T70" s="94" t="n"/>
+      <c r="U70" s="94" t="n"/>
+      <c r="V70" s="94" t="n"/>
+      <c r="W70" s="94" t="n"/>
+      <c r="X70" s="94" t="n"/>
+      <c r="Y70" s="94" t="n"/>
+      <c r="Z70" s="94" t="n"/>
       <c r="AA70" s="1" t="n"/>
       <c r="AB70" s="1" t="n"/>
       <c r="AC70" s="1" t="n"/>
@@ -7032,32 +7623,32 @@
       <c r="BG70" s="1" t="n"/>
     </row>
     <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="1" t="n"/>
-      <c r="B71" s="1" t="n"/>
-      <c r="C71" s="1" t="n"/>
-      <c r="D71" s="1" t="n"/>
-      <c r="E71" s="1" t="n"/>
-      <c r="F71" s="1" t="n"/>
-      <c r="G71" s="1" t="n"/>
-      <c r="H71" s="1" t="n"/>
-      <c r="I71" s="1" t="n"/>
-      <c r="J71" s="1" t="n"/>
-      <c r="K71" s="1" t="n"/>
-      <c r="L71" s="1" t="n"/>
-      <c r="M71" s="1" t="n"/>
-      <c r="N71" s="1" t="n"/>
-      <c r="O71" s="1" t="n"/>
-      <c r="P71" s="1" t="n"/>
-      <c r="Q71" s="1" t="n"/>
-      <c r="R71" s="1" t="n"/>
-      <c r="S71" s="1" t="n"/>
-      <c r="T71" s="1" t="n"/>
-      <c r="U71" s="1" t="n"/>
-      <c r="V71" s="1" t="n"/>
-      <c r="W71" s="1" t="n"/>
-      <c r="X71" s="1" t="n"/>
-      <c r="Y71" s="1" t="n"/>
-      <c r="Z71" s="1" t="n"/>
+      <c r="A71" s="94" t="n"/>
+      <c r="B71" s="94" t="n"/>
+      <c r="C71" s="94" t="n"/>
+      <c r="D71" s="94" t="n"/>
+      <c r="E71" s="94" t="n"/>
+      <c r="F71" s="94" t="n"/>
+      <c r="G71" s="94" t="n"/>
+      <c r="H71" s="94" t="n"/>
+      <c r="I71" s="94" t="n"/>
+      <c r="J71" s="94" t="n"/>
+      <c r="K71" s="94" t="n"/>
+      <c r="L71" s="94" t="n"/>
+      <c r="M71" s="94" t="n"/>
+      <c r="N71" s="94" t="n"/>
+      <c r="O71" s="94" t="n"/>
+      <c r="P71" s="94" t="n"/>
+      <c r="Q71" s="94" t="n"/>
+      <c r="R71" s="94" t="n"/>
+      <c r="S71" s="94" t="n"/>
+      <c r="T71" s="94" t="n"/>
+      <c r="U71" s="94" t="n"/>
+      <c r="V71" s="94" t="n"/>
+      <c r="W71" s="94" t="n"/>
+      <c r="X71" s="94" t="n"/>
+      <c r="Y71" s="94" t="n"/>
+      <c r="Z71" s="94" t="n"/>
       <c r="AA71" s="1" t="n"/>
       <c r="AB71" s="1" t="n"/>
       <c r="AC71" s="1" t="n"/>
@@ -7093,32 +7684,32 @@
       <c r="BG71" s="1" t="n"/>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="1" t="n"/>
-      <c r="B72" s="1" t="n"/>
-      <c r="C72" s="1" t="n"/>
-      <c r="D72" s="1" t="n"/>
-      <c r="E72" s="1" t="n"/>
-      <c r="F72" s="1" t="n"/>
-      <c r="G72" s="1" t="n"/>
-      <c r="H72" s="1" t="n"/>
-      <c r="I72" s="1" t="n"/>
-      <c r="J72" s="1" t="n"/>
-      <c r="K72" s="1" t="n"/>
-      <c r="L72" s="1" t="n"/>
-      <c r="M72" s="1" t="n"/>
-      <c r="N72" s="1" t="n"/>
-      <c r="O72" s="1" t="n"/>
-      <c r="P72" s="1" t="n"/>
-      <c r="Q72" s="1" t="n"/>
-      <c r="R72" s="1" t="n"/>
-      <c r="S72" s="1" t="n"/>
-      <c r="T72" s="1" t="n"/>
-      <c r="U72" s="1" t="n"/>
-      <c r="V72" s="1" t="n"/>
-      <c r="W72" s="1" t="n"/>
-      <c r="X72" s="1" t="n"/>
-      <c r="Y72" s="1" t="n"/>
-      <c r="Z72" s="1" t="n"/>
+      <c r="A72" s="94" t="n"/>
+      <c r="B72" s="94" t="n"/>
+      <c r="C72" s="94" t="n"/>
+      <c r="D72" s="94" t="n"/>
+      <c r="E72" s="94" t="n"/>
+      <c r="F72" s="94" t="n"/>
+      <c r="G72" s="94" t="n"/>
+      <c r="H72" s="94" t="n"/>
+      <c r="I72" s="94" t="n"/>
+      <c r="J72" s="94" t="n"/>
+      <c r="K72" s="94" t="n"/>
+      <c r="L72" s="94" t="n"/>
+      <c r="M72" s="94" t="n"/>
+      <c r="N72" s="94" t="n"/>
+      <c r="O72" s="94" t="n"/>
+      <c r="P72" s="94" t="n"/>
+      <c r="Q72" s="94" t="n"/>
+      <c r="R72" s="94" t="n"/>
+      <c r="S72" s="94" t="n"/>
+      <c r="T72" s="94" t="n"/>
+      <c r="U72" s="94" t="n"/>
+      <c r="V72" s="94" t="n"/>
+      <c r="W72" s="94" t="n"/>
+      <c r="X72" s="94" t="n"/>
+      <c r="Y72" s="94" t="n"/>
+      <c r="Z72" s="94" t="n"/>
       <c r="AA72" s="1" t="n"/>
       <c r="AB72" s="1" t="n"/>
       <c r="AC72" s="1" t="n"/>
@@ -7153,37 +7744,41 @@
       <c r="BF72" s="1" t="n"/>
       <c r="BG72" s="1" t="n"/>
     </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="1" t="n"/>
-      <c r="B73" s="1" t="n"/>
-      <c r="C73" s="1" t="n"/>
-      <c r="D73" s="1" t="n"/>
-      <c r="E73" s="1" t="n"/>
-      <c r="F73" s="1" t="n"/>
-      <c r="G73" s="1" t="n"/>
-      <c r="H73" s="84" t="inlineStr">
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="94" t="n"/>
+      <c r="B73" s="94" t="n"/>
+      <c r="C73" s="94" t="n"/>
+      <c r="D73" s="94" t="n"/>
+      <c r="E73" s="94" t="n"/>
+      <c r="F73" s="94" t="n"/>
+      <c r="G73" s="94" t="n"/>
+      <c r="H73" s="122" t="inlineStr">
         <is>
           <t>DAILY BUDGET</t>
         </is>
       </c>
-      <c r="L73" s="85" t="inlineStr">
+      <c r="I73" s="122" t="n"/>
+      <c r="J73" s="122" t="n"/>
+      <c r="K73" s="122" t="n"/>
+      <c r="L73" s="148" t="inlineStr">
         <is>
           <t>$  65.00</t>
         </is>
       </c>
-      <c r="N73" s="1" t="n"/>
-      <c r="O73" s="1" t="n"/>
-      <c r="P73" s="1" t="n"/>
-      <c r="Q73" s="1" t="n"/>
-      <c r="R73" s="1" t="n"/>
-      <c r="S73" s="1" t="n"/>
-      <c r="T73" s="1" t="n"/>
-      <c r="U73" s="1" t="n"/>
-      <c r="V73" s="1" t="n"/>
-      <c r="W73" s="1" t="n"/>
-      <c r="X73" s="1" t="n"/>
-      <c r="Y73" s="1" t="n"/>
-      <c r="Z73" s="1" t="n"/>
+      <c r="M73" s="105" t="n"/>
+      <c r="N73" s="94" t="n"/>
+      <c r="O73" s="94" t="n"/>
+      <c r="P73" s="94" t="n"/>
+      <c r="Q73" s="94" t="n"/>
+      <c r="R73" s="94" t="n"/>
+      <c r="S73" s="94" t="n"/>
+      <c r="T73" s="94" t="n"/>
+      <c r="U73" s="94" t="n"/>
+      <c r="V73" s="94" t="n"/>
+      <c r="W73" s="94" t="n"/>
+      <c r="X73" s="94" t="n"/>
+      <c r="Y73" s="94" t="n"/>
+      <c r="Z73" s="94" t="n"/>
       <c r="AA73" s="1" t="n"/>
       <c r="AB73" s="1" t="n"/>
       <c r="AC73" s="1" t="n"/>
@@ -7219,32 +7814,32 @@
       <c r="BG73" s="1" t="n"/>
     </row>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="1" t="n"/>
-      <c r="B74" s="1" t="n"/>
-      <c r="C74" s="1" t="n"/>
-      <c r="D74" s="1" t="n"/>
-      <c r="E74" s="1" t="n"/>
-      <c r="F74" s="1" t="n"/>
-      <c r="G74" s="1" t="n"/>
-      <c r="H74" s="1" t="n"/>
-      <c r="I74" s="1" t="n"/>
-      <c r="J74" s="1" t="n"/>
-      <c r="K74" s="1" t="n"/>
-      <c r="L74" s="1" t="n"/>
-      <c r="M74" s="1" t="n"/>
-      <c r="N74" s="1" t="n"/>
-      <c r="O74" s="1" t="n"/>
-      <c r="P74" s="1" t="n"/>
-      <c r="Q74" s="1" t="n"/>
-      <c r="R74" s="1" t="n"/>
-      <c r="S74" s="1" t="n"/>
-      <c r="T74" s="1" t="n"/>
-      <c r="U74" s="1" t="n"/>
-      <c r="V74" s="1" t="n"/>
-      <c r="W74" s="1" t="n"/>
-      <c r="X74" s="1" t="n"/>
-      <c r="Y74" s="1" t="n"/>
-      <c r="Z74" s="1" t="n"/>
+      <c r="A74" s="94" t="n"/>
+      <c r="B74" s="94" t="n"/>
+      <c r="C74" s="94" t="n"/>
+      <c r="D74" s="94" t="n"/>
+      <c r="E74" s="94" t="n"/>
+      <c r="F74" s="94" t="n"/>
+      <c r="G74" s="94" t="n"/>
+      <c r="H74" s="94" t="n"/>
+      <c r="I74" s="94" t="n"/>
+      <c r="J74" s="94" t="n"/>
+      <c r="K74" s="94" t="n"/>
+      <c r="L74" s="94" t="n"/>
+      <c r="M74" s="94" t="n"/>
+      <c r="N74" s="94" t="n"/>
+      <c r="O74" s="94" t="n"/>
+      <c r="P74" s="94" t="n"/>
+      <c r="Q74" s="94" t="n"/>
+      <c r="R74" s="94" t="n"/>
+      <c r="S74" s="94" t="n"/>
+      <c r="T74" s="94" t="n"/>
+      <c r="U74" s="94" t="n"/>
+      <c r="V74" s="94" t="n"/>
+      <c r="W74" s="94" t="n"/>
+      <c r="X74" s="94" t="n"/>
+      <c r="Y74" s="94" t="n"/>
+      <c r="Z74" s="94" t="n"/>
       <c r="AA74" s="1" t="n"/>
       <c r="AB74" s="1" t="n"/>
       <c r="AC74" s="1" t="n"/>
@@ -7280,32 +7875,32 @@
       <c r="BG74" s="1" t="n"/>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="1" t="n"/>
-      <c r="B75" s="1" t="n"/>
-      <c r="C75" s="1" t="n"/>
-      <c r="D75" s="1" t="n"/>
-      <c r="E75" s="1" t="n"/>
-      <c r="F75" s="1" t="n"/>
-      <c r="G75" s="1" t="n"/>
-      <c r="H75" s="1" t="n"/>
-      <c r="I75" s="1" t="n"/>
-      <c r="J75" s="1" t="n"/>
-      <c r="K75" s="1" t="n"/>
-      <c r="L75" s="1" t="n"/>
-      <c r="M75" s="1" t="n"/>
-      <c r="N75" s="1" t="n"/>
-      <c r="O75" s="1" t="n"/>
-      <c r="P75" s="1" t="n"/>
-      <c r="Q75" s="1" t="n"/>
-      <c r="R75" s="1" t="n"/>
-      <c r="S75" s="1" t="n"/>
-      <c r="T75" s="1" t="n"/>
-      <c r="U75" s="1" t="n"/>
-      <c r="V75" s="1" t="n"/>
-      <c r="W75" s="1" t="n"/>
-      <c r="X75" s="1" t="n"/>
-      <c r="Y75" s="1" t="n"/>
-      <c r="Z75" s="1" t="n"/>
+      <c r="A75" s="94" t="n"/>
+      <c r="B75" s="94" t="n"/>
+      <c r="C75" s="94" t="n"/>
+      <c r="D75" s="94" t="n"/>
+      <c r="E75" s="94" t="n"/>
+      <c r="F75" s="94" t="n"/>
+      <c r="G75" s="94" t="n"/>
+      <c r="H75" s="94" t="n"/>
+      <c r="I75" s="94" t="n"/>
+      <c r="J75" s="94" t="n"/>
+      <c r="K75" s="94" t="n"/>
+      <c r="L75" s="94" t="n"/>
+      <c r="M75" s="94" t="n"/>
+      <c r="N75" s="94" t="n"/>
+      <c r="O75" s="94" t="n"/>
+      <c r="P75" s="94" t="n"/>
+      <c r="Q75" s="94" t="n"/>
+      <c r="R75" s="94" t="n"/>
+      <c r="S75" s="94" t="n"/>
+      <c r="T75" s="94" t="n"/>
+      <c r="U75" s="94" t="n"/>
+      <c r="V75" s="94" t="n"/>
+      <c r="W75" s="94" t="n"/>
+      <c r="X75" s="94" t="n"/>
+      <c r="Y75" s="94" t="n"/>
+      <c r="Z75" s="94" t="n"/>
       <c r="AA75" s="1" t="n"/>
       <c r="AB75" s="1" t="n"/>
       <c r="AC75" s="1" t="n"/>
@@ -7340,14 +7935,37 @@
       <c r="BF75" s="1" t="n"/>
       <c r="BG75" s="1" t="n"/>
     </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="1" t="n"/>
-      <c r="B76" s="25" t="inlineStr">
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="94" t="n"/>
+      <c r="B76" s="113" t="inlineStr">
         <is>
           <t>TRANSACTION LOG</t>
         </is>
       </c>
-      <c r="Z76" s="1" t="n"/>
+      <c r="C76" s="113" t="n"/>
+      <c r="D76" s="113" t="n"/>
+      <c r="E76" s="113" t="n"/>
+      <c r="F76" s="113" t="n"/>
+      <c r="G76" s="113" t="n"/>
+      <c r="H76" s="113" t="n"/>
+      <c r="I76" s="105" t="n"/>
+      <c r="J76" s="105" t="n"/>
+      <c r="K76" s="105" t="n"/>
+      <c r="L76" s="105" t="n"/>
+      <c r="M76" s="105" t="n"/>
+      <c r="N76" s="105" t="n"/>
+      <c r="O76" s="105" t="n"/>
+      <c r="P76" s="105" t="n"/>
+      <c r="Q76" s="105" t="n"/>
+      <c r="R76" s="105" t="n"/>
+      <c r="S76" s="105" t="n"/>
+      <c r="T76" s="105" t="n"/>
+      <c r="U76" s="105" t="n"/>
+      <c r="V76" s="105" t="n"/>
+      <c r="W76" s="105" t="n"/>
+      <c r="X76" s="105" t="n"/>
+      <c r="Y76" s="105" t="n"/>
+      <c r="Z76" s="94" t="n"/>
       <c r="AA76" s="1" t="n"/>
       <c r="AB76" s="1" t="n"/>
       <c r="AC76" s="1" t="n"/>
@@ -7382,57 +8000,57 @@
       <c r="BF76" s="1" t="n"/>
       <c r="BG76" s="1" t="n"/>
     </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="1" t="n"/>
-      <c r="B77" s="47" t="inlineStr">
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="94" t="n"/>
+      <c r="B77" s="147" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C77" s="47" t="inlineStr">
+      <c r="C77" s="147" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="D77" s="47" t="inlineStr">
+      <c r="D77" s="147" t="inlineStr">
         <is>
           <t>CATEGORY</t>
         </is>
       </c>
-      <c r="E77" s="47" t="inlineStr">
+      <c r="E77" s="147" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="F77" s="1" t="n"/>
-      <c r="G77" s="47" t="inlineStr">
+      <c r="F77" s="147" t="n"/>
+      <c r="G77" s="147" t="inlineStr">
         <is>
           <t>AMOUNT</t>
         </is>
       </c>
-      <c r="H77" s="47" t="inlineStr">
+      <c r="H77" s="147" t="inlineStr">
         <is>
           <t>BALANCE</t>
         </is>
       </c>
-      <c r="I77" s="1" t="n"/>
-      <c r="J77" s="1" t="n"/>
-      <c r="K77" s="1" t="n"/>
-      <c r="L77" s="1" t="n"/>
-      <c r="M77" s="1" t="n"/>
-      <c r="N77" s="1" t="n"/>
-      <c r="O77" s="1" t="n"/>
-      <c r="P77" s="1" t="n"/>
-      <c r="Q77" s="1" t="n"/>
-      <c r="R77" s="1" t="n"/>
-      <c r="S77" s="1" t="n"/>
-      <c r="T77" s="1" t="n"/>
-      <c r="U77" s="1" t="n"/>
-      <c r="V77" s="1" t="n"/>
-      <c r="W77" s="1" t="n"/>
-      <c r="X77" s="1" t="n"/>
-      <c r="Y77" s="1" t="n"/>
-      <c r="Z77" s="1" t="n"/>
+      <c r="I77" s="94" t="n"/>
+      <c r="J77" s="94" t="n"/>
+      <c r="K77" s="94" t="n"/>
+      <c r="L77" s="94" t="n"/>
+      <c r="M77" s="94" t="n"/>
+      <c r="N77" s="94" t="n"/>
+      <c r="O77" s="94" t="n"/>
+      <c r="P77" s="94" t="n"/>
+      <c r="Q77" s="94" t="n"/>
+      <c r="R77" s="94" t="n"/>
+      <c r="S77" s="94" t="n"/>
+      <c r="T77" s="94" t="n"/>
+      <c r="U77" s="94" t="n"/>
+      <c r="V77" s="94" t="n"/>
+      <c r="W77" s="94" t="n"/>
+      <c r="X77" s="94" t="n"/>
+      <c r="Y77" s="94" t="n"/>
+      <c r="Z77" s="94" t="n"/>
       <c r="AA77" s="1" t="n"/>
       <c r="AB77" s="1" t="n"/>
       <c r="AC77" s="1" t="n"/>
@@ -7467,53 +8085,53 @@
       <c r="BF77" s="1" t="n"/>
       <c r="BG77" s="1" t="n"/>
     </row>
-    <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="1" t="n"/>
-      <c r="B78" s="18" t="inlineStr">
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="94" t="n"/>
+      <c r="B78" s="131" t="inlineStr">
         <is>
           <t>28/04</t>
         </is>
       </c>
-      <c r="C78" s="86" t="inlineStr">
+      <c r="C78" s="131" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D78" s="48" t="inlineStr">
+      <c r="D78" s="131" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="E78" s="87" t="inlineStr">
+      <c r="E78" s="131" t="inlineStr">
         <is>
           <t>Misc expenses</t>
         </is>
       </c>
-      <c r="F78" s="21" t="n"/>
-      <c r="G78" s="88" t="n">
+      <c r="F78" s="131" t="n"/>
+      <c r="G78" s="133" t="n">
         <v>-103.99</v>
       </c>
-      <c r="H78" s="50" t="n">
+      <c r="H78" s="133" t="n">
         <v>3057.01</v>
       </c>
-      <c r="I78" s="1" t="n"/>
-      <c r="J78" s="1" t="n"/>
-      <c r="K78" s="1" t="n"/>
-      <c r="L78" s="1" t="n"/>
-      <c r="M78" s="1" t="n"/>
-      <c r="N78" s="1" t="n"/>
-      <c r="O78" s="1" t="n"/>
-      <c r="P78" s="1" t="n"/>
-      <c r="Q78" s="1" t="n"/>
-      <c r="R78" s="1" t="n"/>
-      <c r="S78" s="1" t="n"/>
-      <c r="T78" s="1" t="n"/>
-      <c r="U78" s="1" t="n"/>
-      <c r="V78" s="1" t="n"/>
-      <c r="W78" s="1" t="n"/>
-      <c r="X78" s="1" t="n"/>
-      <c r="Y78" s="1" t="n"/>
-      <c r="Z78" s="1" t="n"/>
+      <c r="I78" s="94" t="n"/>
+      <c r="J78" s="94" t="n"/>
+      <c r="K78" s="94" t="n"/>
+      <c r="L78" s="94" t="n"/>
+      <c r="M78" s="94" t="n"/>
+      <c r="N78" s="94" t="n"/>
+      <c r="O78" s="94" t="n"/>
+      <c r="P78" s="94" t="n"/>
+      <c r="Q78" s="94" t="n"/>
+      <c r="R78" s="94" t="n"/>
+      <c r="S78" s="94" t="n"/>
+      <c r="T78" s="94" t="n"/>
+      <c r="U78" s="94" t="n"/>
+      <c r="V78" s="94" t="n"/>
+      <c r="W78" s="94" t="n"/>
+      <c r="X78" s="94" t="n"/>
+      <c r="Y78" s="94" t="n"/>
+      <c r="Z78" s="94" t="n"/>
       <c r="AA78" s="1" t="n"/>
       <c r="AB78" s="1" t="n"/>
       <c r="AC78" s="1" t="n"/>
@@ -7548,53 +8166,53 @@
       <c r="BF78" s="1" t="n"/>
       <c r="BG78" s="1" t="n"/>
     </row>
-    <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="1" t="n"/>
-      <c r="B79" s="64" t="inlineStr">
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="94" t="n"/>
+      <c r="B79" s="124" t="inlineStr">
         <is>
           <t>26/04</t>
         </is>
       </c>
-      <c r="C79" s="89" t="inlineStr">
+      <c r="C79" s="124" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D79" s="57" t="inlineStr">
+      <c r="D79" s="124" t="inlineStr">
         <is>
           <t>Pets</t>
         </is>
       </c>
-      <c r="E79" s="90" t="inlineStr">
+      <c r="E79" s="124" t="inlineStr">
         <is>
           <t>Pet expenses</t>
         </is>
       </c>
-      <c r="F79" s="21" t="n"/>
-      <c r="G79" s="91" t="n">
+      <c r="F79" s="124" t="n"/>
+      <c r="G79" s="126" t="n">
         <v>-40.44</v>
       </c>
-      <c r="H79" s="65" t="n">
+      <c r="H79" s="126" t="n">
         <v>3016.57</v>
       </c>
-      <c r="I79" s="1" t="n"/>
-      <c r="J79" s="1" t="n"/>
-      <c r="K79" s="1" t="n"/>
-      <c r="L79" s="1" t="n"/>
-      <c r="M79" s="1" t="n"/>
-      <c r="N79" s="1" t="n"/>
-      <c r="O79" s="1" t="n"/>
-      <c r="P79" s="1" t="n"/>
-      <c r="Q79" s="1" t="n"/>
-      <c r="R79" s="1" t="n"/>
-      <c r="S79" s="1" t="n"/>
-      <c r="T79" s="1" t="n"/>
-      <c r="U79" s="1" t="n"/>
-      <c r="V79" s="1" t="n"/>
-      <c r="W79" s="1" t="n"/>
-      <c r="X79" s="1" t="n"/>
-      <c r="Y79" s="1" t="n"/>
-      <c r="Z79" s="1" t="n"/>
+      <c r="I79" s="94" t="n"/>
+      <c r="J79" s="94" t="n"/>
+      <c r="K79" s="94" t="n"/>
+      <c r="L79" s="94" t="n"/>
+      <c r="M79" s="94" t="n"/>
+      <c r="N79" s="94" t="n"/>
+      <c r="O79" s="94" t="n"/>
+      <c r="P79" s="94" t="n"/>
+      <c r="Q79" s="94" t="n"/>
+      <c r="R79" s="94" t="n"/>
+      <c r="S79" s="94" t="n"/>
+      <c r="T79" s="94" t="n"/>
+      <c r="U79" s="94" t="n"/>
+      <c r="V79" s="94" t="n"/>
+      <c r="W79" s="94" t="n"/>
+      <c r="X79" s="94" t="n"/>
+      <c r="Y79" s="94" t="n"/>
+      <c r="Z79" s="94" t="n"/>
       <c r="AA79" s="1" t="n"/>
       <c r="AB79" s="1" t="n"/>
       <c r="AC79" s="1" t="n"/>
@@ -7629,53 +8247,53 @@
       <c r="BF79" s="1" t="n"/>
       <c r="BG79" s="1" t="n"/>
     </row>
-    <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="1" t="n"/>
-      <c r="B80" s="18" t="inlineStr">
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="94" t="n"/>
+      <c r="B80" s="131" t="inlineStr">
         <is>
           <t>24/04</t>
         </is>
       </c>
-      <c r="C80" s="86" t="inlineStr">
+      <c r="C80" s="131" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D80" s="48" t="inlineStr">
+      <c r="D80" s="131" t="inlineStr">
         <is>
           <t>Shopping</t>
         </is>
       </c>
-      <c r="E80" s="87" t="inlineStr">
+      <c r="E80" s="131" t="inlineStr">
         <is>
           <t>Online shopping</t>
         </is>
       </c>
-      <c r="F80" s="21" t="n"/>
-      <c r="G80" s="88" t="n">
+      <c r="F80" s="131" t="n"/>
+      <c r="G80" s="133" t="n">
         <v>-161.76</v>
       </c>
-      <c r="H80" s="50" t="n">
+      <c r="H80" s="133" t="n">
         <v>2854.81</v>
       </c>
-      <c r="I80" s="1" t="n"/>
-      <c r="J80" s="1" t="n"/>
-      <c r="K80" s="1" t="n"/>
-      <c r="L80" s="1" t="n"/>
-      <c r="M80" s="1" t="n"/>
-      <c r="N80" s="1" t="n"/>
-      <c r="O80" s="1" t="n"/>
-      <c r="P80" s="1" t="n"/>
-      <c r="Q80" s="1" t="n"/>
-      <c r="R80" s="1" t="n"/>
-      <c r="S80" s="1" t="n"/>
-      <c r="T80" s="1" t="n"/>
-      <c r="U80" s="1" t="n"/>
-      <c r="V80" s="1" t="n"/>
-      <c r="W80" s="1" t="n"/>
-      <c r="X80" s="1" t="n"/>
-      <c r="Y80" s="1" t="n"/>
-      <c r="Z80" s="1" t="n"/>
+      <c r="I80" s="94" t="n"/>
+      <c r="J80" s="94" t="n"/>
+      <c r="K80" s="94" t="n"/>
+      <c r="L80" s="94" t="n"/>
+      <c r="M80" s="94" t="n"/>
+      <c r="N80" s="94" t="n"/>
+      <c r="O80" s="94" t="n"/>
+      <c r="P80" s="94" t="n"/>
+      <c r="Q80" s="94" t="n"/>
+      <c r="R80" s="94" t="n"/>
+      <c r="S80" s="94" t="n"/>
+      <c r="T80" s="94" t="n"/>
+      <c r="U80" s="94" t="n"/>
+      <c r="V80" s="94" t="n"/>
+      <c r="W80" s="94" t="n"/>
+      <c r="X80" s="94" t="n"/>
+      <c r="Y80" s="94" t="n"/>
+      <c r="Z80" s="94" t="n"/>
       <c r="AA80" s="1" t="n"/>
       <c r="AB80" s="1" t="n"/>
       <c r="AC80" s="1" t="n"/>
@@ -7710,53 +8328,53 @@
       <c r="BF80" s="1" t="n"/>
       <c r="BG80" s="1" t="n"/>
     </row>
-    <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="1" t="n"/>
-      <c r="B81" s="64" t="inlineStr">
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="94" t="n"/>
+      <c r="B81" s="124" t="inlineStr">
         <is>
           <t>21/04</t>
         </is>
       </c>
-      <c r="C81" s="89" t="inlineStr">
+      <c r="C81" s="124" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D81" s="57" t="inlineStr">
+      <c r="D81" s="124" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
       </c>
-      <c r="E81" s="90" t="inlineStr">
+      <c r="E81" s="124" t="inlineStr">
         <is>
           <t>Pharmacy &amp; medical</t>
         </is>
       </c>
-      <c r="F81" s="21" t="n"/>
-      <c r="G81" s="91" t="n">
+      <c r="F81" s="124" t="n"/>
+      <c r="G81" s="126" t="n">
         <v>-51.99</v>
       </c>
-      <c r="H81" s="65" t="n">
+      <c r="H81" s="126" t="n">
         <v>2802.820000000001</v>
       </c>
-      <c r="I81" s="1" t="n"/>
-      <c r="J81" s="1" t="n"/>
-      <c r="K81" s="1" t="n"/>
-      <c r="L81" s="1" t="n"/>
-      <c r="M81" s="1" t="n"/>
-      <c r="N81" s="1" t="n"/>
-      <c r="O81" s="1" t="n"/>
-      <c r="P81" s="1" t="n"/>
-      <c r="Q81" s="1" t="n"/>
-      <c r="R81" s="1" t="n"/>
-      <c r="S81" s="1" t="n"/>
-      <c r="T81" s="1" t="n"/>
-      <c r="U81" s="1" t="n"/>
-      <c r="V81" s="1" t="n"/>
-      <c r="W81" s="1" t="n"/>
-      <c r="X81" s="1" t="n"/>
-      <c r="Y81" s="1" t="n"/>
-      <c r="Z81" s="1" t="n"/>
+      <c r="I81" s="94" t="n"/>
+      <c r="J81" s="94" t="n"/>
+      <c r="K81" s="94" t="n"/>
+      <c r="L81" s="94" t="n"/>
+      <c r="M81" s="94" t="n"/>
+      <c r="N81" s="94" t="n"/>
+      <c r="O81" s="94" t="n"/>
+      <c r="P81" s="94" t="n"/>
+      <c r="Q81" s="94" t="n"/>
+      <c r="R81" s="94" t="n"/>
+      <c r="S81" s="94" t="n"/>
+      <c r="T81" s="94" t="n"/>
+      <c r="U81" s="94" t="n"/>
+      <c r="V81" s="94" t="n"/>
+      <c r="W81" s="94" t="n"/>
+      <c r="X81" s="94" t="n"/>
+      <c r="Y81" s="94" t="n"/>
+      <c r="Z81" s="94" t="n"/>
       <c r="AA81" s="1" t="n"/>
       <c r="AB81" s="1" t="n"/>
       <c r="AC81" s="1" t="n"/>
@@ -7791,53 +8409,53 @@
       <c r="BF81" s="1" t="n"/>
       <c r="BG81" s="1" t="n"/>
     </row>
-    <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="1" t="n"/>
-      <c r="B82" s="18" t="inlineStr">
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="94" t="n"/>
+      <c r="B82" s="131" t="inlineStr">
         <is>
           <t>18/04</t>
         </is>
       </c>
-      <c r="C82" s="86" t="inlineStr">
+      <c r="C82" s="131" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D82" s="48" t="inlineStr">
+      <c r="D82" s="131" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="E82" s="87" t="inlineStr">
+      <c r="E82" s="131" t="inlineStr">
         <is>
           <t>Personal care</t>
         </is>
       </c>
-      <c r="F82" s="21" t="n"/>
-      <c r="G82" s="88" t="n">
+      <c r="F82" s="131" t="n"/>
+      <c r="G82" s="133" t="n">
         <v>-202.2</v>
       </c>
-      <c r="H82" s="50" t="n">
+      <c r="H82" s="133" t="n">
         <v>2600.620000000001</v>
       </c>
-      <c r="I82" s="1" t="n"/>
-      <c r="J82" s="1" t="n"/>
-      <c r="K82" s="1" t="n"/>
-      <c r="L82" s="1" t="n"/>
-      <c r="M82" s="1" t="n"/>
-      <c r="N82" s="1" t="n"/>
-      <c r="O82" s="1" t="n"/>
-      <c r="P82" s="1" t="n"/>
-      <c r="Q82" s="1" t="n"/>
-      <c r="R82" s="1" t="n"/>
-      <c r="S82" s="1" t="n"/>
-      <c r="T82" s="1" t="n"/>
-      <c r="U82" s="1" t="n"/>
-      <c r="V82" s="1" t="n"/>
-      <c r="W82" s="1" t="n"/>
-      <c r="X82" s="1" t="n"/>
-      <c r="Y82" s="1" t="n"/>
-      <c r="Z82" s="1" t="n"/>
+      <c r="I82" s="94" t="n"/>
+      <c r="J82" s="94" t="n"/>
+      <c r="K82" s="94" t="n"/>
+      <c r="L82" s="94" t="n"/>
+      <c r="M82" s="94" t="n"/>
+      <c r="N82" s="94" t="n"/>
+      <c r="O82" s="94" t="n"/>
+      <c r="P82" s="94" t="n"/>
+      <c r="Q82" s="94" t="n"/>
+      <c r="R82" s="94" t="n"/>
+      <c r="S82" s="94" t="n"/>
+      <c r="T82" s="94" t="n"/>
+      <c r="U82" s="94" t="n"/>
+      <c r="V82" s="94" t="n"/>
+      <c r="W82" s="94" t="n"/>
+      <c r="X82" s="94" t="n"/>
+      <c r="Y82" s="94" t="n"/>
+      <c r="Z82" s="94" t="n"/>
       <c r="AA82" s="1" t="n"/>
       <c r="AB82" s="1" t="n"/>
       <c r="AC82" s="1" t="n"/>
@@ -7872,53 +8490,53 @@
       <c r="BF82" s="1" t="n"/>
       <c r="BG82" s="1" t="n"/>
     </row>
-    <row r="83" ht="17" customHeight="1">
-      <c r="A83" s="1" t="n"/>
-      <c r="B83" s="64" t="inlineStr">
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="94" t="n"/>
+      <c r="B83" s="124" t="inlineStr">
         <is>
           <t>17/04</t>
         </is>
       </c>
-      <c r="C83" s="89" t="inlineStr">
+      <c r="C83" s="124" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D83" s="57" t="inlineStr">
+      <c r="D83" s="124" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="E83" s="90" t="inlineStr">
+      <c r="E83" s="124" t="inlineStr">
         <is>
           <t>Dining out</t>
         </is>
       </c>
-      <c r="F83" s="21" t="n"/>
-      <c r="G83" s="91" t="n">
+      <c r="F83" s="124" t="n"/>
+      <c r="G83" s="126" t="n">
         <v>-109.76</v>
       </c>
-      <c r="H83" s="65" t="n">
+      <c r="H83" s="126" t="n">
         <v>2490.860000000001</v>
       </c>
-      <c r="I83" s="1" t="n"/>
-      <c r="J83" s="1" t="n"/>
-      <c r="K83" s="1" t="n"/>
-      <c r="L83" s="1" t="n"/>
-      <c r="M83" s="1" t="n"/>
-      <c r="N83" s="1" t="n"/>
-      <c r="O83" s="1" t="n"/>
-      <c r="P83" s="1" t="n"/>
-      <c r="Q83" s="1" t="n"/>
-      <c r="R83" s="1" t="n"/>
-      <c r="S83" s="1" t="n"/>
-      <c r="T83" s="1" t="n"/>
-      <c r="U83" s="1" t="n"/>
-      <c r="V83" s="1" t="n"/>
-      <c r="W83" s="1" t="n"/>
-      <c r="X83" s="1" t="n"/>
-      <c r="Y83" s="1" t="n"/>
-      <c r="Z83" s="1" t="n"/>
+      <c r="I83" s="94" t="n"/>
+      <c r="J83" s="94" t="n"/>
+      <c r="K83" s="94" t="n"/>
+      <c r="L83" s="94" t="n"/>
+      <c r="M83" s="94" t="n"/>
+      <c r="N83" s="94" t="n"/>
+      <c r="O83" s="94" t="n"/>
+      <c r="P83" s="94" t="n"/>
+      <c r="Q83" s="94" t="n"/>
+      <c r="R83" s="94" t="n"/>
+      <c r="S83" s="94" t="n"/>
+      <c r="T83" s="94" t="n"/>
+      <c r="U83" s="94" t="n"/>
+      <c r="V83" s="94" t="n"/>
+      <c r="W83" s="94" t="n"/>
+      <c r="X83" s="94" t="n"/>
+      <c r="Y83" s="94" t="n"/>
+      <c r="Z83" s="94" t="n"/>
       <c r="AA83" s="1" t="n"/>
       <c r="AB83" s="1" t="n"/>
       <c r="AC83" s="1" t="n"/>
@@ -7953,33 +8571,33 @@
       <c r="BF83" s="1" t="n"/>
       <c r="BG83" s="1" t="n"/>
     </row>
-    <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="1" t="n"/>
-      <c r="B84" s="1" t="n"/>
-      <c r="C84" s="1" t="n"/>
-      <c r="D84" s="1" t="n"/>
-      <c r="E84" s="1" t="n"/>
-      <c r="F84" s="1" t="n"/>
-      <c r="G84" s="1" t="n"/>
-      <c r="H84" s="1" t="n"/>
-      <c r="I84" s="1" t="n"/>
-      <c r="J84" s="1" t="n"/>
-      <c r="K84" s="1" t="n"/>
-      <c r="L84" s="1" t="n"/>
-      <c r="M84" s="1" t="n"/>
-      <c r="N84" s="1" t="n"/>
-      <c r="O84" s="1" t="n"/>
-      <c r="P84" s="1" t="n"/>
-      <c r="Q84" s="1" t="n"/>
-      <c r="R84" s="1" t="n"/>
-      <c r="S84" s="1" t="n"/>
-      <c r="T84" s="1" t="n"/>
-      <c r="U84" s="1" t="n"/>
-      <c r="V84" s="1" t="n"/>
-      <c r="W84" s="1" t="n"/>
-      <c r="X84" s="1" t="n"/>
-      <c r="Y84" s="1" t="n"/>
-      <c r="Z84" s="1" t="n"/>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="94" t="n"/>
+      <c r="B84" s="131" t="n"/>
+      <c r="C84" s="131" t="n"/>
+      <c r="D84" s="131" t="n"/>
+      <c r="E84" s="131" t="n"/>
+      <c r="F84" s="131" t="n"/>
+      <c r="G84" s="137" t="n"/>
+      <c r="H84" s="137" t="n"/>
+      <c r="I84" s="94" t="n"/>
+      <c r="J84" s="94" t="n"/>
+      <c r="K84" s="94" t="n"/>
+      <c r="L84" s="94" t="n"/>
+      <c r="M84" s="94" t="n"/>
+      <c r="N84" s="94" t="n"/>
+      <c r="O84" s="94" t="n"/>
+      <c r="P84" s="94" t="n"/>
+      <c r="Q84" s="94" t="n"/>
+      <c r="R84" s="94" t="n"/>
+      <c r="S84" s="94" t="n"/>
+      <c r="T84" s="94" t="n"/>
+      <c r="U84" s="94" t="n"/>
+      <c r="V84" s="94" t="n"/>
+      <c r="W84" s="94" t="n"/>
+      <c r="X84" s="94" t="n"/>
+      <c r="Y84" s="94" t="n"/>
+      <c r="Z84" s="94" t="n"/>
       <c r="AA84" s="1" t="n"/>
       <c r="AB84" s="1" t="n"/>
       <c r="AC84" s="1" t="n"/>
@@ -8014,33 +8632,33 @@
       <c r="BF84" s="1" t="n"/>
       <c r="BG84" s="1" t="n"/>
     </row>
-    <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="1" t="n"/>
-      <c r="B85" s="1" t="n"/>
-      <c r="C85" s="1" t="n"/>
-      <c r="D85" s="1" t="n"/>
-      <c r="E85" s="1" t="n"/>
-      <c r="F85" s="1" t="n"/>
-      <c r="G85" s="1" t="n"/>
-      <c r="H85" s="1" t="n"/>
-      <c r="I85" s="1" t="n"/>
-      <c r="J85" s="1" t="n"/>
-      <c r="K85" s="1" t="n"/>
-      <c r="L85" s="1" t="n"/>
-      <c r="M85" s="1" t="n"/>
-      <c r="N85" s="1" t="n"/>
-      <c r="O85" s="1" t="n"/>
-      <c r="P85" s="1" t="n"/>
-      <c r="Q85" s="1" t="n"/>
-      <c r="R85" s="1" t="n"/>
-      <c r="S85" s="1" t="n"/>
-      <c r="T85" s="1" t="n"/>
-      <c r="U85" s="1" t="n"/>
-      <c r="V85" s="1" t="n"/>
-      <c r="W85" s="1" t="n"/>
-      <c r="X85" s="1" t="n"/>
-      <c r="Y85" s="1" t="n"/>
-      <c r="Z85" s="1" t="n"/>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="94" t="n"/>
+      <c r="B85" s="124" t="n"/>
+      <c r="C85" s="124" t="n"/>
+      <c r="D85" s="124" t="n"/>
+      <c r="E85" s="124" t="n"/>
+      <c r="F85" s="124" t="n"/>
+      <c r="G85" s="130" t="n"/>
+      <c r="H85" s="130" t="n"/>
+      <c r="I85" s="94" t="n"/>
+      <c r="J85" s="94" t="n"/>
+      <c r="K85" s="94" t="n"/>
+      <c r="L85" s="94" t="n"/>
+      <c r="M85" s="94" t="n"/>
+      <c r="N85" s="94" t="n"/>
+      <c r="O85" s="94" t="n"/>
+      <c r="P85" s="94" t="n"/>
+      <c r="Q85" s="94" t="n"/>
+      <c r="R85" s="94" t="n"/>
+      <c r="S85" s="94" t="n"/>
+      <c r="T85" s="94" t="n"/>
+      <c r="U85" s="94" t="n"/>
+      <c r="V85" s="94" t="n"/>
+      <c r="W85" s="94" t="n"/>
+      <c r="X85" s="94" t="n"/>
+      <c r="Y85" s="94" t="n"/>
+      <c r="Z85" s="94" t="n"/>
       <c r="AA85" s="1" t="n"/>
       <c r="AB85" s="1" t="n"/>
       <c r="AC85" s="1" t="n"/>
@@ -8076,13 +8694,36 @@
       <c r="BG85" s="1" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="92" t="n"/>
-      <c r="B86" s="93" t="inlineStr">
+      <c r="A86" s="94" t="n"/>
+      <c r="B86" s="121" t="inlineStr">
         <is>
           <t>PLANQLY ASSETS  ·  Budget Planner  ·  Gerado em 20 Abril 2026  ·  Dados de Abril 2026</t>
         </is>
       </c>
-      <c r="Z86" s="92" t="n"/>
+      <c r="C86" s="121" t="n"/>
+      <c r="D86" s="121" t="n"/>
+      <c r="E86" s="121" t="n"/>
+      <c r="F86" s="121" t="n"/>
+      <c r="G86" s="121" t="n"/>
+      <c r="H86" s="121" t="n"/>
+      <c r="I86" s="105" t="n"/>
+      <c r="J86" s="105" t="n"/>
+      <c r="K86" s="105" t="n"/>
+      <c r="L86" s="105" t="n"/>
+      <c r="M86" s="105" t="n"/>
+      <c r="N86" s="105" t="n"/>
+      <c r="O86" s="105" t="n"/>
+      <c r="P86" s="105" t="n"/>
+      <c r="Q86" s="105" t="n"/>
+      <c r="R86" s="105" t="n"/>
+      <c r="S86" s="105" t="n"/>
+      <c r="T86" s="105" t="n"/>
+      <c r="U86" s="105" t="n"/>
+      <c r="V86" s="105" t="n"/>
+      <c r="W86" s="105" t="n"/>
+      <c r="X86" s="105" t="n"/>
+      <c r="Y86" s="105" t="n"/>
+      <c r="Z86" s="94" t="n"/>
       <c r="AA86" s="1" t="n"/>
       <c r="AB86" s="1" t="n"/>
       <c r="AC86" s="1" t="n"/>
@@ -8849,7 +9490,7 @@
       <c r="BF98" s="1" t="n"/>
       <c r="BG98" s="1" t="n"/>
     </row>
-    <row r="99" ht="16" customHeight="1">
+    <row r="99" hidden="1" ht="16" customHeight="1">
       <c r="A99" s="1" t="n"/>
       <c r="B99" s="1" t="n"/>
       <c r="C99" s="1" t="n"/>
@@ -8918,7 +9559,7 @@
       <c r="BF99" s="1" t="n"/>
       <c r="BG99" s="1" t="n"/>
     </row>
-    <row r="100" ht="16" customHeight="1">
+    <row r="100" hidden="1" ht="16" customHeight="1">
       <c r="A100" s="1" t="n"/>
       <c r="B100" s="1" t="n"/>
       <c r="C100" s="1" t="n"/>
@@ -8963,7 +9604,7 @@
           <t>Income</t>
         </is>
       </c>
-      <c r="AO100" s="1" t="n">
+      <c r="AO100" s="149" t="n">
         <v>3161</v>
       </c>
       <c r="AP100" s="1" t="inlineStr">
@@ -8971,10 +9612,10 @@
           <t>Expenses</t>
         </is>
       </c>
-      <c r="AQ100" s="1" t="n">
+      <c r="AQ100" s="149" t="n">
         <v>1914.8</v>
       </c>
-      <c r="AR100" s="1" t="n">
+      <c r="AR100" s="149" t="n">
         <v>1850.07</v>
       </c>
       <c r="AS100" s="1" t="n"/>
@@ -8983,7 +9624,7 @@
           <t>Apr 1</t>
         </is>
       </c>
-      <c r="AU100" s="1" t="n">
+      <c r="AU100" s="149" t="n">
         <v>3161</v>
       </c>
       <c r="AV100" s="1" t="n"/>
@@ -8992,7 +9633,7 @@
           <t>Housing</t>
         </is>
       </c>
-      <c r="AX100" s="1" t="n">
+      <c r="AX100" s="149" t="n">
         <v>708.5</v>
       </c>
       <c r="AY100" s="1" t="n"/>
@@ -9001,7 +9642,7 @@
           <t>Savings</t>
         </is>
       </c>
-      <c r="BA100" s="1" t="n">
+      <c r="BA100" s="149" t="n">
         <v>982</v>
       </c>
       <c r="BB100" s="1" t="n"/>
@@ -9010,16 +9651,16 @@
           <t>Apr 1</t>
         </is>
       </c>
-      <c r="BD100" s="1" t="n">
+      <c r="BD100" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE100" s="1" t="n">
+      <c r="BE100" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF100" s="1" t="n"/>
       <c r="BG100" s="1" t="n"/>
     </row>
-    <row r="101" ht="16" customHeight="1">
+    <row r="101" hidden="1" ht="16" customHeight="1">
       <c r="A101" s="1" t="n"/>
       <c r="B101" s="1" t="n"/>
       <c r="C101" s="1" t="n"/>
@@ -9064,7 +9705,7 @@
           <t>Expenses</t>
         </is>
       </c>
-      <c r="AO101" s="1" t="n">
+      <c r="AO101" s="149" t="n">
         <v>1850</v>
       </c>
       <c r="AP101" s="1" t="inlineStr">
@@ -9072,10 +9713,10 @@
           <t>Bills</t>
         </is>
       </c>
-      <c r="AQ101" s="1" t="n">
+      <c r="AQ101" s="149" t="n">
         <v>766.15</v>
       </c>
-      <c r="AR101" s="1" t="n">
+      <c r="AR101" s="149" t="n">
         <v>766.15</v>
       </c>
       <c r="AS101" s="1" t="n"/>
@@ -9084,7 +9725,7 @@
           <t>Apr 2</t>
         </is>
       </c>
-      <c r="AU101" s="1" t="n">
+      <c r="AU101" s="149" t="n">
         <v>3057</v>
       </c>
       <c r="AV101" s="1" t="n"/>
@@ -9093,7 +9734,7 @@
           <t>Food</t>
         </is>
       </c>
-      <c r="AX101" s="1" t="n">
+      <c r="AX101" s="149" t="n">
         <v>433.28</v>
       </c>
       <c r="AY101" s="1" t="n"/>
@@ -9102,7 +9743,7 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="BA101" s="1" t="n">
+      <c r="BA101" s="149" t="n">
         <v>8175</v>
       </c>
       <c r="BB101" s="1" t="n"/>
@@ -9111,16 +9752,16 @@
           <t>Apr 2</t>
         </is>
       </c>
-      <c r="BD101" s="1" t="n">
+      <c r="BD101" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE101" s="1" t="n">
+      <c r="BE101" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF101" s="1" t="n"/>
       <c r="BG101" s="1" t="n"/>
     </row>
-    <row r="102" ht="16" customHeight="1">
+    <row r="102" hidden="1" ht="16" customHeight="1">
       <c r="A102" s="1" t="n"/>
       <c r="B102" s="1" t="n"/>
       <c r="C102" s="1" t="n"/>
@@ -9165,7 +9806,7 @@
           <t>Bills</t>
         </is>
       </c>
-      <c r="AO102" s="1" t="n">
+      <c r="AO102" s="149" t="n">
         <v>766</v>
       </c>
       <c r="AP102" s="1" t="inlineStr">
@@ -9173,10 +9814,10 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="AQ102" s="1" t="n">
+      <c r="AQ102" s="149" t="n">
         <v>8175</v>
       </c>
-      <c r="AR102" s="1" t="n">
+      <c r="AR102" s="149" t="n">
         <v>8175</v>
       </c>
       <c r="AS102" s="1" t="n"/>
@@ -9185,7 +9826,7 @@
           <t>Apr 3</t>
         </is>
       </c>
-      <c r="AU102" s="1" t="n">
+      <c r="AU102" s="149" t="n">
         <v>2895</v>
       </c>
       <c r="AV102" s="1" t="n"/>
@@ -9194,7 +9835,7 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="AX102" s="1" t="n">
+      <c r="AX102" s="149" t="n">
         <v>202.2</v>
       </c>
       <c r="AY102" s="1" t="n"/>
@@ -9206,16 +9847,16 @@
           <t>Apr 3</t>
         </is>
       </c>
-      <c r="BD102" s="1" t="n">
+      <c r="BD102" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE102" s="1" t="n">
+      <c r="BE102" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF102" s="1" t="n"/>
       <c r="BG102" s="1" t="n"/>
     </row>
-    <row r="103" ht="16" customHeight="1">
+    <row r="103" hidden="1" ht="16" customHeight="1">
       <c r="A103" s="1" t="n"/>
       <c r="B103" s="1" t="n"/>
       <c r="C103" s="1" t="n"/>
@@ -9260,7 +9901,7 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="AO103" s="1" t="n">
+      <c r="AO103" s="149" t="n">
         <v>8175</v>
       </c>
       <c r="AP103" s="1" t="inlineStr">
@@ -9268,10 +9909,10 @@
           <t>Savings</t>
         </is>
       </c>
-      <c r="AQ103" s="1" t="n">
+      <c r="AQ103" s="149" t="n">
         <v>5668</v>
       </c>
-      <c r="AR103" s="1" t="n">
+      <c r="AR103" s="149" t="n">
         <v>982</v>
       </c>
       <c r="AS103" s="1" t="n"/>
@@ -9280,7 +9921,7 @@
           <t>Apr 4</t>
         </is>
       </c>
-      <c r="AU103" s="1" t="n">
+      <c r="AU103" s="149" t="n">
         <v>2733</v>
       </c>
       <c r="AV103" s="1" t="n"/>
@@ -9289,7 +9930,7 @@
           <t>Bills</t>
         </is>
       </c>
-      <c r="AX103" s="1" t="n">
+      <c r="AX103" s="149" t="n">
         <v>147.91</v>
       </c>
       <c r="AY103" s="1" t="n"/>
@@ -9301,16 +9942,16 @@
           <t>Apr 4</t>
         </is>
       </c>
-      <c r="BD103" s="1" t="n">
+      <c r="BD103" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE103" s="1" t="n">
+      <c r="BE103" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF103" s="1" t="n"/>
       <c r="BG103" s="1" t="n"/>
     </row>
-    <row r="104" ht="16" customHeight="1">
+    <row r="104" hidden="1" ht="16" customHeight="1">
       <c r="A104" s="1" t="n"/>
       <c r="B104" s="1" t="n"/>
       <c r="C104" s="1" t="n"/>
@@ -9355,7 +9996,7 @@
           <t>Savings</t>
         </is>
       </c>
-      <c r="AO104" s="1" t="n">
+      <c r="AO104" s="149" t="n">
         <v>982</v>
       </c>
       <c r="AP104" s="1" t="inlineStr">
@@ -9363,10 +10004,10 @@
           <t>Income</t>
         </is>
       </c>
-      <c r="AQ104" s="1" t="n">
+      <c r="AQ104" s="149" t="n">
         <v>3161</v>
       </c>
-      <c r="AR104" s="1" t="n">
+      <c r="AR104" s="149" t="n">
         <v>3161</v>
       </c>
       <c r="AS104" s="1" t="n"/>
@@ -9375,7 +10016,7 @@
           <t>Apr 5</t>
         </is>
       </c>
-      <c r="AU104" s="1" t="n">
+      <c r="AU104" s="149" t="n">
         <v>2530</v>
       </c>
       <c r="AV104" s="1" t="n"/>
@@ -9384,7 +10025,7 @@
           <t>Health</t>
         </is>
       </c>
-      <c r="AX104" s="1" t="n">
+      <c r="AX104" s="149" t="n">
         <v>51.99</v>
       </c>
       <c r="AY104" s="1" t="n"/>
@@ -9396,16 +10037,16 @@
           <t>Apr 5</t>
         </is>
       </c>
-      <c r="BD104" s="1" t="n">
+      <c r="BD104" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE104" s="1" t="n">
+      <c r="BE104" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF104" s="1" t="n"/>
       <c r="BG104" s="1" t="n"/>
     </row>
-    <row r="105" ht="16" customHeight="1">
+    <row r="105" hidden="1" ht="16" customHeight="1">
       <c r="A105" s="1" t="n"/>
       <c r="B105" s="1" t="n"/>
       <c r="C105" s="1" t="n"/>
@@ -9456,7 +10097,7 @@
           <t>Apr 6</t>
         </is>
       </c>
-      <c r="AU105" s="1" t="n">
+      <c r="AU105" s="149" t="n">
         <v>2370</v>
       </c>
       <c r="AV105" s="1" t="n"/>
@@ -9465,7 +10106,7 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="AX105" s="1" t="n">
+      <c r="AX105" s="149" t="n">
         <v>103.99</v>
       </c>
       <c r="AY105" s="1" t="n"/>
@@ -9477,16 +10118,16 @@
           <t>Apr 6</t>
         </is>
       </c>
-      <c r="BD105" s="1" t="n">
+      <c r="BD105" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE105" s="1" t="n">
+      <c r="BE105" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF105" s="1" t="n"/>
       <c r="BG105" s="1" t="n"/>
     </row>
-    <row r="106" ht="16" customHeight="1">
+    <row r="106" hidden="1" ht="16" customHeight="1">
       <c r="A106" s="1" t="n"/>
       <c r="B106" s="1" t="n"/>
       <c r="C106" s="1" t="n"/>
@@ -9537,7 +10178,7 @@
           <t>Apr 7</t>
         </is>
       </c>
-      <c r="AU106" s="1" t="n">
+      <c r="AU106" s="149" t="n">
         <v>2200</v>
       </c>
       <c r="AV106" s="1" t="n"/>
@@ -9546,7 +10187,7 @@
           <t>Shopping</t>
         </is>
       </c>
-      <c r="AX106" s="1" t="n">
+      <c r="AX106" s="149" t="n">
         <v>161.76</v>
       </c>
       <c r="AY106" s="1" t="n"/>
@@ -9558,16 +10199,16 @@
           <t>Apr 7</t>
         </is>
       </c>
-      <c r="BD106" s="1" t="n">
+      <c r="BD106" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE106" s="1" t="n">
+      <c r="BE106" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF106" s="1" t="n"/>
       <c r="BG106" s="1" t="n"/>
     </row>
-    <row r="107" ht="16" customHeight="1">
+    <row r="107" hidden="1" ht="16" customHeight="1">
       <c r="A107" s="1" t="n"/>
       <c r="B107" s="1" t="n"/>
       <c r="C107" s="1" t="n"/>
@@ -9618,7 +10259,7 @@
           <t>Apr 8</t>
         </is>
       </c>
-      <c r="AU107" s="1" t="n">
+      <c r="AU107" s="149" t="n">
         <v>2100</v>
       </c>
       <c r="AV107" s="1" t="n"/>
@@ -9627,7 +10268,7 @@
           <t>Pets</t>
         </is>
       </c>
-      <c r="AX107" s="1" t="n">
+      <c r="AX107" s="149" t="n">
         <v>40.44</v>
       </c>
       <c r="AY107" s="1" t="n"/>
@@ -9639,16 +10280,16 @@
           <t>Apr 8</t>
         </is>
       </c>
-      <c r="BD107" s="1" t="n">
+      <c r="BD107" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE107" s="1" t="n">
+      <c r="BE107" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF107" s="1" t="n"/>
       <c r="BG107" s="1" t="n"/>
     </row>
-    <row r="108" ht="16" customHeight="1">
+    <row r="108" hidden="1" ht="16" customHeight="1">
       <c r="A108" s="1" t="n"/>
       <c r="B108" s="1" t="n"/>
       <c r="C108" s="1" t="n"/>
@@ -9699,7 +10340,7 @@
           <t>Apr 9</t>
         </is>
       </c>
-      <c r="AU108" s="1" t="n">
+      <c r="AU108" s="149" t="n">
         <v>1980</v>
       </c>
       <c r="AV108" s="1" t="n"/>
@@ -9714,16 +10355,16 @@
           <t>Apr 9</t>
         </is>
       </c>
-      <c r="BD108" s="1" t="n">
+      <c r="BD108" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE108" s="1" t="n">
+      <c r="BE108" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF108" s="1" t="n"/>
       <c r="BG108" s="1" t="n"/>
     </row>
-    <row r="109" ht="16" customHeight="1">
+    <row r="109" hidden="1" ht="16" customHeight="1">
       <c r="A109" s="1" t="n"/>
       <c r="B109" s="1" t="n"/>
       <c r="C109" s="1" t="n"/>
@@ -9774,7 +10415,7 @@
           <t>Apr 10</t>
         </is>
       </c>
-      <c r="AU109" s="1" t="n">
+      <c r="AU109" s="149" t="n">
         <v>1860</v>
       </c>
       <c r="AV109" s="1" t="n"/>
@@ -9789,16 +10430,16 @@
           <t>Apr 10</t>
         </is>
       </c>
-      <c r="BD109" s="1" t="n">
+      <c r="BD109" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE109" s="1" t="n">
+      <c r="BE109" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF109" s="1" t="n"/>
       <c r="BG109" s="1" t="n"/>
     </row>
-    <row r="110" ht="16" customHeight="1">
+    <row r="110" hidden="1" ht="16" customHeight="1">
       <c r="A110" s="1" t="n"/>
       <c r="B110" s="1" t="n"/>
       <c r="C110" s="1" t="n"/>
@@ -9849,7 +10490,7 @@
           <t>Apr 11</t>
         </is>
       </c>
-      <c r="AU110" s="1" t="n">
+      <c r="AU110" s="149" t="n">
         <v>1749</v>
       </c>
       <c r="AV110" s="1" t="n"/>
@@ -9864,16 +10505,16 @@
           <t>Apr 11</t>
         </is>
       </c>
-      <c r="BD110" s="1" t="n">
+      <c r="BD110" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE110" s="1" t="n">
+      <c r="BE110" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF110" s="1" t="n"/>
       <c r="BG110" s="1" t="n"/>
     </row>
-    <row r="111" ht="16" customHeight="1">
+    <row r="111" hidden="1" ht="16" customHeight="1">
       <c r="A111" s="1" t="n"/>
       <c r="B111" s="1" t="n"/>
       <c r="C111" s="1" t="n"/>
@@ -9924,7 +10565,7 @@
           <t>Apr 12</t>
         </is>
       </c>
-      <c r="AU111" s="1" t="n">
+      <c r="AU111" s="149" t="n">
         <v>1650</v>
       </c>
       <c r="AV111" s="1" t="n"/>
@@ -9939,16 +10580,16 @@
           <t>Apr 12</t>
         </is>
       </c>
-      <c r="BD111" s="1" t="n">
+      <c r="BD111" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE111" s="1" t="n">
+      <c r="BE111" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF111" s="1" t="n"/>
       <c r="BG111" s="1" t="n"/>
     </row>
-    <row r="112" ht="16" customHeight="1">
+    <row r="112" hidden="1" ht="16" customHeight="1">
       <c r="A112" s="1" t="n"/>
       <c r="B112" s="1" t="n"/>
       <c r="C112" s="1" t="n"/>
@@ -9999,7 +10640,7 @@
           <t>Apr 13</t>
         </is>
       </c>
-      <c r="AU112" s="1" t="n">
+      <c r="AU112" s="149" t="n">
         <v>1500</v>
       </c>
       <c r="AV112" s="1" t="n"/>
@@ -10014,16 +10655,16 @@
           <t>Apr 13</t>
         </is>
       </c>
-      <c r="BD112" s="1" t="n">
+      <c r="BD112" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE112" s="1" t="n">
+      <c r="BE112" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF112" s="1" t="n"/>
       <c r="BG112" s="1" t="n"/>
     </row>
-    <row r="113" ht="16" customHeight="1">
+    <row r="113" hidden="1" ht="16" customHeight="1">
       <c r="A113" s="1" t="n"/>
       <c r="B113" s="1" t="n"/>
       <c r="C113" s="1" t="n"/>
@@ -10074,7 +10715,7 @@
           <t>Apr 14</t>
         </is>
       </c>
-      <c r="AU113" s="1" t="n">
+      <c r="AU113" s="149" t="n">
         <v>1149</v>
       </c>
       <c r="AV113" s="1" t="n"/>
@@ -10089,16 +10730,16 @@
           <t>Apr 14</t>
         </is>
       </c>
-      <c r="BD113" s="1" t="n">
+      <c r="BD113" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE113" s="1" t="n">
+      <c r="BE113" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF113" s="1" t="n"/>
       <c r="BG113" s="1" t="n"/>
     </row>
-    <row r="114" ht="16" customHeight="1">
+    <row r="114" hidden="1" ht="16" customHeight="1">
       <c r="A114" s="1" t="n"/>
       <c r="B114" s="1" t="n"/>
       <c r="C114" s="1" t="n"/>
@@ -10158,16 +10799,16 @@
           <t>Apr 15</t>
         </is>
       </c>
-      <c r="BD114" s="1" t="n">
+      <c r="BD114" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE114" s="1" t="n">
+      <c r="BE114" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF114" s="1" t="n"/>
       <c r="BG114" s="1" t="n"/>
     </row>
-    <row r="115" ht="16" customHeight="1">
+    <row r="115" hidden="1" ht="16" customHeight="1">
       <c r="A115" s="1" t="n"/>
       <c r="B115" s="1" t="n"/>
       <c r="C115" s="1" t="n"/>
@@ -10227,16 +10868,16 @@
           <t>Apr 16</t>
         </is>
       </c>
-      <c r="BD115" s="1" t="n">
+      <c r="BD115" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE115" s="1" t="n">
+      <c r="BE115" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF115" s="1" t="n"/>
       <c r="BG115" s="1" t="n"/>
     </row>
-    <row r="116" ht="16" customHeight="1">
+    <row r="116" hidden="1" ht="16" customHeight="1">
       <c r="A116" s="1" t="n"/>
       <c r="B116" s="1" t="n"/>
       <c r="C116" s="1" t="n"/>
@@ -10296,16 +10937,16 @@
           <t>Apr 17</t>
         </is>
       </c>
-      <c r="BD116" s="1" t="n">
+      <c r="BD116" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE116" s="1" t="n">
+      <c r="BE116" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF116" s="1" t="n"/>
       <c r="BG116" s="1" t="n"/>
     </row>
-    <row r="117" ht="16" customHeight="1">
+    <row r="117" hidden="1" ht="16" customHeight="1">
       <c r="A117" s="1" t="n"/>
       <c r="B117" s="1" t="n"/>
       <c r="C117" s="1" t="n"/>
@@ -10365,16 +11006,16 @@
           <t>Apr 18</t>
         </is>
       </c>
-      <c r="BD117" s="1" t="n">
+      <c r="BD117" s="149" t="n">
         <v>202.2</v>
       </c>
-      <c r="BE117" s="1" t="n">
+      <c r="BE117" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF117" s="1" t="n"/>
       <c r="BG117" s="1" t="n"/>
     </row>
-    <row r="118" ht="16" customHeight="1">
+    <row r="118" hidden="1" ht="16" customHeight="1">
       <c r="A118" s="1" t="n"/>
       <c r="B118" s="1" t="n"/>
       <c r="C118" s="1" t="n"/>
@@ -10434,16 +11075,16 @@
           <t>Apr 19</t>
         </is>
       </c>
-      <c r="BD118" s="1" t="n">
+      <c r="BD118" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE118" s="1" t="n">
+      <c r="BE118" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF118" s="1" t="n"/>
       <c r="BG118" s="1" t="n"/>
     </row>
-    <row r="119" ht="16" customHeight="1">
+    <row r="119" hidden="1" ht="16" customHeight="1">
       <c r="A119" s="1" t="n"/>
       <c r="B119" s="1" t="n"/>
       <c r="C119" s="1" t="n"/>
@@ -10503,16 +11144,16 @@
           <t>Apr 20</t>
         </is>
       </c>
-      <c r="BD119" s="1" t="n">
+      <c r="BD119" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE119" s="1" t="n">
+      <c r="BE119" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF119" s="1" t="n"/>
       <c r="BG119" s="1" t="n"/>
     </row>
-    <row r="120" ht="16" customHeight="1">
+    <row r="120" hidden="1" ht="16" customHeight="1">
       <c r="A120" s="1" t="n"/>
       <c r="B120" s="1" t="n"/>
       <c r="C120" s="1" t="n"/>
@@ -10572,16 +11213,16 @@
           <t>Apr 21</t>
         </is>
       </c>
-      <c r="BD120" s="1" t="n">
+      <c r="BD120" s="149" t="n">
         <v>51.99</v>
       </c>
-      <c r="BE120" s="1" t="n">
+      <c r="BE120" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF120" s="1" t="n"/>
       <c r="BG120" s="1" t="n"/>
     </row>
-    <row r="121" ht="16" customHeight="1">
+    <row r="121" hidden="1" ht="16" customHeight="1">
       <c r="A121" s="1" t="n"/>
       <c r="B121" s="1" t="n"/>
       <c r="C121" s="1" t="n"/>
@@ -10641,16 +11282,16 @@
           <t>Apr 22</t>
         </is>
       </c>
-      <c r="BD121" s="1" t="n">
+      <c r="BD121" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE121" s="1" t="n">
+      <c r="BE121" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF121" s="1" t="n"/>
       <c r="BG121" s="1" t="n"/>
     </row>
-    <row r="122" ht="16" customHeight="1">
+    <row r="122" hidden="1" ht="16" customHeight="1">
       <c r="A122" s="1" t="n"/>
       <c r="B122" s="1" t="n"/>
       <c r="C122" s="1" t="n"/>
@@ -10710,16 +11351,16 @@
           <t>Apr 23</t>
         </is>
       </c>
-      <c r="BD122" s="1" t="n">
+      <c r="BD122" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE122" s="1" t="n">
+      <c r="BE122" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF122" s="1" t="n"/>
       <c r="BG122" s="1" t="n"/>
     </row>
-    <row r="123" ht="16" customHeight="1">
+    <row r="123" hidden="1" ht="16" customHeight="1">
       <c r="A123" s="1" t="n"/>
       <c r="B123" s="1" t="n"/>
       <c r="C123" s="1" t="n"/>
@@ -10779,16 +11420,16 @@
           <t>Apr 24</t>
         </is>
       </c>
-      <c r="BD123" s="1" t="n">
+      <c r="BD123" s="149" t="n">
         <v>161.76</v>
       </c>
-      <c r="BE123" s="1" t="n">
+      <c r="BE123" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF123" s="1" t="n"/>
       <c r="BG123" s="1" t="n"/>
     </row>
-    <row r="124" ht="16" customHeight="1">
+    <row r="124" hidden="1" ht="16" customHeight="1">
       <c r="A124" s="1" t="n"/>
       <c r="B124" s="1" t="n"/>
       <c r="C124" s="1" t="n"/>
@@ -10848,16 +11489,16 @@
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="BD124" s="1" t="n">
+      <c r="BD124" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE124" s="1" t="n">
+      <c r="BE124" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF124" s="1" t="n"/>
       <c r="BG124" s="1" t="n"/>
     </row>
-    <row r="125" ht="16" customHeight="1">
+    <row r="125" hidden="1" ht="16" customHeight="1">
       <c r="A125" s="1" t="n"/>
       <c r="B125" s="1" t="n"/>
       <c r="C125" s="1" t="n"/>
@@ -10917,16 +11558,16 @@
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="BD125" s="1" t="n">
+      <c r="BD125" s="149" t="n">
         <v>40.44</v>
       </c>
-      <c r="BE125" s="1" t="n">
+      <c r="BE125" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF125" s="1" t="n"/>
       <c r="BG125" s="1" t="n"/>
     </row>
-    <row r="126" ht="16" customHeight="1">
+    <row r="126" hidden="1" ht="16" customHeight="1">
       <c r="A126" s="1" t="n"/>
       <c r="B126" s="1" t="n"/>
       <c r="C126" s="1" t="n"/>
@@ -10986,16 +11627,16 @@
           <t>Apr 27</t>
         </is>
       </c>
-      <c r="BD126" s="1" t="n">
+      <c r="BD126" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE126" s="1" t="n">
+      <c r="BE126" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF126" s="1" t="n"/>
       <c r="BG126" s="1" t="n"/>
     </row>
-    <row r="127" ht="16" customHeight="1">
+    <row r="127" hidden="1" ht="16" customHeight="1">
       <c r="A127" s="1" t="n"/>
       <c r="B127" s="1" t="n"/>
       <c r="C127" s="1" t="n"/>
@@ -11055,16 +11696,16 @@
           <t>Apr 28</t>
         </is>
       </c>
-      <c r="BD127" s="1" t="n">
+      <c r="BD127" s="149" t="n">
         <v>109.76</v>
       </c>
-      <c r="BE127" s="1" t="n">
+      <c r="BE127" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF127" s="1" t="n"/>
       <c r="BG127" s="1" t="n"/>
     </row>
-    <row r="128" ht="16" customHeight="1">
+    <row r="128" hidden="1" ht="16" customHeight="1">
       <c r="A128" s="1" t="n"/>
       <c r="B128" s="1" t="n"/>
       <c r="C128" s="1" t="n"/>
@@ -11124,16 +11765,16 @@
           <t>Apr 29</t>
         </is>
       </c>
-      <c r="BD128" s="1" t="n">
+      <c r="BD128" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="BE128" s="1" t="n">
+      <c r="BE128" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF128" s="1" t="n"/>
       <c r="BG128" s="1" t="n"/>
     </row>
-    <row r="129" ht="16" customHeight="1">
+    <row r="129" hidden="1" ht="16" customHeight="1">
       <c r="A129" s="1" t="n"/>
       <c r="B129" s="1" t="n"/>
       <c r="C129" s="1" t="n"/>
@@ -11193,16 +11834,17 @@
           <t>Apr 30</t>
         </is>
       </c>
-      <c r="BD129" s="1" t="n">
+      <c r="BD129" s="149" t="n">
         <v>103.99</v>
       </c>
-      <c r="BE129" s="1" t="n">
+      <c r="BE129" s="149" t="n">
         <v>65</v>
       </c>
       <c r="BF129" s="1" t="n"/>
       <c r="BG129" s="1" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="B77:H85"/>
   <mergeCells count="101">
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B22:C22"/>
@@ -11306,7 +11948,20 @@
     <mergeCell ref="S31:T31"/>
     <mergeCell ref="F31"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="K31:K45">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="1" stopIfTrue="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G78:G85">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0" stopIfTrue="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/templates/PLANQLY_PREMIUM_TEMPLATE.xlsx
+++ b/templates/PLANQLY_PREMIUM_TEMPLATE.xlsx
@@ -1220,14 +1220,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
-    <spPr>
-      <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-      <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:noFill/>
-      </a:ln>
-    </spPr>
     <title>
       <tx>
         <rich>
@@ -1244,12 +1237,6 @@
       </tx>
     </title>
     <plotArea>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-        </a:ln>
-      </spPr>
       <pieChart>
         <varyColors val="1"/>
         <ser>
@@ -1316,9 +1303,9 @@
             </spPr>
           </dPt>
           <cat>
-            <numRef>
+            <strRef>
               <f>'PLANQLY Budget'!$AN$100:$AN$104</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1335,12 +1322,6 @@
     </plotArea>
     <legend>
       <legendPos val="r"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-        </a:ln>
-      </spPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1350,14 +1331,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
-    <spPr>
-      <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-      <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:noFill/>
-      </a:ln>
-    </spPr>
     <title>
       <tx>
         <rich>
@@ -1374,12 +1348,6 @@
       </tx>
     </title>
     <plotArea>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-        </a:ln>
-      </spPr>
       <barChart>
         <barDir val="col"/>
         <grouping val="clustered"/>
@@ -1400,9 +1368,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'PLANQLY Budget'!$AP$100:$AP$104</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1427,9 +1395,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'PLANQLY Budget'!$AP$100:$AP$104</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1467,12 +1435,6 @@
     </plotArea>
     <legend>
       <legendPos val="r"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-        </a:ln>
-      </spPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1482,14 +1444,7 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
-    <spPr>
-      <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-      <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:noFill/>
-      </a:ln>
-    </spPr>
     <title>
       <tx>
         <rich>
@@ -1506,12 +1461,6 @@
       </tx>
     </title>
     <plotArea>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-        </a:ln>
-      </spPr>
       <areaChart>
         <grouping val="standard"/>
         <ser>
@@ -1529,9 +1478,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'PLANQLY Budget'!$AT$100:$AT$113</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1567,12 +1516,6 @@
     </plotArea>
     <legend>
       <legendPos val="r"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-        </a:ln>
-      </spPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1582,14 +1525,7 @@
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
-    <spPr>
-      <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-      <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:noFill/>
-      </a:ln>
-    </spPr>
     <title>
       <tx>
         <rich>
@@ -1606,12 +1542,6 @@
       </tx>
     </title>
     <plotArea>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-        </a:ln>
-      </spPr>
       <barChart>
         <barDir val="col"/>
         <grouping val="clustered"/>
@@ -1649,9 +1579,9 @@
             </spPr>
           </dPt>
           <cat>
-            <numRef>
+            <strRef>
               <f>'PLANQLY Budget'!$AZ$100:$AZ$101</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1688,12 +1618,6 @@
     </plotArea>
     <legend>
       <legendPos val="r"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-        </a:ln>
-      </spPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1703,14 +1627,7 @@
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
-    <spPr>
-      <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-      <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:noFill/>
-      </a:ln>
-    </spPr>
     <title>
       <tx>
         <rich>
@@ -1727,12 +1644,6 @@
       </tx>
     </title>
     <plotArea>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-        </a:ln>
-      </spPr>
       <lineChart>
         <grouping val="standard"/>
         <ser>
@@ -1755,9 +1666,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'PLANQLY Budget'!$BC$100:$BC$129</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1785,9 +1696,9 @@
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'PLANQLY Budget'!$BC$100:$BC$129</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1823,12 +1734,6 @@
     </plotArea>
     <legend>
       <legendPos val="r"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-        </a:ln>
-      </spPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1838,14 +1743,7 @@
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
-    <spPr>
-      <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-      <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:noFill/>
-      </a:ln>
-    </spPr>
     <title>
       <tx>
         <rich>
@@ -1862,12 +1760,6 @@
       </tx>
     </title>
     <plotArea>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-        </a:ln>
-      </spPr>
       <pieChart>
         <varyColors val="1"/>
         <ser>
@@ -1967,9 +1859,9 @@
             </spPr>
           </dPt>
           <cat>
-            <numRef>
+            <strRef>
               <f>'PLANQLY Budget'!$AW$100:$AW$107</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -1985,12 +1877,6 @@
     </plotArea>
     <legend>
       <legendPos val="r"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-        </a:ln>
-      </spPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>

--- a/templates/PLANQLY_PREMIUM_TEMPLATE.xlsx
+++ b/templates/PLANQLY_PREMIUM_TEMPLATE.xlsx
@@ -1303,9 +1303,9 @@
             </spPr>
           </dPt>
           <cat>
-            <strRef>
+            <numRef>
               <f>'PLANQLY Budget'!$AN$100:$AN$104</f>
-            </strRef>
+            </numRef>
           </cat>
           <val>
             <numRef>
@@ -1368,9 +1368,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <strRef>
+            <numRef>
               <f>'PLANQLY Budget'!$AP$100:$AP$104</f>
-            </strRef>
+            </numRef>
           </cat>
           <val>
             <numRef>
@@ -1395,9 +1395,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <strRef>
+            <numRef>
               <f>'PLANQLY Budget'!$AP$100:$AP$104</f>
-            </strRef>
+            </numRef>
           </cat>
           <val>
             <numRef>
@@ -1478,9 +1478,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <strRef>
+            <numRef>
               <f>'PLANQLY Budget'!$AT$100:$AT$113</f>
-            </strRef>
+            </numRef>
           </cat>
           <val>
             <numRef>
@@ -1579,9 +1579,9 @@
             </spPr>
           </dPt>
           <cat>
-            <strRef>
+            <numRef>
               <f>'PLANQLY Budget'!$AZ$100:$AZ$101</f>
-            </strRef>
+            </numRef>
           </cat>
           <val>
             <numRef>
@@ -1666,9 +1666,9 @@
             </spPr>
           </marker>
           <cat>
-            <strRef>
+            <numRef>
               <f>'PLANQLY Budget'!$BC$100:$BC$129</f>
-            </strRef>
+            </numRef>
           </cat>
           <val>
             <numRef>
@@ -1696,9 +1696,9 @@
             </spPr>
           </marker>
           <cat>
-            <strRef>
+            <numRef>
               <f>'PLANQLY Budget'!$BC$100:$BC$129</f>
-            </strRef>
+            </numRef>
           </cat>
           <val>
             <numRef>
@@ -1859,9 +1859,9 @@
             </spPr>
           </dPt>
           <cat>
-            <strRef>
+            <numRef>
               <f>'PLANQLY Budget'!$AW$100:$AW$107</f>
-            </strRef>
+            </numRef>
           </cat>
           <val>
             <numRef>
@@ -1886,19 +1886,14 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="twoCell">
+  <oneCellAnchor>
     <from>
       <col>7</col>
       <colOff>0</colOff>
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <to>
-      <col>13</col>
-      <colOff>0</colOff>
-      <row>28</row>
-      <rowOff>0</rowOff>
-    </to>
+    <ext cx="3600000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1912,20 +1907,15 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="twoCell">
+  </oneCellAnchor>
+  <oneCellAnchor>
     <from>
       <col>13</col>
       <colOff>0</colOff>
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <to>
-      <col>20</col>
-      <colOff>0</colOff>
-      <row>28</row>
-      <rowOff>0</rowOff>
-    </to>
+    <ext cx="5040000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1939,20 +1929,15 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="twoCell">
+  </oneCellAnchor>
+  <oneCellAnchor>
     <from>
       <col>20</col>
       <colOff>0</colOff>
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <to>
-      <col>26</col>
-      <colOff>0</colOff>
-      <row>28</row>
-      <rowOff>0</rowOff>
-    </to>
+    <ext cx="5760000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1966,20 +1951,15 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="twoCell">
+  </oneCellAnchor>
+  <oneCellAnchor>
     <from>
       <col>1</col>
       <colOff>0</colOff>
       <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <to>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>0</rowOff>
-    </to>
+    <ext cx="4320000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -1993,20 +1973,15 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="twoCell">
+  </oneCellAnchor>
+  <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <to>
-      <col>17</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>0</rowOff>
-    </to>
+    <ext cx="7200000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -2020,20 +1995,15 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="twoCell">
+  </oneCellAnchor>
+  <oneCellAnchor>
     <from>
-      <col>17</col>
+      <col>16</col>
       <colOff>0</colOff>
       <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <to>
-      <col>26</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>0</rowOff>
-    </to>
+    <ext cx="5040000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -2047,7 +2017,7 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </twoCellAnchor>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
